--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ember</v>
+        <v>Sick Of Love</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/ember/1880484164</v>
+        <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-08</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G2" t="str">
-        <v>3:25</v>
+        <v>3:36</v>
       </c>
       <c r="H2" t="str">
-        <v>Iceage</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/ember/1880484160</v>
+        <v>https://music.apple.com/us/album/sick-of-love/1857952252</v>
       </c>
       <c r="L2" t="str">
-        <v>Ember - Iceage</v>
+        <v>Sick Of Love - Lykke Li</v>
       </c>
     </row>
     <row r="3">
@@ -778,13 +778,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Turnaround</v>
+        <v>Ember</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
+        <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-08</v>
@@ -793,25 +793,25 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Turnaround / I'm Hooked - Single</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G11" t="str">
-        <v>3:14</v>
+        <v>3:25</v>
       </c>
       <c r="H11" t="str">
-        <v>54 Ultra</v>
+        <v>Iceage</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
+        <v>https://music.apple.com/us/album/ember/1880484160</v>
       </c>
       <c r="L11" t="str">
-        <v>Turnaround - 54 Ultra</v>
+        <v>Ember - Iceage</v>
       </c>
     </row>
     <row r="12">
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Jet Lag Mouth</v>
+        <v>Turnaround</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
+        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-08</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Jet Lag Mouth - Single</v>
+        <v>Turnaround / I'm Hooked - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>2:32</v>
+        <v>3:14</v>
       </c>
       <c r="H13" t="str">
-        <v>In Color</v>
+        <v>54 Ultra</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
+        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
       </c>
       <c r="L13" t="str">
-        <v>Jet Lag Mouth - In Color</v>
+        <v>Turnaround - 54 Ultra</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Home on the Range</v>
+        <v>Jet Lag Mouth</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
+        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-08</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Jet Lag Mouth - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>1:37</v>
+        <v>2:32</v>
       </c>
       <c r="H14" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>In Color</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
+        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
       </c>
       <c r="L14" t="str">
-        <v>Home on the Range - Earl Sweatshirt</v>
+        <v>Jet Lag Mouth - In Color</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Back Home</v>
+        <v>Home on the Range</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/back-home/1870867424</v>
+        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-08</v>
@@ -948,33 +948,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G15" t="str">
-        <v>1:36</v>
+        <v>1:37</v>
       </c>
       <c r="H15" t="str">
-        <v>MIKE</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/back-home/1870867411</v>
+        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
       </c>
       <c r="L15" t="str">
-        <v>Back Home - MIKE</v>
+        <v>Home on the Range - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Reputation</v>
+        <v>Back Home</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/reputation/1888615203</v>
+        <v>https://music.apple.com/us/song/back-home/1870867424</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-08</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Reputation / Bobby - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G16" t="str">
-        <v>3:55</v>
+        <v>1:36</v>
       </c>
       <c r="H16" t="str">
-        <v>Ravyn Lenae</v>
+        <v>MIKE</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/reputation/1888615202</v>
+        <v>https://music.apple.com/us/album/back-home/1870867411</v>
       </c>
       <c r="L16" t="str">
-        <v>Reputation - Ravyn Lenae</v>
+        <v>Back Home - MIKE</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>MURAL</v>
+        <v>Reputation</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/mural/1885914724</v>
+        <v>https://music.apple.com/us/song/reputation/1888615203</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-08</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>Reputation / Bobby - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>3:26</v>
+        <v>3:55</v>
       </c>
       <c r="H17" t="str">
-        <v>Swae Lee</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/mural/1885914714</v>
+        <v>https://music.apple.com/us/album/reputation/1888615202</v>
       </c>
       <c r="L17" t="str">
-        <v>MURAL - Swae Lee</v>
+        <v>Reputation - Ravyn Lenae</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Business &amp; Personal (second half)</v>
+        <v>MURAL</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/business-personal-second-half/1889934787</v>
+        <v>https://music.apple.com/us/song/mural/1885914724</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-08</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Business &amp; Personal - Single</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G18" t="str">
-        <v>2:19</v>
+        <v>3:26</v>
       </c>
       <c r="H18" t="str">
-        <v>Latto</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/business-personal-second-half/1889934634</v>
+        <v>https://music.apple.com/us/album/mural/1885914714</v>
       </c>
       <c r="L18" t="str">
-        <v>Business &amp; Personal (second half) - Latto</v>
+        <v>MURAL - Swae Lee</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Beams</v>
+        <v>Business &amp; Personal (second half)</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/beams/1862570896</v>
+        <v>https://music.apple.com/us/song/business-personal-second-half/1889934787</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-08</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Business &amp; Personal - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:39</v>
+        <v>2:19</v>
       </c>
       <c r="H19" t="str">
-        <v>Arlo Parks</v>
+        <v>Latto</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/beams/1862570378</v>
+        <v>https://music.apple.com/us/album/business-personal-second-half/1889934634</v>
       </c>
       <c r="L19" t="str">
-        <v>Beams - Arlo Parks</v>
+        <v>Business &amp; Personal (second half) - Latto</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Hysteria</v>
+        <v>Beams</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/hysteria/1887407036</v>
+        <v>https://music.apple.com/us/song/beams/1862570896</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-08</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Hysteria - Single</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G20" t="str">
-        <v>2:23</v>
+        <v>3:39</v>
       </c>
       <c r="H20" t="str">
-        <v>Bebe Rexha</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/hysteria/1887407035</v>
+        <v>https://music.apple.com/us/album/beams/1862570378</v>
       </c>
       <c r="L20" t="str">
-        <v>Hysteria - Bebe Rexha</v>
+        <v>Beams - Arlo Parks</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Need Your Love</v>
+        <v>Hysteria</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/need-your-love/1884740423</v>
+        <v>https://music.apple.com/us/song/hysteria/1887407036</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-08</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Need Your Love - Single</v>
+        <v>Hysteria - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>3:58</v>
+        <v>2:23</v>
       </c>
       <c r="H21" t="str">
-        <v>OneRepublic</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/need-your-love/1884740422</v>
+        <v>https://music.apple.com/us/album/hysteria/1887407035</v>
       </c>
       <c r="L21" t="str">
-        <v>Need Your Love - OneRepublic</v>
+        <v>Hysteria - Bebe Rexha</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>My Mouth Is Lonely For You (from Mother Mary)</v>
+        <v>Need Your Love</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/my-mouth-is-lonely-for-you-from-mother-mary/1886744205</v>
+        <v>https://music.apple.com/us/song/need-your-love/1884740423</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-08</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>My Mouth Is Lonely For You (from Mother Mary) - Single</v>
+        <v>Need Your Love - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>4:04</v>
+        <v>3:58</v>
       </c>
       <c r="H22" t="str">
-        <v>Anne Hathaway</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/my-mouth-is-lonely-for-you-from-mother-mary/1886744203</v>
+        <v>https://music.apple.com/us/album/need-your-love/1884740422</v>
       </c>
       <c r="L22" t="str">
-        <v>My Mouth Is Lonely For You (from Mother Mary) - Anne Hathaway</v>
+        <v>Need Your Love - OneRepublic</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SORRY! CRASH!</v>
+        <v>My Mouth Is Lonely For You (from Mother Mary)</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/sorry-crash/1886485698</v>
+        <v>https://music.apple.com/us/song/my-mouth-is-lonely-for-you-from-mother-mary/1886744205</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-08</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>My Mouth Is Lonely For You (from Mother Mary) - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>3:09</v>
+        <v>4:04</v>
       </c>
       <c r="H23" t="str">
-        <v>Ecca Vandal</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/sorry-crash/1886485694</v>
+        <v>https://music.apple.com/us/album/my-mouth-is-lonely-for-you-from-mother-mary/1886744203</v>
       </c>
       <c r="L23" t="str">
-        <v>SORRY! CRASH! - Ecca Vandal</v>
+        <v>My Mouth Is Lonely For You (from Mother Mary) - Anne Hathaway</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Shine Again</v>
+        <v>SORRY! CRASH!</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/shine-again/1887991690</v>
+        <v>https://music.apple.com/us/song/sorry-crash/1886485698</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-08</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Shine Again - Single</v>
+        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
       </c>
       <c r="G24" t="str">
-        <v>4:05</v>
+        <v>3:09</v>
       </c>
       <c r="H24" t="str">
-        <v>Weezer</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/shine-again/1887991688</v>
+        <v>https://music.apple.com/us/album/sorry-crash/1886485694</v>
       </c>
       <c r="L24" t="str">
-        <v>Shine Again - Weezer</v>
+        <v>SORRY! CRASH! - Ecca Vandal</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Choose Love</v>
+        <v>Shine Again</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/choose-love/1877910665</v>
+        <v>https://music.apple.com/us/song/shine-again/1887991690</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-08</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Long Long Road</v>
+        <v>Shine Again - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:54</v>
+        <v>4:05</v>
       </c>
       <c r="H25" t="str">
-        <v>Ringo Starr</v>
+        <v>Weezer</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/choose-love/1877910655</v>
+        <v>https://music.apple.com/us/album/shine-again/1887991688</v>
       </c>
       <c r="L25" t="str">
-        <v>Choose Love - Ringo Starr</v>
+        <v>Shine Again - Weezer</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>BABYRECORDS.</v>
+        <v>Choose Love</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/babyrecords/1888590545</v>
+        <v>https://music.apple.com/us/song/choose-love/1877910665</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-08</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>BABYRECORDS. - Single</v>
+        <v>Long Long Road</v>
       </c>
       <c r="G26" t="str">
-        <v>2:29</v>
+        <v>3:54</v>
       </c>
       <c r="H26" t="str">
-        <v>Álvaro Díaz</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/babyrecords/1888590544</v>
+        <v>https://music.apple.com/us/album/choose-love/1877910655</v>
       </c>
       <c r="L26" t="str">
-        <v>BABYRECORDS. - Álvaro Díaz</v>
+        <v>Choose Love - Ringo Starr</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Paperbag Boy</v>
+        <v>BABYRECORDS.</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/paperbag-boy/1889345415</v>
+        <v>https://music.apple.com/us/song/babyrecords/1888590545</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-08</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Paperbag Boy - Single</v>
+        <v>BABYRECORDS. - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>3:11</v>
+        <v>2:29</v>
       </c>
       <c r="H27" t="str">
-        <v>Trippie Redd</v>
+        <v>Álvaro Díaz</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/trippie-redd/1203172438</v>
+        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/paperbag-boy/1889345414</v>
+        <v>https://music.apple.com/us/album/babyrecords/1888590544</v>
       </c>
       <c r="L27" t="str">
-        <v>Paperbag Boy - Trippie Redd</v>
+        <v>BABYRECORDS. - Álvaro Díaz</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>I AM</v>
+        <v>Paperbag Boy</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/i-am/1880890454</v>
+        <v>https://music.apple.com/us/song/paperbag-boy/1889345415</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-08</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>CLARITY OF MIND</v>
+        <v>Paperbag Boy - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>3:12</v>
+        <v>3:11</v>
       </c>
       <c r="H28" t="str">
-        <v>OMAH LAY</v>
+        <v>Trippie Redd</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
+        <v>https://music.apple.com/us/artist/trippie-redd/1203172438</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/i-am/1880890112</v>
+        <v>https://music.apple.com/us/album/paperbag-boy/1889345414</v>
       </c>
       <c r="L28" t="str">
-        <v>I AM - OMAH LAY</v>
+        <v>Paperbag Boy - Trippie Redd</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Want Love</v>
+        <v>I AM</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/want-love/1886384365</v>
+        <v>https://music.apple.com/us/song/i-am/1880890454</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-08</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Want Love - Single</v>
+        <v>CLARITY OF MIND</v>
       </c>
       <c r="G29" t="str">
-        <v>3:20</v>
+        <v>3:12</v>
       </c>
       <c r="H29" t="str">
-        <v>Mary J. Blige</v>
+        <v>OMAH LAY</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/want-love/1886384355</v>
+        <v>https://music.apple.com/us/album/i-am/1880890112</v>
       </c>
       <c r="L29" t="str">
-        <v>Want Love - Mary J. Blige</v>
+        <v>I AM - OMAH LAY</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Live, Love, Learn</v>
+        <v>Want Love</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/live-love-learn/1884749128</v>
+        <v>https://music.apple.com/us/song/want-love/1886384365</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-08</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Live, Love, Learn - Single</v>
+        <v>Want Love - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>4:19</v>
+        <v>3:20</v>
       </c>
       <c r="H30" t="str">
-        <v>Estelle</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/estelle/27060010</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/live-love-learn/1884749126</v>
+        <v>https://music.apple.com/us/album/want-love/1886384355</v>
       </c>
       <c r="L30" t="str">
-        <v>Live, Love, Learn - Estelle</v>
+        <v>Want Love - Mary J. Blige</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Footlights</v>
+        <v>Live, Love, Learn</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/footlights/1885660551</v>
+        <v>https://music.apple.com/us/song/live-love-learn/1884749128</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-08</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Footlights - Single</v>
+        <v>Live, Love, Learn - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>4:24</v>
+        <v>4:19</v>
       </c>
       <c r="H31" t="str">
-        <v>Cody Johnson</v>
+        <v>Estelle</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/estelle/27060010</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/footlights/1885660550</v>
+        <v>https://music.apple.com/us/album/live-love-learn/1884749126</v>
       </c>
       <c r="L31" t="str">
-        <v>Footlights - Cody Johnson</v>
+        <v>Live, Love, Learn - Estelle</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Remember to Forget</v>
+        <v>Footlights</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/remember-to-forget/1887886676</v>
+        <v>https://music.apple.com/us/song/footlights/1885660551</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-08</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Remember to Forget - Single</v>
+        <v>Footlights - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>3:39</v>
+        <v>4:24</v>
       </c>
       <c r="H32" t="str">
-        <v>Hailey Whitters</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/hailey-whitters/553410914</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/remember-to-forget/1887886674</v>
+        <v>https://music.apple.com/us/album/footlights/1885660550</v>
       </c>
       <c r="L32" t="str">
-        <v>Remember to Forget - Hailey Whitters</v>
+        <v>Footlights - Cody Johnson</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Sun Comes Up Tremendous</v>
+        <v>Remember to Forget</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/sun-comes-up-tremendous/1883229766</v>
+        <v>https://music.apple.com/us/song/remember-to-forget/1887886676</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-08</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Sun Comes Up Tremendous - Single</v>
+        <v>Remember to Forget - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:33</v>
+        <v>3:39</v>
       </c>
       <c r="H33" t="str">
-        <v>Disclosure</v>
+        <v>Hailey Whitters</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/disclosure/520848228</v>
+        <v>https://music.apple.com/us/artist/hailey-whitters/553410914</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/sun-comes-up-tremendous/1883229765</v>
+        <v>https://music.apple.com/us/album/remember-to-forget/1887886674</v>
       </c>
       <c r="L33" t="str">
-        <v>Sun Comes Up Tremendous - Disclosure</v>
+        <v>Remember to Forget - Hailey Whitters</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Say So</v>
+        <v>Sun Comes Up Tremendous</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/say-so/1888326036</v>
+        <v>https://music.apple.com/us/song/sun-comes-up-tremendous/1883229766</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-08</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Say So - Single</v>
+        <v>Sun Comes Up Tremendous - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:21</v>
+        <v>3:33</v>
       </c>
       <c r="H34" t="str">
-        <v>Dan + Shay</v>
+        <v>Disclosure</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
+        <v>https://music.apple.com/us/artist/disclosure/520848228</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/say-so/1888325785</v>
+        <v>https://music.apple.com/us/album/sun-comes-up-tremendous/1883229765</v>
       </c>
       <c r="L34" t="str">
-        <v>Say So - Dan + Shay</v>
+        <v>Sun Comes Up Tremendous - Disclosure</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Fantasy</v>
+        <v>Say So</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1880361475</v>
+        <v>https://music.apple.com/us/song/say-so/1888326036</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-08</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Lost, Found &amp; Forgotten...</v>
+        <v>Say So - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>4:07</v>
+        <v>3:21</v>
       </c>
       <c r="H35" t="str">
-        <v>Chris Stussy</v>
+        <v>Dan + Shay</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1880361449</v>
+        <v>https://music.apple.com/us/album/say-so/1888325785</v>
       </c>
       <c r="L35" t="str">
-        <v>Fantasy - Chris Stussy</v>
+        <v>Say So - Dan + Shay</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Favour</v>
+        <v>Fantasy</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/favour/1885941038</v>
+        <v>https://music.apple.com/us/song/fantasy/1880361475</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-08</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Favour - Single</v>
+        <v>Lost, Found &amp; Forgotten...</v>
       </c>
       <c r="G36" t="str">
-        <v>3:14</v>
+        <v>4:07</v>
       </c>
       <c r="H36" t="str">
-        <v>FISHER</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/favour/1885941037</v>
+        <v>https://music.apple.com/us/album/fantasy/1880361449</v>
       </c>
       <c r="L36" t="str">
-        <v>Favour - FISHER</v>
+        <v>Fantasy - Chris Stussy</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dangerous Lover</v>
+        <v>Favour</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/dangerous-lover/1884781285</v>
+        <v>https://music.apple.com/us/song/favour/1885941038</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-08</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Dangerous Lover - Single</v>
+        <v>Favour - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>3:24</v>
+        <v>3:14</v>
       </c>
       <c r="H37" t="str">
-        <v>Sekou</v>
+        <v>FISHER</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/sekou/1685844750</v>
+        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/dangerous-lover/1884781284</v>
+        <v>https://music.apple.com/us/album/favour/1885941037</v>
       </c>
       <c r="L37" t="str">
-        <v>Dangerous Lover - Sekou</v>
+        <v>Favour - FISHER</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Foolsong</v>
+        <v>Dangerous Lover</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/foolsong/1886215975</v>
+        <v>https://music.apple.com/us/song/dangerous-lover/1884781285</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-08</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Foolsong - Single</v>
+        <v>Dangerous Lover - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>3:18</v>
+        <v>3:24</v>
       </c>
       <c r="H38" t="str">
-        <v>aron!</v>
+        <v>Sekou</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/sekou/1685844750</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/foolsong/1886215974</v>
+        <v>https://music.apple.com/us/album/dangerous-lover/1884781284</v>
       </c>
       <c r="L38" t="str">
-        <v>Foolsong - aron!</v>
+        <v>Dangerous Lover - Sekou</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>I Don't Wanna Be</v>
+        <v>Foolsong</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/i-dont-wanna-be/1888501665</v>
+        <v>https://music.apple.com/us/song/foolsong/1886215975</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-08</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>I Don't Wanna Be - Single</v>
+        <v>Foolsong - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:16</v>
+        <v>3:18</v>
       </c>
       <c r="H39" t="str">
-        <v>Blake Rose</v>
+        <v>aron!</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/blake-rose/1167991720</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/i-dont-wanna-be/1888501664</v>
+        <v>https://music.apple.com/us/album/foolsong/1886215974</v>
       </c>
       <c r="L39" t="str">
-        <v>I Don't Wanna Be - Blake Rose</v>
+        <v>Foolsong - aron!</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lonesome Dove</v>
+        <v>I Don't Wanna Be</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/lonesome-dove/1874700246</v>
+        <v>https://music.apple.com/us/song/i-dont-wanna-be/1888501665</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-08</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Age of the Ram</v>
+        <v>I Don't Wanna Be - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:04</v>
+        <v>3:16</v>
       </c>
       <c r="H40" t="str">
-        <v>Charley Crockett</v>
+        <v>Blake Rose</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/blake-rose/1167991720</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/lonesome-dove/1874700242</v>
+        <v>https://music.apple.com/us/album/i-dont-wanna-be/1888501664</v>
       </c>
       <c r="L40" t="str">
-        <v>Lonesome Dove - Charley Crockett</v>
+        <v>I Don't Wanna Be - Blake Rose</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Cowgirl's Prayer</v>
+        <v>Lonesome Dove</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/cowgirls-prayer/1884167296</v>
+        <v>https://music.apple.com/us/song/lonesome-dove/1874700246</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-08</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Cowgirl's Prayer - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G41" t="str">
-        <v>3:49</v>
+        <v>3:04</v>
       </c>
       <c r="H41" t="str">
-        <v>Danielle Bradbery</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/danielle-bradbery/624068729</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/cowgirls-prayer/1884167295</v>
+        <v>https://music.apple.com/us/album/lonesome-dove/1874700242</v>
       </c>
       <c r="L41" t="str">
-        <v>Cowgirl's Prayer - Danielle Bradbery</v>
+        <v>Lonesome Dove - Charley Crockett</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Hall of Fame</v>
+        <v>Cowgirl's Prayer</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/hall-of-fame/1886576289</v>
+        <v>https://music.apple.com/us/song/cowgirls-prayer/1884167296</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-08</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Hall of Fame - Single</v>
+        <v>Cowgirl's Prayer - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:11</v>
+        <v>3:49</v>
       </c>
       <c r="H42" t="str">
-        <v>Chxrry</v>
+        <v>Danielle Bradbery</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/danielle-bradbery/624068729</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/hall-of-fame/1886576288</v>
+        <v>https://music.apple.com/us/album/cowgirls-prayer/1884167295</v>
       </c>
       <c r="L42" t="str">
-        <v>Hall of Fame - Chxrry</v>
+        <v>Cowgirl's Prayer - Danielle Bradbery</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>American Wedding</v>
+        <v>Hall of Fame</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/american-wedding/1885995636</v>
+        <v>https://music.apple.com/us/song/hall-of-fame/1886576289</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-08</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>American Wedding - Single</v>
+        <v>Hall of Fame - Single</v>
       </c>
       <c r="G43" t="str">
         <v>3:11</v>
       </c>
       <c r="H43" t="str">
-        <v>flowerovlove</v>
+        <v>Chxrry</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/american-wedding/1885995635</v>
+        <v>https://music.apple.com/us/album/hall-of-fame/1886576288</v>
       </c>
       <c r="L43" t="str">
-        <v>American Wedding - flowerovlove</v>
+        <v>Hall of Fame - Chxrry</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Fashion</v>
+        <v>American Wedding</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/fashion/1887487303</v>
+        <v>https://music.apple.com/us/song/american-wedding/1885995636</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-08</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Fashion - Single</v>
+        <v>American Wedding - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>2:08</v>
+        <v>3:11</v>
       </c>
       <c r="H44" t="str">
-        <v>IVE</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/fashion/1887487297</v>
+        <v>https://music.apple.com/us/album/american-wedding/1885995635</v>
       </c>
       <c r="L44" t="str">
-        <v>Fashion - IVE</v>
+        <v>American Wedding - flowerovlove</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>heal</v>
+        <v>Fashion</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/heal/1880216061</v>
+        <v>https://music.apple.com/us/song/fashion/1887487303</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-08</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Unfold</v>
+        <v>Fashion - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:59</v>
+        <v>2:08</v>
       </c>
       <c r="H45" t="str">
-        <v>MONSTA X</v>
+        <v>IVE</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/monsta-x/992315362</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/heal/1880216060</v>
+        <v>https://music.apple.com/us/album/fashion/1887487297</v>
       </c>
       <c r="L45" t="str">
-        <v>heal - MONSTA X</v>
+        <v>Fashion - IVE</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Beautiful</v>
+        <v>heal</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1887979307</v>
+        <v>https://music.apple.com/us/song/heal/1880216061</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-08</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Beautiful - Single</v>
+        <v>Unfold</v>
       </c>
       <c r="G46" t="str">
-        <v>3:35</v>
+        <v>3:59</v>
       </c>
       <c r="H46" t="str">
-        <v>Anyma</v>
+        <v>MONSTA X</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
+        <v>https://music.apple.com/us/artist/monsta-x/992315362</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1887979305</v>
+        <v>https://music.apple.com/us/album/heal/1880216060</v>
       </c>
       <c r="L46" t="str">
-        <v>Beautiful - Anyma</v>
+        <v>heal - MONSTA X</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Wildfire</v>
+        <v>Beautiful</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/wildfire/1887444526</v>
+        <v>https://music.apple.com/us/song/beautiful/1887979307</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-08</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>For All The Right Reasons Vol. 1</v>
+        <v>Beautiful - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:11</v>
+        <v>3:35</v>
       </c>
       <c r="H47" t="str">
-        <v>Lekan</v>
+        <v>Anyma</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/wildfire/1887444297</v>
+        <v>https://music.apple.com/us/album/beautiful/1887979305</v>
       </c>
       <c r="L47" t="str">
-        <v>Wildfire - Lekan</v>
+        <v>Beautiful - Anyma</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Sliced by a Fingernail</v>
+        <v>Wildfire</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/sliced-by-a-fingernail/1879769225</v>
+        <v>https://music.apple.com/us/song/wildfire/1887444526</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-08</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Sliced by a Fingernail - Single</v>
+        <v>For All The Right Reasons, Vol. 1</v>
       </c>
       <c r="G48" t="str">
-        <v>4:08</v>
+        <v>3:11</v>
       </c>
       <c r="H48" t="str">
-        <v>Dry Cleaning</v>
+        <v>Lekan</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/dry-cleaning/1469164908</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/sliced-by-a-fingernail/1879769223</v>
+        <v>https://music.apple.com/us/album/wildfire/1887444297</v>
       </c>
       <c r="L48" t="str">
-        <v>Sliced by a Fingernail - Dry Cleaning</v>
+        <v>Wildfire - Lekan</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>FENIAN (feat. Casiokids)</v>
+        <v>Sliced by a Fingernail</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/fenian-feat-casiokids/1881565596</v>
+        <v>https://music.apple.com/us/song/sliced-by-a-fingernail/1879769225</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-08</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>FENIAN - Single</v>
+        <v>Sliced by a Fingernail - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:14</v>
+        <v>4:08</v>
       </c>
       <c r="H49" t="str">
-        <v>Kneecap</v>
+        <v>Dry Cleaning</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/dry-cleaning/1469164908</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/fenian-feat-casiokids/1881565579</v>
+        <v>https://music.apple.com/us/album/sliced-by-a-fingernail/1879769223</v>
       </c>
       <c r="L49" t="str">
-        <v>FENIAN (feat. Casiokids) - Kneecap</v>
+        <v>Sliced by a Fingernail - Dry Cleaning</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Sólo Tú</v>
+        <v>FENIAN (feat. Casiokids)</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/s%C3%B3lo-t%C3%BA/1887417656</v>
+        <v>https://music.apple.com/us/song/fenian-feat-casiokids/1881565596</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-08</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Sólo Tú - Single</v>
+        <v>FENIAN - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>2:37</v>
+        <v>3:14</v>
       </c>
       <c r="H50" t="str">
-        <v>Los Primos Del Este</v>
+        <v>Kneecap</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/los-primos-del-este/1462043487</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/s%C3%B3lo-t%C3%BA/1887417649</v>
+        <v>https://music.apple.com/us/album/fenian-feat-casiokids/1881565579</v>
       </c>
       <c r="L50" t="str">
-        <v>Sólo Tú - Los Primos Del Este</v>
+        <v>FENIAN (feat. Casiokids) - Kneecap</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Jesus I Know Now</v>
+        <v>Sólo Tú</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-i-know-now/1887978274</v>
+        <v>https://music.apple.com/us/song/s%C3%B3lo-t%C3%BA/1887417656</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-08</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>The Jesus I Know Now - Single</v>
+        <v>Sólo Tú - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>3:33</v>
+        <v>2:37</v>
       </c>
       <c r="H51" t="str">
-        <v>Brandon Lake</v>
+        <v>Los Primos Del Este</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
+        <v>https://music.apple.com/us/artist/los-primos-del-este/1462043487</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-i-know-now/1887978263</v>
+        <v>https://music.apple.com/us/album/s%C3%B3lo-t%C3%BA/1887417649</v>
       </c>
       <c r="L51" t="str">
-        <v>The Jesus I Know Now - Brandon Lake</v>
+        <v>Sólo Tú - Los Primos Del Este</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Turnstile</v>
+        <v>The Jesus I Know Now</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/turnstile/1867616937</v>
+        <v>https://music.apple.com/us/song/the-jesus-i-know-now/1887978274</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-08</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>The Weight of the Woods</v>
+        <v>The Jesus I Know Now - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:50</v>
+        <v>3:33</v>
       </c>
       <c r="H52" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/turnstile/1867616617</v>
+        <v>https://music.apple.com/us/album/the-jesus-i-know-now/1887978263</v>
       </c>
       <c r="L52" t="str">
-        <v>Turnstile - Dermot Kennedy</v>
+        <v>The Jesus I Know Now - Brandon Lake</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Surrender (From Your Friends &amp; Neighbors)</v>
+        <v>Turnstile</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/surrender-from-your-friends-neighbors/1887371368</v>
+        <v>https://music.apple.com/us/song/turnstile/1867616937</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-08</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Surrender (From Your Friends &amp; Neighbors) - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G53" t="str">
-        <v>3:04</v>
+        <v>3:50</v>
       </c>
       <c r="H53" t="str">
-        <v>Lindsey Stirling</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/lindsey-stirling/403025113</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/surrender-from-your-friends-neighbors/1887371353</v>
+        <v>https://music.apple.com/us/album/turnstile/1867616617</v>
       </c>
       <c r="L53" t="str">
-        <v>Surrender (From Your Friends &amp; Neighbors) - Lindsey Stirling</v>
+        <v>Turnstile - Dermot Kennedy</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Before This Even Starts</v>
+        <v>Surrender (From Your Friends &amp; Neighbors)</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/before-this-even-starts/1883698214</v>
+        <v>https://music.apple.com/us/song/surrender-from-your-friends-neighbors/1887371368</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-08</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Therapy &amp; Yoga - EP</v>
+        <v>Surrender (From Your Friends &amp; Neighbors) - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>2:44</v>
+        <v>3:04</v>
       </c>
       <c r="H54" t="str">
-        <v>JESSIA</v>
+        <v>Lindsey Stirling</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/jessia/1399415802</v>
+        <v>https://music.apple.com/us/artist/lindsey-stirling/403025113</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/before-this-even-starts/1883698028</v>
+        <v>https://music.apple.com/us/album/surrender-from-your-friends-neighbors/1887371353</v>
       </c>
       <c r="L54" t="str">
-        <v>Before This Even Starts - JESSIA</v>
+        <v>Surrender (From Your Friends &amp; Neighbors) - Lindsey Stirling</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Roses</v>
+        <v>Before This Even Starts</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/roses/1883777517</v>
+        <v>https://music.apple.com/us/song/before-this-even-starts/1883698214</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-08</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Middle School Dropout - EP</v>
+        <v>Therapy &amp; Yoga - EP</v>
       </c>
       <c r="G55" t="str">
-        <v>3:10</v>
+        <v>2:44</v>
       </c>
       <c r="H55" t="str">
-        <v>Iris Copperman</v>
+        <v>JESSIA</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/jessia/1399415802</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/roses/1883777352</v>
+        <v>https://music.apple.com/us/album/before-this-even-starts/1883698028</v>
       </c>
       <c r="L55" t="str">
-        <v>Roses - Iris Copperman</v>
+        <v>Before This Even Starts - JESSIA</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Does Your Father Know You Dance Like That?</v>
+        <v>Roses</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/does-your-father-know-you-dance-like-that/1886621446</v>
+        <v>https://music.apple.com/us/song/roses/1883777517</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-08</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Does Your Father Know You Dance Like That? - Single</v>
+        <v>Middle School Dropout - EP</v>
       </c>
       <c r="G56" t="str">
-        <v>2:28</v>
+        <v>3:10</v>
       </c>
       <c r="H56" t="str">
-        <v>Steve Aoki</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/does-your-father-know-you-dance-like-that/1886621445</v>
+        <v>https://music.apple.com/us/album/roses/1883777352</v>
       </c>
       <c r="L56" t="str">
-        <v>Does Your Father Know You Dance Like That? - Steve Aoki</v>
+        <v>Roses - Iris Copperman</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Loco</v>
+        <v>Does Your Father Know You Dance Like That?</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/loco/1888397210</v>
+        <v>https://music.apple.com/us/song/does-your-father-know-you-dance-like-that/1886621446</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-08</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Loco - Single</v>
+        <v>Does Your Father Know You Dance Like That? - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:34</v>
+        <v>2:28</v>
       </c>
       <c r="H57" t="str">
-        <v>Key Glock</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/key-glock/1199258326</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/loco/1888397209</v>
+        <v>https://music.apple.com/us/album/does-your-father-know-you-dance-like-that/1886621445</v>
       </c>
       <c r="L57" t="str">
-        <v>Loco - Key Glock</v>
+        <v>Does Your Father Know You Dance Like That? - Steve Aoki</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Hold It For Her</v>
+        <v>Loco</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/hold-it-for-her/1861380253</v>
+        <v>https://music.apple.com/us/song/loco/1888397210</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-08</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Porcelain</v>
+        <v>Loco - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="H58" t="str">
-        <v>Peach PRC</v>
+        <v>Key Glock</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/key-glock/1199258326</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/hold-it-for-her/1861380240</v>
+        <v>https://music.apple.com/us/album/loco/1888397209</v>
       </c>
       <c r="L58" t="str">
-        <v>Hold It For Her - Peach PRC</v>
+        <v>Loco - Key Glock</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Ghost town...</v>
+        <v>Hold It For Her</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/ghost-town/1870971561</v>
+        <v>https://music.apple.com/us/song/hold-it-for-her/1861380253</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-08</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Porcelain</v>
       </c>
       <c r="G59" t="str">
-        <v>2:44</v>
+        <v>3:48</v>
       </c>
       <c r="H59" t="str">
-        <v>R3HAB</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/ghost-town/1870971550</v>
+        <v>https://music.apple.com/us/album/hold-it-for-her/1861380240</v>
       </c>
       <c r="L59" t="str">
-        <v>Ghost town... - R3HAB</v>
+        <v>Hold It For Her - Peach PRC</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>WASTE SOME TIME</v>
+        <v>Ghost town...</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/waste-some-time/1887768620</v>
+        <v>https://music.apple.com/us/song/ghost-town/1870971561</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-08</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>DAWN PATROL</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G60" t="str">
-        <v>3:26</v>
+        <v>2:44</v>
       </c>
       <c r="H60" t="str">
-        <v>Forrest Frank</v>
+        <v>R3HAB</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/waste-some-time/1887768606</v>
+        <v>https://music.apple.com/us/album/ghost-town/1870971550</v>
       </c>
       <c r="L60" t="str">
-        <v>WASTE SOME TIME - Forrest Frank</v>
+        <v>Ghost town... - R3HAB</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>control.</v>
+        <v>WASTE SOME TIME</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/control/1887392580</v>
+        <v>https://music.apple.com/us/song/waste-some-time/1887768620</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-08</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>control. - Single</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G61" t="str">
-        <v>2:50</v>
+        <v>3:26</v>
       </c>
       <c r="H61" t="str">
-        <v>Paco</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/paco/1513830139</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/control/1887392578</v>
+        <v>https://music.apple.com/us/album/waste-some-time/1887768606</v>
       </c>
       <c r="L61" t="str">
-        <v>control. - Paco</v>
+        <v>WASTE SOME TIME - Forrest Frank</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Wouldn't Try Again</v>
+        <v>control.</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/wouldnt-try-again/1889328836</v>
+        <v>https://music.apple.com/us/song/control/1887392580</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-08</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Wouldn't Try Again - Single</v>
+        <v>control. - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>2:45</v>
+        <v>2:50</v>
       </c>
       <c r="H62" t="str">
-        <v>Quail P</v>
+        <v>Paco</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/quail-p/1447409001</v>
+        <v>https://music.apple.com/us/artist/paco/1513830139</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/wouldnt-try-again/1889328830</v>
+        <v>https://music.apple.com/us/album/control/1887392578</v>
       </c>
       <c r="L62" t="str">
-        <v>Wouldn't Try Again - Quail P</v>
+        <v>control. - Paco</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>i need u</v>
+        <v>Wouldn't Try Again</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/i-need-u/1889349101</v>
+        <v>https://music.apple.com/us/song/wouldnt-try-again/1889328836</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-08</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>i need u - Single</v>
+        <v>Wouldn't Try Again - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:45</v>
+        <v>2:45</v>
       </c>
       <c r="H63" t="str">
-        <v>BUNT.</v>
+        <v>Quail P</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/quail-p/1447409001</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/i-need-u/1889349100</v>
+        <v>https://music.apple.com/us/album/wouldnt-try-again/1889328830</v>
       </c>
       <c r="L63" t="str">
-        <v>i need u - BUNT.</v>
+        <v>Wouldn't Try Again - Quail P</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Outlaw</v>
+        <v>i need u</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/outlaw/1877229747</v>
+        <v>https://music.apple.com/us/song/i-need-u/1889349101</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-08</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>EI8HT</v>
+        <v>i need u - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:35</v>
+        <v>3:45</v>
       </c>
       <c r="H64" t="str">
-        <v>Shinedown</v>
+        <v>BUNT.</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/outlaw/1877229738</v>
+        <v>https://music.apple.com/us/album/i-need-u/1889349100</v>
       </c>
       <c r="L64" t="str">
-        <v>Outlaw - Shinedown</v>
+        <v>i need u - BUNT.</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>A.L.O.N.E.</v>
+        <v>Outlaw</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/a-l-o-n-e/1886537119</v>
+        <v>https://music.apple.com/us/song/outlaw/1877229747</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-08</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>ADDENDUM</v>
+        <v>EI8HT</v>
       </c>
       <c r="G65" t="str">
-        <v>3:24</v>
+        <v>3:35</v>
       </c>
       <c r="H65" t="str">
-        <v>HEALTH</v>
+        <v>Shinedown</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/health/317478211</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/a-l-o-n-e/1886536873</v>
+        <v>https://music.apple.com/us/album/outlaw/1877229738</v>
       </c>
       <c r="L65" t="str">
-        <v>A.L.O.N.E. - HEALTH</v>
+        <v>Outlaw - Shinedown</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Him</v>
+        <v>A.L.O.N.E.</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/him/1887319676</v>
+        <v>https://music.apple.com/us/song/a-l-o-n-e/1886537119</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-08</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Him - Single</v>
+        <v>ADDENDUM</v>
       </c>
       <c r="G66" t="str">
-        <v>2:07</v>
+        <v>3:24</v>
       </c>
       <c r="H66" t="str">
-        <v>Sheff G</v>
+        <v>HEALTH</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/health/317478211</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/him/1887319675</v>
+        <v>https://music.apple.com/us/album/a-l-o-n-e/1886536873</v>
       </c>
       <c r="L66" t="str">
-        <v>Him - Sheff G</v>
+        <v>A.L.O.N.E. - HEALTH</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>MVP (feat. Key Glock)</v>
+        <v>Him</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/mvp-feat-key-glock/1888298376</v>
+        <v>https://music.apple.com/us/song/him/1887319676</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-08</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>AREA 41</v>
+        <v>Him - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:08</v>
+        <v>2:07</v>
       </c>
       <c r="H67" t="str">
-        <v>41</v>
+        <v>Sheff G</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/mvp-feat-key-glock/1888298368</v>
+        <v>https://music.apple.com/us/album/him/1887319675</v>
       </c>
       <c r="L67" t="str">
-        <v>MVP (feat. Key Glock) - 41</v>
+        <v>Him - Sheff G</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>S.I.M.P.L.E</v>
+        <v>MVP (feat. Key Glock)</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/s-i-m-p-l-e/1885386665</v>
+        <v>https://music.apple.com/us/song/mvp-feat-key-glock/1888298376</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-08</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>DND</v>
+        <v>AREA 41</v>
       </c>
       <c r="G68" t="str">
-        <v>2:33</v>
+        <v>3:08</v>
       </c>
       <c r="H68" t="str">
-        <v>TheARTI$t</v>
+        <v>41</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/s-i-m-p-l-e/1885386569</v>
+        <v>https://music.apple.com/us/album/mvp-feat-key-glock/1888298368</v>
       </c>
       <c r="L68" t="str">
-        <v>S.I.M.P.L.E - TheARTI$t</v>
+        <v>MVP (feat. Key Glock) - 41</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>S.I.M.P.L.E</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/at-least-shes-beautiful/1884405874</v>
+        <v>https://music.apple.com/us/song/s-i-m-p-l-e/1885386665</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-08</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>At Least She's Beautiful - Single</v>
+        <v>DND</v>
       </c>
       <c r="G69" t="str">
-        <v>2:36</v>
+        <v>2:33</v>
       </c>
       <c r="H69" t="str">
-        <v>rjtheweirdo</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/at-least-shes-beautiful/1884405873</v>
+        <v>https://music.apple.com/us/album/s-i-m-p-l-e/1885386569</v>
       </c>
       <c r="L69" t="str">
-        <v>At Least She's Beautiful - rjtheweirdo</v>
+        <v>S.I.M.P.L.E - TheARTI$t</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Hella Good (feat. Bonnie McKee)</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/hella-good-feat-bonnie-mckee/1886001675</v>
+        <v>https://music.apple.com/us/song/at-least-shes-beautiful/1884405874</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-08</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Hella Good (feat. Bonnie McKee) - Single</v>
+        <v>At Least She's Beautiful - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:45</v>
+        <v>2:36</v>
       </c>
       <c r="H70" t="str">
-        <v>Trixie Mattel</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/trixie-mattel/960467089</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/hella-good-feat-bonnie-mckee/1886001667</v>
+        <v>https://music.apple.com/us/album/at-least-shes-beautiful/1884405873</v>
       </c>
       <c r="L70" t="str">
-        <v>Hella Good (feat. Bonnie McKee) - Trixie Mattel</v>
+        <v>At Least She's Beautiful - rjtheweirdo</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Show</v>
+        <v>Hella Good (feat. Bonnie McKee)</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/the-show/1889121528</v>
+        <v>https://music.apple.com/us/song/hella-good-feat-bonnie-mckee/1886001675</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-08</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>The Show - Single</v>
+        <v>Hella Good (feat. Bonnie McKee) - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:47</v>
+        <v>3:45</v>
       </c>
       <c r="H71" t="str">
-        <v>DPR IAN</v>
+        <v>Trixie Mattel</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/dpr-ian/1500739803</v>
+        <v>https://music.apple.com/us/artist/trixie-mattel/960467089</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/the-show/1889121369</v>
+        <v>https://music.apple.com/us/album/hella-good-feat-bonnie-mckee/1886001667</v>
       </c>
       <c r="L71" t="str">
-        <v>The Show - DPR IAN</v>
+        <v>Hella Good (feat. Bonnie McKee) - Trixie Mattel</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>His Eye Is On the Sparrow</v>
+        <v>The Show</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/his-eye-is-on-the-sparrow/1880392628</v>
+        <v>https://music.apple.com/us/song/the-show/1889121528</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-08</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Grandma's Gospel Favorites</v>
+        <v>The Show - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:20</v>
+        <v>2:47</v>
       </c>
       <c r="H72" t="str">
-        <v>Jason Mraz</v>
+        <v>DPR IAN</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/jason-mraz/156987</v>
+        <v>https://music.apple.com/us/artist/dpr-ian/1500739803</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/his-eye-is-on-the-sparrow/1880392609</v>
+        <v>https://music.apple.com/us/album/the-show/1889121369</v>
       </c>
       <c r="L72" t="str">
-        <v>His Eye Is On the Sparrow - Jason Mraz</v>
+        <v>The Show - DPR IAN</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Slowly</v>
+        <v>His Eye Is On the Sparrow</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/slowly/1869140941</v>
+        <v>https://music.apple.com/us/song/his-eye-is-on-the-sparrow/1880392628</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-08</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Change Of Plans</v>
+        <v>Grandma's Gospel Favorites</v>
       </c>
       <c r="G73" t="str">
-        <v>3:11</v>
+        <v>3:20</v>
       </c>
       <c r="H73" t="str">
-        <v>49 Winchester</v>
+        <v>Jason Mraz</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
+        <v>https://music.apple.com/us/artist/jason-mraz/156987</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/slowly/1869140544</v>
+        <v>https://music.apple.com/us/album/his-eye-is-on-the-sparrow/1880392609</v>
       </c>
       <c r="L73" t="str">
-        <v>Slowly - 49 Winchester</v>
+        <v>His Eye Is On the Sparrow - Jason Mraz</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>On Our Way Along</v>
+        <v>Slowly</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/on-our-way-along/1863814124</v>
+        <v>https://music.apple.com/us/song/slowly/1869140941</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-08</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>On Our Way Along - Single</v>
+        <v>Change Of Plans</v>
       </c>
       <c r="G74" t="str">
-        <v>4:21</v>
+        <v>3:11</v>
       </c>
       <c r="H74" t="str">
-        <v>Billy Ray Cyrus</v>
+        <v>49 Winchester</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/billy-ray-cyrus/1793659079</v>
+        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/on-our-way-along/1863813853</v>
+        <v>https://music.apple.com/us/album/slowly/1869140544</v>
       </c>
       <c r="L74" t="str">
-        <v>On Our Way Along - Billy Ray Cyrus</v>
+        <v>Slowly - 49 Winchester</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>COMING OF AGE</v>
+        <v>On Our Way Along</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/coming-of-age/1882886175</v>
+        <v>https://music.apple.com/us/song/on-our-way-along/1863814124</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-08</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>COMING OF AGE - Single</v>
+        <v>On Our Way Along - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>4:08</v>
+        <v>4:21</v>
       </c>
       <c r="H75" t="str">
-        <v>METTE</v>
+        <v>Billy Ray Cyrus</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/mette/1553768125</v>
+        <v>https://music.apple.com/us/artist/billy-ray-cyrus/1793659079</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/coming-of-age/1882886174</v>
+        <v>https://music.apple.com/us/album/on-our-way-along/1863813853</v>
       </c>
       <c r="L75" t="str">
-        <v>COMING OF AGE - METTE</v>
+        <v>On Our Way Along - Billy Ray Cyrus</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>the man with money in his hands</v>
+        <v>COMING OF AGE</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/the-man-with-money-in-his-hands/1887707057</v>
+        <v>https://music.apple.com/us/song/coming-of-age/1882886175</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-08</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>the man with money in his hands - Single</v>
+        <v>COMING OF AGE - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:57</v>
+        <v>4:08</v>
       </c>
       <c r="H76" t="str">
-        <v>Jessie Mazin</v>
+        <v>METTE</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
+        <v>https://music.apple.com/us/artist/mette/1553768125</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/the-man-with-money-in-his-hands/1887707053</v>
+        <v>https://music.apple.com/us/album/coming-of-age/1882886174</v>
       </c>
       <c r="L76" t="str">
-        <v>the man with money in his hands - Jessie Mazin</v>
+        <v>COMING OF AGE - METTE</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WRANGLER</v>
+        <v>the man with money in his hands</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/wrangler/1876267962</v>
+        <v>https://music.apple.com/us/song/the-man-with-money-in-his-hands/1887707057</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-08</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>WHAT CAN I TELL U</v>
+        <v>the man with money in his hands - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:05</v>
+        <v>2:57</v>
       </c>
       <c r="H77" t="str">
-        <v>Claudia Valentina</v>
+        <v>Jessie Mazin</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/wrangler/1876267654</v>
+        <v>https://music.apple.com/us/album/the-man-with-money-in-his-hands/1887707053</v>
       </c>
       <c r="L77" t="str">
-        <v>WRANGLER - Claudia Valentina</v>
+        <v>the man with money in his hands - Jessie Mazin</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Rydly</v>
+        <v>WRANGLER</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/rydly/1878477155</v>
+        <v>https://music.apple.com/us/song/wrangler/1876267962</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-08</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>We Are Friends, Vol. 12 (Disk 2)</v>
+        <v>WHAT CAN I TELL U</v>
       </c>
       <c r="G78" t="str">
-        <v>6:52</v>
+        <v>2:05</v>
       </c>
       <c r="H78" t="str">
-        <v>deadmau5</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/rydly/1878476797</v>
+        <v>https://music.apple.com/us/album/wrangler/1876267654</v>
       </c>
       <c r="L78" t="str">
-        <v>Rydly - deadmau5</v>
+        <v>WRANGLER - Claudia Valentina</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>all the time</v>
+        <v>Rydly</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1874100418</v>
+        <v>https://music.apple.com/us/song/rydly/1878477155</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-08</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>ARCADE</v>
+        <v>We Are Friends, Vol. 12 (Disk 2)</v>
       </c>
       <c r="G79" t="str">
-        <v>3:01</v>
+        <v>6:52</v>
       </c>
       <c r="H79" t="str">
-        <v>Deb Never</v>
+        <v>deadmau5</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1874100412</v>
+        <v>https://music.apple.com/us/album/rydly/1878476797</v>
       </c>
       <c r="L79" t="str">
-        <v>all the time - Deb Never</v>
+        <v>Rydly - deadmau5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Misery</v>
+        <v>all the time</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/misery/1888294484</v>
+        <v>https://music.apple.com/us/song/all-the-time/1874100418</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-08</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Misery - Single</v>
+        <v>ARCADE</v>
       </c>
       <c r="G80" t="str">
-        <v>2:55</v>
+        <v>3:01</v>
       </c>
       <c r="H80" t="str">
-        <v>Alex Sampson</v>
+        <v>Deb Never</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/alex-sampson/1486112083</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/misery/1888294483</v>
+        <v>https://music.apple.com/us/album/all-the-time/1874100412</v>
       </c>
       <c r="L80" t="str">
-        <v>Misery - Alex Sampson</v>
+        <v>all the time - Deb Never</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Don't Fall</v>
+        <v>Misery</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/dont-fall/1884794995</v>
+        <v>https://music.apple.com/us/song/misery/1888294484</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-08</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Games - EP</v>
+        <v>Misery - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>4:20</v>
+        <v>2:55</v>
       </c>
       <c r="H81" t="str">
-        <v>Common People</v>
+        <v>Alex Sampson</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/alex-sampson/1486112083</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/dont-fall/1884794990</v>
+        <v>https://music.apple.com/us/album/misery/1888294483</v>
       </c>
       <c r="L81" t="str">
-        <v>Don't Fall - Common People</v>
+        <v>Misery - Alex Sampson</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Alternate Ending</v>
+        <v>Don't Fall</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/alternate-ending/1886010374</v>
+        <v>https://music.apple.com/us/song/dont-fall/1884794995</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-08</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Alternate Ending - Single</v>
+        <v>Games - EP</v>
       </c>
       <c r="G82" t="str">
-        <v>3:10</v>
+        <v>4:20</v>
       </c>
       <c r="H82" t="str">
-        <v>Thelma &amp; James</v>
+        <v>Common People</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/thelma-james/1787091600</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/alternate-ending/1886010053</v>
+        <v>https://music.apple.com/us/album/dont-fall/1884794990</v>
       </c>
       <c r="L82" t="str">
-        <v>Alternate Ending - Thelma &amp; James</v>
+        <v>Don't Fall - Common People</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>LuCkY</v>
+        <v>Alternate Ending</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/lucky/1888001208</v>
+        <v>https://music.apple.com/us/song/alternate-ending/1886010374</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-08</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>MOEWYA</v>
+        <v>Alternate Ending - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>2:17</v>
+        <v>3:10</v>
       </c>
       <c r="H83" t="str">
-        <v>MoeIsBetter</v>
+        <v>Thelma &amp; James</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/moeisbetter/1762833637</v>
+        <v>https://music.apple.com/us/artist/thelma-james/1787091600</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/lucky/1888001204</v>
+        <v>https://music.apple.com/us/album/alternate-ending/1886010053</v>
       </c>
       <c r="L83" t="str">
-        <v>LuCkY - MoeIsBetter</v>
+        <v>Alternate Ending - Thelma &amp; James</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Mutual</v>
+        <v>LuCkY</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/mutual/1882922798</v>
+        <v>https://music.apple.com/us/song/lucky/1888001208</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-08</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Mutual - Single</v>
+        <v>MOEWYA</v>
       </c>
       <c r="G84" t="str">
-        <v>3:49</v>
+        <v>2:17</v>
       </c>
       <c r="H84" t="str">
-        <v>PJ Morton</v>
+        <v>MoeIsBetter</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/pj-morton/44719201</v>
+        <v>https://music.apple.com/us/artist/moeisbetter/1762833637</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/mutual/1882922794</v>
+        <v>https://music.apple.com/us/album/lucky/1888001204</v>
       </c>
       <c r="L84" t="str">
-        <v>Mutual - PJ Morton</v>
+        <v>LuCkY - MoeIsBetter</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Waiting On</v>
+        <v>Mutual</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/waiting-on/1883846539</v>
+        <v>https://music.apple.com/us/song/mutual/1882922798</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-08</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Waiting On - Single</v>
+        <v>Mutual - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:11</v>
+        <v>3:49</v>
       </c>
       <c r="H85" t="str">
-        <v>Tniyah</v>
+        <v>PJ Morton</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/tniyah/513967453</v>
+        <v>https://music.apple.com/us/artist/pj-morton/44719201</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/waiting-on/1883846538</v>
+        <v>https://music.apple.com/us/album/mutual/1882922794</v>
       </c>
       <c r="L85" t="str">
-        <v>Waiting On - Tniyah</v>
+        <v>Mutual - PJ Morton</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>En La Montaña</v>
+        <v>Waiting On</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/en-la-monta%C3%B1a/1884092212</v>
+        <v>https://music.apple.com/us/song/waiting-on/1883846539</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-08</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>En La Montaña - Single</v>
+        <v>Waiting On - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>2:23</v>
+        <v>3:11</v>
       </c>
       <c r="H86" t="str">
-        <v>Nueva H</v>
+        <v>Tniyah</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/tniyah/513967453</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/en-la-monta%C3%B1a/1884092207</v>
+        <v>https://music.apple.com/us/album/waiting-on/1883846538</v>
       </c>
       <c r="L86" t="str">
-        <v>En La Montaña - Nueva H</v>
+        <v>Waiting On - Tniyah</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Falling Short</v>
+        <v>En La Montaña</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/falling-short/1884803703</v>
+        <v>https://music.apple.com/us/song/en-la-monta%C3%B1a/1884092212</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-08</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Falling Short - Single</v>
+        <v>En La Montaña - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:05</v>
+        <v>2:23</v>
       </c>
       <c r="H87" t="str">
-        <v>Hudson Macready</v>
+        <v>Nueva H</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/hudson-macready/1534530042</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/falling-short/1884803515</v>
+        <v>https://music.apple.com/us/album/en-la-monta%C3%B1a/1884092207</v>
       </c>
       <c r="L87" t="str">
-        <v>Falling Short - Hudson Macready</v>
+        <v>En La Montaña - Nueva H</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>When You Give It Up</v>
+        <v>Falling Short</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/when-you-give-it-up/1879883866</v>
+        <v>https://music.apple.com/us/song/falling-short/1884803703</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-08</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>When You Give It Up - Single</v>
+        <v>Falling Short - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>2:42</v>
+        <v>3:05</v>
       </c>
       <c r="H88" t="str">
-        <v>Chelsea Plank</v>
+        <v>Hudson Macready</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
+        <v>https://music.apple.com/us/artist/hudson-macready/1534530042</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/when-you-give-it-up/1879883863</v>
+        <v>https://music.apple.com/us/album/falling-short/1884803515</v>
       </c>
       <c r="L88" t="str">
-        <v>When You Give It Up - Chelsea Plank</v>
+        <v>Falling Short - Hudson Macready</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Wasted</v>
+        <v>When You Give It Up</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/wasted/1885578001</v>
+        <v>https://music.apple.com/us/song/when-you-give-it-up/1879883866</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-08</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Wasted - Single</v>
+        <v>When You Give It Up - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:18</v>
+        <v>2:42</v>
       </c>
       <c r="H89" t="str">
-        <v>Highly Suspect</v>
+        <v>Chelsea Plank</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/highly-suspect/419913603</v>
+        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/wasted/1885578000</v>
+        <v>https://music.apple.com/us/album/when-you-give-it-up/1879883863</v>
       </c>
       <c r="L89" t="str">
-        <v>Wasted - Highly Suspect</v>
+        <v>When You Give It Up - Chelsea Plank</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Burn</v>
+        <v>Wasted</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/burn/1883195616</v>
+        <v>https://music.apple.com/us/song/wasted/1885578001</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-08</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Burn - Single</v>
+        <v>Wasted - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>2:56</v>
+        <v>3:18</v>
       </c>
       <c r="H90" t="str">
-        <v>Cold Court</v>
+        <v>Highly Suspect</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/cold-court/1809708831</v>
+        <v>https://music.apple.com/us/artist/highly-suspect/419913603</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/burn/1883195615</v>
+        <v>https://music.apple.com/us/album/wasted/1885578000</v>
       </c>
       <c r="L90" t="str">
-        <v>Burn - Cold Court</v>
+        <v>Wasted - Highly Suspect</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Smash</v>
+        <v>Burn</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/smash/1884655608</v>
+        <v>https://music.apple.com/us/song/burn/1883195616</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-08</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Eternal BAM Nation</v>
+        <v>Burn - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>2:27</v>
+        <v>2:56</v>
       </c>
       <c r="H91" t="str">
-        <v>Born At Midnite</v>
+        <v>Cold Court</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/born-at-midnite/1497209280</v>
+        <v>https://music.apple.com/us/artist/cold-court/1809708831</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/smash/1884655462</v>
+        <v>https://music.apple.com/us/album/burn/1883195615</v>
       </c>
       <c r="L91" t="str">
-        <v>Smash - Born At Midnite</v>
+        <v>Burn - Cold Court</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Smile</v>
+        <v>Smash</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/smile/1859619683</v>
+        <v>https://music.apple.com/us/song/smash/1884655608</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-08</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Birding</v>
+        <v>Eternal BAM Nation</v>
       </c>
       <c r="G92" t="str">
-        <v>5:09</v>
+        <v>2:27</v>
       </c>
       <c r="H92" t="str">
-        <v>deary</v>
+        <v>Born At Midnite</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/deary/1641536096</v>
+        <v>https://music.apple.com/us/artist/born-at-midnite/1497209280</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/smile/1859619407</v>
+        <v>https://music.apple.com/us/album/smash/1884655462</v>
       </c>
       <c r="L92" t="str">
-        <v>Smile - deary</v>
+        <v>Smash - Born At Midnite</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Eshi</v>
+        <v>Smile</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/eshi/1880700566</v>
+        <v>https://music.apple.com/us/song/smile/1859619683</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-08</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Zero</v>
+        <v>Birding</v>
       </c>
       <c r="G93" t="str">
-        <v>3:12</v>
+        <v>5:09</v>
       </c>
       <c r="H93" t="str">
-        <v>Alewya</v>
+        <v>deary</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/alewya/1450971317</v>
+        <v>https://music.apple.com/us/artist/deary/1641536096</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/eshi/1880699673</v>
+        <v>https://music.apple.com/us/album/smile/1859619407</v>
       </c>
       <c r="L93" t="str">
-        <v>Eshi - Alewya</v>
+        <v>Smile - deary</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>NO HOMEGIRLS</v>
+        <v>Eshi</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/no-homegirls/1886801763</v>
+        <v>https://music.apple.com/us/song/eshi/1880700566</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-08</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>NO HOMEGIRLS - Single</v>
+        <v>Zero</v>
       </c>
       <c r="G94" t="str">
-        <v>2:05</v>
+        <v>3:12</v>
       </c>
       <c r="H94" t="str">
-        <v>BBYKOBE</v>
+        <v>Alewya</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/bbykobe/1693491560</v>
+        <v>https://music.apple.com/us/artist/alewya/1450971317</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/no-homegirls/1886801762</v>
+        <v>https://music.apple.com/us/album/eshi/1880699673</v>
       </c>
       <c r="L94" t="str">
-        <v>NO HOMEGIRLS - BBYKOBE</v>
+        <v>Eshi - Alewya</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>I Want You Back</v>
+        <v>NO HOMEGIRLS</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/i-want-you-back/1889281139</v>
+        <v>https://music.apple.com/us/song/no-homegirls/1886801763</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-08</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>I Want You Back - Single</v>
+        <v>NO HOMEGIRLS - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:18</v>
+        <v>2:05</v>
       </c>
       <c r="H95" t="str">
-        <v>Johnny Venus</v>
+        <v>BBYKOBE</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/johnny-venus/1777129720</v>
+        <v>https://music.apple.com/us/artist/bbykobe/1693491560</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/i-want-you-back/1889281136</v>
+        <v>https://music.apple.com/us/album/no-homegirls/1886801762</v>
       </c>
       <c r="L95" t="str">
-        <v>I Want You Back - Johnny Venus</v>
+        <v>NO HOMEGIRLS - BBYKOBE</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Needed You</v>
+        <v>I Want You Back</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/needed-you/1887702402</v>
+        <v>https://music.apple.com/us/song/i-want-you-back/1889281139</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-08</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Active Child</v>
+        <v>I Want You Back - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>3:17</v>
+        <v>3:18</v>
       </c>
       <c r="H96" t="str">
-        <v>Active Child</v>
+        <v>Johnny Venus</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/johnny-venus/1777129720</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/needed-you/1887701924</v>
+        <v>https://music.apple.com/us/album/i-want-you-back/1889281136</v>
       </c>
       <c r="L96" t="str">
-        <v>Needed You - Active Child</v>
+        <v>I Want You Back - Johnny Venus</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Finish Line</v>
+        <v>Needed You</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/finish-line/1887371855</v>
+        <v>https://music.apple.com/us/song/needed-you/1887702402</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-08</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Finish Line - Single</v>
+        <v>Active Child</v>
       </c>
       <c r="G97" t="str">
-        <v>3:18</v>
+        <v>3:17</v>
       </c>
       <c r="H97" t="str">
-        <v>Ally Salort</v>
+        <v>Active Child</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/finish-line/1887371854</v>
+        <v>https://music.apple.com/us/album/needed-you/1887701924</v>
       </c>
       <c r="L97" t="str">
-        <v>Finish Line - Ally Salort</v>
+        <v>Needed You - Active Child</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Daredevil</v>
+        <v>Finish Line</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/daredevil/1883231048</v>
+        <v>https://music.apple.com/us/song/finish-line/1887371855</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-08</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Daredevil - Single</v>
+        <v>Finish Line - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>4:16</v>
+        <v>3:18</v>
       </c>
       <c r="H98" t="str">
-        <v>Zach Hood</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/zach-hood/1518857330</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/daredevil/1883231047</v>
+        <v>https://music.apple.com/us/album/finish-line/1887371854</v>
       </c>
       <c r="L98" t="str">
-        <v>Daredevil - Zach Hood</v>
+        <v>Finish Line - Ally Salort</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Asleep On The Killing Floor</v>
+        <v>Daredevil</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/asleep-on-the-killing-floor/1869086163</v>
+        <v>https://music.apple.com/us/song/daredevil/1883231048</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-08</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Daredevil - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>4:08</v>
+        <v>4:16</v>
       </c>
       <c r="H99" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Zach Hood</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/zach-hood/1518857330</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/asleep-on-the-killing-floor/1869085524</v>
+        <v>https://music.apple.com/us/album/daredevil/1883231047</v>
       </c>
       <c r="L99" t="str">
-        <v>Asleep On The Killing Floor - Corrosion of Conformity</v>
+        <v>Daredevil - Zach Hood</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>You Bastard</v>
+        <v>Asleep On The Killing Floor</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/you-bastard/1871211807</v>
+        <v>https://music.apple.com/us/song/asleep-on-the-killing-floor/1869086163</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-08</v>
@@ -4175,36 +4175,36 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Neverending</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G100" t="str">
-        <v>4:19</v>
+        <v>4:08</v>
       </c>
       <c r="H100" t="str">
-        <v>Monolord</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/you-bastard/1871211801</v>
+        <v>https://music.apple.com/us/album/asleep-on-the-killing-floor/1869085524</v>
       </c>
       <c r="L100" t="str">
-        <v>You Bastard - Monolord</v>
+        <v>Asleep On The Killing Floor - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Vanilla Latte</v>
+        <v>You Bastard</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/vanilla-latte/1884524943</v>
+        <v>https://music.apple.com/us/song/you-bastard/1871211807</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-08</v>
@@ -4213,68 +4213,106 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>Vanilla Latte - EP</v>
+        <v>Neverending</v>
       </c>
       <c r="G101" t="str">
-        <v>2:24</v>
+        <v>4:19</v>
       </c>
       <c r="H101" t="str">
-        <v>The Barbarians of California</v>
+        <v>Monolord</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/vanilla-latte/1884524941</v>
+        <v>https://music.apple.com/us/album/you-bastard/1871211801</v>
       </c>
       <c r="L101" t="str">
-        <v>Vanilla Latte - The Barbarians of California</v>
+        <v>You Bastard - Monolord</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>Vanilla Latte</v>
+      </c>
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
+        <v>https://music.apple.com/us/song/vanilla-latte/1884524943</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-04-08</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v>Vanilla Latte - EP</v>
+      </c>
+      <c r="G102" t="str">
+        <v>2:24</v>
+      </c>
+      <c r="H102" t="str">
+        <v>The Barbarians of California</v>
+      </c>
+      <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
+        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
+      </c>
+      <c r="K102" t="str">
+        <v>https://music.apple.com/us/album/vanilla-latte/1884524941</v>
+      </c>
+      <c r="L102" t="str">
+        <v>Vanilla Latte - The Barbarians of California</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
         <v>Nostalgia Kills</v>
       </c>
-      <c r="B102" t="str">
-        <v/>
-      </c>
-      <c r="C102" t="str">
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
         <v>https://music.apple.com/us/song/nostalgia-kills/1887961043</v>
       </c>
-      <c r="D102" t="str">
-        <v>2026-04-08</v>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
+      <c r="D103" t="str">
+        <v>2026-04-08</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
         <v>Nostalgia Kills - Single</v>
       </c>
-      <c r="G102" t="str">
+      <c r="G103" t="str">
         <v>3:03</v>
       </c>
-      <c r="H102" t="str">
+      <c r="H103" t="str">
         <v>Static Dress</v>
       </c>
-      <c r="I102" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J102" t="str">
+      <c r="I103" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J103" t="str">
         <v>https://music.apple.com/us/artist/static-dress/1476714067</v>
       </c>
-      <c r="K102" t="str">
+      <c r="K103" t="str">
         <v>https://music.apple.com/us/album/nostalgia-kills/1887961038</v>
       </c>
-      <c r="L102" t="str">
+      <c r="L103" t="str">
         <v>Nostalgia Kills - Static Dress</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L103"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/the-more-i-hope/1882826389</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/the-van/1872842315</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/reply-to-this/1888625007</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/funny-friends/1861531673</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/turtleneck/1890056028</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/g-o-d-and-the-broken-ribs/1883199709</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/in-a-life/1888147404</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/buy-me-a-car/1887659688</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/chica-305/1888292975</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/back-home/1870867424</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/reputation/1888615203</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/mural/1885914724</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/business-personal-second-half/1889934787</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/beams/1862570896</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/hysteria/1887407036</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/need-your-love/1884740423</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/my-mouth-is-lonely-for-you-from-mother-mary/1886744205</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/sorry-crash/1886485698</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/shine-again/1887991690</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/choose-love/1877910665</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/babyrecords/1888590545</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/paperbag-boy/1889345415</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/i-am/1880890454</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/want-love/1886384365</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/live-love-learn/1884749128</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/footlights/1885660551</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/remember-to-forget/1887886676</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/sun-comes-up-tremendous/1883229766</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/say-so/1888326036</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/fantasy/1880361475</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/favour/1885941038</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/dangerous-lover/1884781285</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/foolsong/1886215975</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/i-dont-wanna-be/1888501665</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/lonesome-dove/1874700246</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/cowgirls-prayer/1884167296</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/hall-of-fame/1886576289</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/american-wedding/1885995636</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/fashion/1887487303</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/heal/1880216061</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/beautiful/1887979307</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/wildfire/1887444526</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/sliced-by-a-fingernail/1879769225</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/fenian-feat-casiokids/1881565596</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/s%C3%B3lo-t%C3%BA/1887417656</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/the-jesus-i-know-now/1887978274</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/turnstile/1867616937</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/surrender-from-your-friends-neighbors/1887371368</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/before-this-even-starts/1883698214</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/roses/1883777517</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/does-your-father-know-you-dance-like-that/1886621446</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/loco/1888397210</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/hold-it-for-her/1861380253</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/ghost-town/1870971561</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/waste-some-time/1887768620</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/control/1887392580</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/wouldnt-try-again/1889328836</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/i-need-u/1889349101</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/outlaw/1877229747</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/a-l-o-n-e/1886537119</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/him/1887319676</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/mvp-feat-key-glock/1888298376</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/s-i-m-p-l-e/1885386665</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/at-least-shes-beautiful/1884405874</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/hella-good-feat-bonnie-mckee/1886001675</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/the-show/1889121528</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/his-eye-is-on-the-sparrow/1880392628</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/slowly/1869140941</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/on-our-way-along/1863814124</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/coming-of-age/1882886175</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/the-man-with-money-in-his-hands/1887707057</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/wrangler/1876267962</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/rydly/1878477155</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/all-the-time/1874100418</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/misery/1888294484</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/dont-fall/1884794995</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/alternate-ending/1886010374</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/lucky/1888001208</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/mutual/1882922798</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/waiting-on/1883846539</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/en-la-monta%C3%B1a/1884092212</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/falling-short/1884803703</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/when-you-give-it-up/1879883866</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/wasted/1885578001</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/burn/1883195616</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/smash/1884655608</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/smile/1859619683</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/eshi/1880700566</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/no-homegirls/1886801763</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/i-want-you-back/1889281139</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/needed-you/1887702402</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/finish-line/1887371855</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/daredevil/1883231048</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/asleep-on-the-killing-floor/1869086163</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/you-bastard/1871211807</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/vanilla-latte/1884524943</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/nostalgia-kills/1887961043</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E103" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L104"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Sick Of Love</v>
+        <v>PINKY UP</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
+        <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-09</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>The Afterparty</v>
+        <v>PINKY UP - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>3:36</v>
+        <v>2:11</v>
       </c>
       <c r="H2" t="str">
-        <v>Lykke Li</v>
+        <v>KATSEYE</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/katseye/1754284416</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/sick-of-love/1857952252</v>
+        <v>https://music.apple.com/us/album/pinky-up/1888235065</v>
       </c>
       <c r="L2" t="str">
-        <v>Sick Of Love - Lykke Li</v>
+        <v>PINKY UP - KATSEYE</v>
       </c>
     </row>
     <row r="3">
@@ -778,13 +778,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ember</v>
+        <v>Sick Of Love</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/ember/1880484164</v>
+        <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-09</v>
@@ -793,25 +793,25 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G11" t="str">
-        <v>3:25</v>
+        <v>3:36</v>
       </c>
       <c r="H11" t="str">
-        <v>Iceage</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/ember/1880484160</v>
+        <v>https://music.apple.com/us/album/sick-of-love/1857952252</v>
       </c>
       <c r="L11" t="str">
-        <v>Ember - Iceage</v>
+        <v>Sick Of Love - Lykke Li</v>
       </c>
     </row>
     <row r="12">
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Turnaround</v>
+        <v>Ember</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
+        <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-09</v>
@@ -869,25 +869,25 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Turnaround / I'm Hooked - Single</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G13" t="str">
-        <v>3:14</v>
+        <v>3:25</v>
       </c>
       <c r="H13" t="str">
-        <v>54 Ultra</v>
+        <v>Iceage</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
+        <v>https://music.apple.com/us/album/ember/1880484160</v>
       </c>
       <c r="L13" t="str">
-        <v>Turnaround - 54 Ultra</v>
+        <v>Ember - Iceage</v>
       </c>
     </row>
     <row r="14">
@@ -930,13 +930,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Home on the Range</v>
+        <v>Turnaround</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
+        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-09</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Turnaround / I'm Hooked - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>1:37</v>
+        <v>3:14</v>
       </c>
       <c r="H15" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>54 Ultra</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
+        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
       </c>
       <c r="L15" t="str">
-        <v>Home on the Range - Earl Sweatshirt</v>
+        <v>Turnaround - 54 Ultra</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Back Home</v>
+        <v>Home on the Range</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/back-home/1870867424</v>
+        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-09</v>
@@ -986,33 +986,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G16" t="str">
-        <v>1:36</v>
+        <v>1:37</v>
       </c>
       <c r="H16" t="str">
-        <v>MIKE</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/back-home/1870867411</v>
+        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
       </c>
       <c r="L16" t="str">
-        <v>Back Home - MIKE</v>
+        <v>Home on the Range - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Reputation</v>
+        <v>Back Home</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/reputation/1888615203</v>
+        <v>https://music.apple.com/us/song/back-home/1870867424</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-09</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Reputation / Bobby - Single</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G17" t="str">
-        <v>3:55</v>
+        <v>1:36</v>
       </c>
       <c r="H17" t="str">
-        <v>Ravyn Lenae</v>
+        <v>MIKE</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/reputation/1888615202</v>
+        <v>https://music.apple.com/us/album/back-home/1870867411</v>
       </c>
       <c r="L17" t="str">
-        <v>Reputation - Ravyn Lenae</v>
+        <v>Back Home - MIKE</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>MURAL</v>
+        <v>Reputation</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/mural/1885914724</v>
+        <v>https://music.apple.com/us/song/reputation/1888615203</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-09</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>Reputation / Bobby - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>3:26</v>
+        <v>3:55</v>
       </c>
       <c r="H18" t="str">
-        <v>Swae Lee</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/mural/1885914714</v>
+        <v>https://music.apple.com/us/album/reputation/1888615202</v>
       </c>
       <c r="L18" t="str">
-        <v>MURAL - Swae Lee</v>
+        <v>Reputation - Ravyn Lenae</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Business &amp; Personal (second half)</v>
+        <v>MURAL</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/business-personal-second-half/1889934787</v>
+        <v>https://music.apple.com/us/song/mural/1885914724</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-09</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Business &amp; Personal - Single</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G19" t="str">
-        <v>2:19</v>
+        <v>3:26</v>
       </c>
       <c r="H19" t="str">
-        <v>Latto</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/business-personal-second-half/1889934634</v>
+        <v>https://music.apple.com/us/album/mural/1885914714</v>
       </c>
       <c r="L19" t="str">
-        <v>Business &amp; Personal (second half) - Latto</v>
+        <v>MURAL - Swae Lee</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Beams</v>
+        <v>Business &amp; Personal (second half)</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/beams/1862570896</v>
+        <v>https://music.apple.com/us/song/business-personal-second-half/1889934787</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-09</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Business &amp; Personal - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:39</v>
+        <v>2:19</v>
       </c>
       <c r="H20" t="str">
-        <v>Arlo Parks</v>
+        <v>Latto</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/beams/1862570378</v>
+        <v>https://music.apple.com/us/album/business-personal-second-half/1889934634</v>
       </c>
       <c r="L20" t="str">
-        <v>Beams - Arlo Parks</v>
+        <v>Business &amp; Personal (second half) - Latto</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Hysteria</v>
+        <v>Beams</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/hysteria/1887407036</v>
+        <v>https://music.apple.com/us/song/beams/1862570896</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-09</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Hysteria - Single</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G21" t="str">
-        <v>2:23</v>
+        <v>3:39</v>
       </c>
       <c r="H21" t="str">
-        <v>Bebe Rexha</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/hysteria/1887407035</v>
+        <v>https://music.apple.com/us/album/beams/1862570378</v>
       </c>
       <c r="L21" t="str">
-        <v>Hysteria - Bebe Rexha</v>
+        <v>Beams - Arlo Parks</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Need Your Love</v>
+        <v>Hysteria</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/need-your-love/1884740423</v>
+        <v>https://music.apple.com/us/song/hysteria/1887407036</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-09</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Need Your Love - Single</v>
+        <v>Hysteria - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:58</v>
+        <v>2:23</v>
       </c>
       <c r="H22" t="str">
-        <v>OneRepublic</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/need-your-love/1884740422</v>
+        <v>https://music.apple.com/us/album/hysteria/1887407035</v>
       </c>
       <c r="L22" t="str">
-        <v>Need Your Love - OneRepublic</v>
+        <v>Hysteria - Bebe Rexha</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>My Mouth Is Lonely For You (from Mother Mary)</v>
+        <v>Need Your Love</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/my-mouth-is-lonely-for-you-from-mother-mary/1886744205</v>
+        <v>https://music.apple.com/us/song/need-your-love/1884740423</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-09</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>My Mouth Is Lonely For You (from Mother Mary) - Single</v>
+        <v>Need Your Love - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>4:04</v>
+        <v>3:58</v>
       </c>
       <c r="H23" t="str">
-        <v>Anne Hathaway</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/my-mouth-is-lonely-for-you-from-mother-mary/1886744203</v>
+        <v>https://music.apple.com/us/album/need-your-love/1884740422</v>
       </c>
       <c r="L23" t="str">
-        <v>My Mouth Is Lonely For You (from Mother Mary) - Anne Hathaway</v>
+        <v>Need Your Love - OneRepublic</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SORRY! CRASH!</v>
+        <v>My Mouth Is Lonely For You (from Mother Mary)</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/sorry-crash/1886485698</v>
+        <v>https://music.apple.com/us/song/my-mouth-is-lonely-for-you-from-mother-mary/1886744205</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-09</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>My Mouth Is Lonely For You (from Mother Mary) - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>3:09</v>
+        <v>4:04</v>
       </c>
       <c r="H24" t="str">
-        <v>Ecca Vandal</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/sorry-crash/1886485694</v>
+        <v>https://music.apple.com/us/album/my-mouth-is-lonely-for-you-from-mother-mary/1886744203</v>
       </c>
       <c r="L24" t="str">
-        <v>SORRY! CRASH! - Ecca Vandal</v>
+        <v>My Mouth Is Lonely For You (from Mother Mary) - Anne Hathaway</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Shine Again</v>
+        <v>SORRY! CRASH!</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/shine-again/1887991690</v>
+        <v>https://music.apple.com/us/song/sorry-crash/1886485698</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-09</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Shine Again - Single</v>
+        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
       </c>
       <c r="G25" t="str">
-        <v>4:05</v>
+        <v>3:09</v>
       </c>
       <c r="H25" t="str">
-        <v>Weezer</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/shine-again/1887991688</v>
+        <v>https://music.apple.com/us/album/sorry-crash/1886485694</v>
       </c>
       <c r="L25" t="str">
-        <v>Shine Again - Weezer</v>
+        <v>SORRY! CRASH! - Ecca Vandal</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Choose Love</v>
+        <v>Shine Again</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/choose-love/1877910665</v>
+        <v>https://music.apple.com/us/song/shine-again/1887991690</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-09</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Long Long Road</v>
+        <v>Shine Again - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>3:54</v>
+        <v>4:05</v>
       </c>
       <c r="H26" t="str">
-        <v>Ringo Starr</v>
+        <v>Weezer</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/choose-love/1877910655</v>
+        <v>https://music.apple.com/us/album/shine-again/1887991688</v>
       </c>
       <c r="L26" t="str">
-        <v>Choose Love - Ringo Starr</v>
+        <v>Shine Again - Weezer</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>BABYRECORDS.</v>
+        <v>Choose Love</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/babyrecords/1888590545</v>
+        <v>https://music.apple.com/us/song/choose-love/1877910665</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-09</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>BABYRECORDS. - Single</v>
+        <v>Long Long Road</v>
       </c>
       <c r="G27" t="str">
-        <v>2:29</v>
+        <v>3:54</v>
       </c>
       <c r="H27" t="str">
-        <v>Álvaro Díaz</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/babyrecords/1888590544</v>
+        <v>https://music.apple.com/us/album/choose-love/1877910655</v>
       </c>
       <c r="L27" t="str">
-        <v>BABYRECORDS. - Álvaro Díaz</v>
+        <v>Choose Love - Ringo Starr</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Paperbag Boy</v>
+        <v>BABYRECORDS.</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/paperbag-boy/1889345415</v>
+        <v>https://music.apple.com/us/song/babyrecords/1888590545</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-09</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Paperbag Boy - Single</v>
+        <v>BABYRECORDS. - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>3:11</v>
+        <v>2:29</v>
       </c>
       <c r="H28" t="str">
-        <v>Trippie Redd</v>
+        <v>Álvaro Díaz</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/trippie-redd/1203172438</v>
+        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/paperbag-boy/1889345414</v>
+        <v>https://music.apple.com/us/album/babyrecords/1888590544</v>
       </c>
       <c r="L28" t="str">
-        <v>Paperbag Boy - Trippie Redd</v>
+        <v>BABYRECORDS. - Álvaro Díaz</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>I AM</v>
+        <v>Paperbag Boy</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/i-am/1880890454</v>
+        <v>https://music.apple.com/us/song/paperbag-boy/1889345415</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-09</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>CLARITY OF MIND</v>
+        <v>Paperbag Boy - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:12</v>
+        <v>3:11</v>
       </c>
       <c r="H29" t="str">
-        <v>OMAH LAY</v>
+        <v>Trippie Redd</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
+        <v>https://music.apple.com/us/artist/trippie-redd/1203172438</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/i-am/1880890112</v>
+        <v>https://music.apple.com/us/album/paperbag-boy/1889345414</v>
       </c>
       <c r="L29" t="str">
-        <v>I AM - OMAH LAY</v>
+        <v>Paperbag Boy - Trippie Redd</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Want Love</v>
+        <v>I AM</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/want-love/1886384365</v>
+        <v>https://music.apple.com/us/song/i-am/1880890454</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-09</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Want Love - Single</v>
+        <v>CLARITY OF MIND</v>
       </c>
       <c r="G30" t="str">
-        <v>3:20</v>
+        <v>3:12</v>
       </c>
       <c r="H30" t="str">
-        <v>Mary J. Blige</v>
+        <v>OMAH LAY</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/want-love/1886384355</v>
+        <v>https://music.apple.com/us/album/i-am/1880890112</v>
       </c>
       <c r="L30" t="str">
-        <v>Want Love - Mary J. Blige</v>
+        <v>I AM - OMAH LAY</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Live, Love, Learn</v>
+        <v>Want Love</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/live-love-learn/1884749128</v>
+        <v>https://music.apple.com/us/song/want-love/1886384365</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-09</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Live, Love, Learn - Single</v>
+        <v>Want Love - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>4:19</v>
+        <v>3:20</v>
       </c>
       <c r="H31" t="str">
-        <v>Estelle</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/estelle/27060010</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/live-love-learn/1884749126</v>
+        <v>https://music.apple.com/us/album/want-love/1886384355</v>
       </c>
       <c r="L31" t="str">
-        <v>Live, Love, Learn - Estelle</v>
+        <v>Want Love - Mary J. Blige</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Footlights</v>
+        <v>Live, Love, Learn</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/footlights/1885660551</v>
+        <v>https://music.apple.com/us/song/live-love-learn/1884749128</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-09</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Footlights - Single</v>
+        <v>Live, Love, Learn - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>4:24</v>
+        <v>4:19</v>
       </c>
       <c r="H32" t="str">
-        <v>Cody Johnson</v>
+        <v>Estelle</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/estelle/27060010</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/footlights/1885660550</v>
+        <v>https://music.apple.com/us/album/live-love-learn/1884749126</v>
       </c>
       <c r="L32" t="str">
-        <v>Footlights - Cody Johnson</v>
+        <v>Live, Love, Learn - Estelle</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Remember to Forget</v>
+        <v>Footlights</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/remember-to-forget/1887886676</v>
+        <v>https://music.apple.com/us/song/footlights/1885660551</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-09</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Remember to Forget - Single</v>
+        <v>Footlights - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:39</v>
+        <v>4:24</v>
       </c>
       <c r="H33" t="str">
-        <v>Hailey Whitters</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/hailey-whitters/553410914</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/remember-to-forget/1887886674</v>
+        <v>https://music.apple.com/us/album/footlights/1885660550</v>
       </c>
       <c r="L33" t="str">
-        <v>Remember to Forget - Hailey Whitters</v>
+        <v>Footlights - Cody Johnson</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Sun Comes Up Tremendous</v>
+        <v>Remember to Forget</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/sun-comes-up-tremendous/1883229766</v>
+        <v>https://music.apple.com/us/song/remember-to-forget/1887886676</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-09</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Sun Comes Up Tremendous - Single</v>
+        <v>Remember to Forget - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:33</v>
+        <v>3:39</v>
       </c>
       <c r="H34" t="str">
-        <v>Disclosure</v>
+        <v>Hailey Whitters</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/disclosure/520848228</v>
+        <v>https://music.apple.com/us/artist/hailey-whitters/553410914</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/sun-comes-up-tremendous/1883229765</v>
+        <v>https://music.apple.com/us/album/remember-to-forget/1887886674</v>
       </c>
       <c r="L34" t="str">
-        <v>Sun Comes Up Tremendous - Disclosure</v>
+        <v>Remember to Forget - Hailey Whitters</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Say So</v>
+        <v>Sun Comes Up Tremendous</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/say-so/1888326036</v>
+        <v>https://music.apple.com/us/song/sun-comes-up-tremendous/1883229766</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-09</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Say So - Single</v>
+        <v>Sun Comes Up Tremendous - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:21</v>
+        <v>3:33</v>
       </c>
       <c r="H35" t="str">
-        <v>Dan + Shay</v>
+        <v>Disclosure</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
+        <v>https://music.apple.com/us/artist/disclosure/520848228</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/say-so/1888325785</v>
+        <v>https://music.apple.com/us/album/sun-comes-up-tremendous/1883229765</v>
       </c>
       <c r="L35" t="str">
-        <v>Say So - Dan + Shay</v>
+        <v>Sun Comes Up Tremendous - Disclosure</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Fantasy</v>
+        <v>Say So</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1880361475</v>
+        <v>https://music.apple.com/us/song/say-so/1888326036</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-09</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Lost, Found &amp; Forgotten...</v>
+        <v>Say So - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>4:07</v>
+        <v>3:21</v>
       </c>
       <c r="H36" t="str">
-        <v>Chris Stussy</v>
+        <v>Dan + Shay</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1880361449</v>
+        <v>https://music.apple.com/us/album/say-so/1888325785</v>
       </c>
       <c r="L36" t="str">
-        <v>Fantasy - Chris Stussy</v>
+        <v>Say So - Dan + Shay</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Favour</v>
+        <v>Fantasy</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/favour/1885941038</v>
+        <v>https://music.apple.com/us/song/fantasy/1880361475</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-09</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Favour - Single</v>
+        <v>Lost, Found &amp; Forgotten...</v>
       </c>
       <c r="G37" t="str">
-        <v>3:14</v>
+        <v>4:07</v>
       </c>
       <c r="H37" t="str">
-        <v>FISHER</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/favour/1885941037</v>
+        <v>https://music.apple.com/us/album/fantasy/1880361449</v>
       </c>
       <c r="L37" t="str">
-        <v>Favour - FISHER</v>
+        <v>Fantasy - Chris Stussy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dangerous Lover</v>
+        <v>Favour</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/dangerous-lover/1884781285</v>
+        <v>https://music.apple.com/us/song/favour/1885941038</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-09</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Dangerous Lover - Single</v>
+        <v>Favour - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>3:24</v>
+        <v>3:14</v>
       </c>
       <c r="H38" t="str">
-        <v>Sekou</v>
+        <v>FISHER</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/sekou/1685844750</v>
+        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/dangerous-lover/1884781284</v>
+        <v>https://music.apple.com/us/album/favour/1885941037</v>
       </c>
       <c r="L38" t="str">
-        <v>Dangerous Lover - Sekou</v>
+        <v>Favour - FISHER</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Foolsong</v>
+        <v>Dangerous Lover</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/foolsong/1886215975</v>
+        <v>https://music.apple.com/us/song/dangerous-lover/1884781285</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-09</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Foolsong - Single</v>
+        <v>Dangerous Lover - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:18</v>
+        <v>3:24</v>
       </c>
       <c r="H39" t="str">
-        <v>aron!</v>
+        <v>Sekou</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/sekou/1685844750</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/foolsong/1886215974</v>
+        <v>https://music.apple.com/us/album/dangerous-lover/1884781284</v>
       </c>
       <c r="L39" t="str">
-        <v>Foolsong - aron!</v>
+        <v>Dangerous Lover - Sekou</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>I Don't Wanna Be</v>
+        <v>Foolsong</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/i-dont-wanna-be/1888501665</v>
+        <v>https://music.apple.com/us/song/foolsong/1886215975</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-09</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>I Don't Wanna Be - Single</v>
+        <v>Foolsong - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:16</v>
+        <v>3:18</v>
       </c>
       <c r="H40" t="str">
-        <v>Blake Rose</v>
+        <v>aron!</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/blake-rose/1167991720</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/i-dont-wanna-be/1888501664</v>
+        <v>https://music.apple.com/us/album/foolsong/1886215974</v>
       </c>
       <c r="L40" t="str">
-        <v>I Don't Wanna Be - Blake Rose</v>
+        <v>Foolsong - aron!</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Lonesome Dove</v>
+        <v>I Don't Wanna Be</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/lonesome-dove/1874700246</v>
+        <v>https://music.apple.com/us/song/i-dont-wanna-be/1888501665</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-09</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Age of the Ram</v>
+        <v>I Don't Wanna Be - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:04</v>
+        <v>3:16</v>
       </c>
       <c r="H41" t="str">
-        <v>Charley Crockett</v>
+        <v>Blake Rose</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/blake-rose/1167991720</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/lonesome-dove/1874700242</v>
+        <v>https://music.apple.com/us/album/i-dont-wanna-be/1888501664</v>
       </c>
       <c r="L41" t="str">
-        <v>Lonesome Dove - Charley Crockett</v>
+        <v>I Don't Wanna Be - Blake Rose</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Cowgirl's Prayer</v>
+        <v>Lonesome Dove</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/cowgirls-prayer/1884167296</v>
+        <v>https://music.apple.com/us/song/lonesome-dove/1874700246</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-09</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Cowgirl's Prayer - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G42" t="str">
-        <v>3:49</v>
+        <v>3:04</v>
       </c>
       <c r="H42" t="str">
-        <v>Danielle Bradbery</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/danielle-bradbery/624068729</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/cowgirls-prayer/1884167295</v>
+        <v>https://music.apple.com/us/album/lonesome-dove/1874700242</v>
       </c>
       <c r="L42" t="str">
-        <v>Cowgirl's Prayer - Danielle Bradbery</v>
+        <v>Lonesome Dove - Charley Crockett</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Hall of Fame</v>
+        <v>Cowgirl's Prayer</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/hall-of-fame/1886576289</v>
+        <v>https://music.apple.com/us/song/cowgirls-prayer/1884167296</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-09</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Hall of Fame - Single</v>
+        <v>Cowgirl's Prayer - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:11</v>
+        <v>3:49</v>
       </c>
       <c r="H43" t="str">
-        <v>Chxrry</v>
+        <v>Danielle Bradbery</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/danielle-bradbery/624068729</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/hall-of-fame/1886576288</v>
+        <v>https://music.apple.com/us/album/cowgirls-prayer/1884167295</v>
       </c>
       <c r="L43" t="str">
-        <v>Hall of Fame - Chxrry</v>
+        <v>Cowgirl's Prayer - Danielle Bradbery</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>American Wedding</v>
+        <v>Hall of Fame</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/american-wedding/1885995636</v>
+        <v>https://music.apple.com/us/song/hall-of-fame/1886576289</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-09</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>American Wedding - Single</v>
+        <v>Hall of Fame - Single</v>
       </c>
       <c r="G44" t="str">
         <v>3:11</v>
       </c>
       <c r="H44" t="str">
-        <v>flowerovlove</v>
+        <v>Chxrry</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/american-wedding/1885995635</v>
+        <v>https://music.apple.com/us/album/hall-of-fame/1886576288</v>
       </c>
       <c r="L44" t="str">
-        <v>American Wedding - flowerovlove</v>
+        <v>Hall of Fame - Chxrry</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Fashion</v>
+        <v>American Wedding</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/fashion/1887487303</v>
+        <v>https://music.apple.com/us/song/american-wedding/1885995636</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-09</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Fashion - Single</v>
+        <v>American Wedding - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>2:08</v>
+        <v>3:11</v>
       </c>
       <c r="H45" t="str">
-        <v>IVE</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/fashion/1887487297</v>
+        <v>https://music.apple.com/us/album/american-wedding/1885995635</v>
       </c>
       <c r="L45" t="str">
-        <v>Fashion - IVE</v>
+        <v>American Wedding - flowerovlove</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>heal</v>
+        <v>Fashion</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/heal/1880216061</v>
+        <v>https://music.apple.com/us/song/fashion/1887487303</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-09</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Unfold</v>
+        <v>Fashion - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:59</v>
+        <v>2:08</v>
       </c>
       <c r="H46" t="str">
-        <v>MONSTA X</v>
+        <v>IVE</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/monsta-x/992315362</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/heal/1880216060</v>
+        <v>https://music.apple.com/us/album/fashion/1887487297</v>
       </c>
       <c r="L46" t="str">
-        <v>heal - MONSTA X</v>
+        <v>Fashion - IVE</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Beautiful</v>
+        <v>heal</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1887979307</v>
+        <v>https://music.apple.com/us/song/heal/1880216061</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-09</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Beautiful - Single</v>
+        <v>Unfold</v>
       </c>
       <c r="G47" t="str">
-        <v>3:35</v>
+        <v>3:59</v>
       </c>
       <c r="H47" t="str">
-        <v>Anyma</v>
+        <v>MONSTA X</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
+        <v>https://music.apple.com/us/artist/monsta-x/992315362</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1887979305</v>
+        <v>https://music.apple.com/us/album/heal/1880216060</v>
       </c>
       <c r="L47" t="str">
-        <v>Beautiful - Anyma</v>
+        <v>heal - MONSTA X</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Wildfire</v>
+        <v>Beautiful</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/wildfire/1887444526</v>
+        <v>https://music.apple.com/us/song/beautiful/1887979307</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-09</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>For All The Right Reasons, Vol. 1</v>
+        <v>Beautiful - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>3:11</v>
+        <v>3:35</v>
       </c>
       <c r="H48" t="str">
-        <v>Lekan</v>
+        <v>Anyma</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/wildfire/1887444297</v>
+        <v>https://music.apple.com/us/album/beautiful/1887979305</v>
       </c>
       <c r="L48" t="str">
-        <v>Wildfire - Lekan</v>
+        <v>Beautiful - Anyma</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Sliced by a Fingernail</v>
+        <v>Wildfire</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/sliced-by-a-fingernail/1879769225</v>
+        <v>https://music.apple.com/us/song/wildfire/1887444526</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-09</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Sliced by a Fingernail - Single</v>
+        <v>For All The Right Reasons, Vol. 1</v>
       </c>
       <c r="G49" t="str">
-        <v>4:08</v>
+        <v>3:11</v>
       </c>
       <c r="H49" t="str">
-        <v>Dry Cleaning</v>
+        <v>Lekan</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/dry-cleaning/1469164908</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/sliced-by-a-fingernail/1879769223</v>
+        <v>https://music.apple.com/us/album/wildfire/1887444297</v>
       </c>
       <c r="L49" t="str">
-        <v>Sliced by a Fingernail - Dry Cleaning</v>
+        <v>Wildfire - Lekan</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>FENIAN (feat. Casiokids)</v>
+        <v>Sliced by a Fingernail</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/fenian-feat-casiokids/1881565596</v>
+        <v>https://music.apple.com/us/song/sliced-by-a-fingernail/1879769225</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-09</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>FENIAN - Single</v>
+        <v>Sliced by a Fingernail - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>3:14</v>
+        <v>4:08</v>
       </c>
       <c r="H50" t="str">
-        <v>Kneecap</v>
+        <v>Dry Cleaning</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/dry-cleaning/1469164908</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/fenian-feat-casiokids/1881565579</v>
+        <v>https://music.apple.com/us/album/sliced-by-a-fingernail/1879769223</v>
       </c>
       <c r="L50" t="str">
-        <v>FENIAN (feat. Casiokids) - Kneecap</v>
+        <v>Sliced by a Fingernail - Dry Cleaning</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Sólo Tú</v>
+        <v>FENIAN (feat. Casiokids)</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/s%C3%B3lo-t%C3%BA/1887417656</v>
+        <v>https://music.apple.com/us/song/fenian-feat-casiokids/1881565596</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-09</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Sólo Tú - Single</v>
+        <v>FENIAN - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>2:37</v>
+        <v>3:14</v>
       </c>
       <c r="H51" t="str">
-        <v>Los Primos Del Este</v>
+        <v>Kneecap</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/los-primos-del-este/1462043487</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/s%C3%B3lo-t%C3%BA/1887417649</v>
+        <v>https://music.apple.com/us/album/fenian-feat-casiokids/1881565579</v>
       </c>
       <c r="L51" t="str">
-        <v>Sólo Tú - Los Primos Del Este</v>
+        <v>FENIAN (feat. Casiokids) - Kneecap</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>The Jesus I Know Now</v>
+        <v>Sólo Tú</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-i-know-now/1887978274</v>
+        <v>https://music.apple.com/us/song/s%C3%B3lo-t%C3%BA/1887417656</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-09</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>The Jesus I Know Now - Single</v>
+        <v>Sólo Tú - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:33</v>
+        <v>2:37</v>
       </c>
       <c r="H52" t="str">
-        <v>Brandon Lake</v>
+        <v>Los Primos Del Este</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
+        <v>https://music.apple.com/us/artist/los-primos-del-este/1462043487</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-i-know-now/1887978263</v>
+        <v>https://music.apple.com/us/album/s%C3%B3lo-t%C3%BA/1887417649</v>
       </c>
       <c r="L52" t="str">
-        <v>The Jesus I Know Now - Brandon Lake</v>
+        <v>Sólo Tú - Los Primos Del Este</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Turnstile</v>
+        <v>The Jesus I Know Now</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/turnstile/1867616937</v>
+        <v>https://music.apple.com/us/song/the-jesus-i-know-now/1887978274</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-09</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>The Weight of the Woods</v>
+        <v>The Jesus I Know Now - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>3:50</v>
+        <v>3:33</v>
       </c>
       <c r="H53" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/turnstile/1867616617</v>
+        <v>https://music.apple.com/us/album/the-jesus-i-know-now/1887978263</v>
       </c>
       <c r="L53" t="str">
-        <v>Turnstile - Dermot Kennedy</v>
+        <v>The Jesus I Know Now - Brandon Lake</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Surrender (From Your Friends &amp; Neighbors)</v>
+        <v>Turnstile</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/surrender-from-your-friends-neighbors/1887371368</v>
+        <v>https://music.apple.com/us/song/turnstile/1867616937</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-09</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Surrender (From Your Friends &amp; Neighbors) - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G54" t="str">
-        <v>3:04</v>
+        <v>3:50</v>
       </c>
       <c r="H54" t="str">
-        <v>Lindsey Stirling</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/lindsey-stirling/403025113</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/surrender-from-your-friends-neighbors/1887371353</v>
+        <v>https://music.apple.com/us/album/turnstile/1867616617</v>
       </c>
       <c r="L54" t="str">
-        <v>Surrender (From Your Friends &amp; Neighbors) - Lindsey Stirling</v>
+        <v>Turnstile - Dermot Kennedy</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Before This Even Starts</v>
+        <v>Surrender (From Your Friends &amp; Neighbors)</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/before-this-even-starts/1883698214</v>
+        <v>https://music.apple.com/us/song/surrender-from-your-friends-neighbors/1887371368</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-09</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Therapy &amp; Yoga - EP</v>
+        <v>Surrender (From Your Friends &amp; Neighbors) - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>2:44</v>
+        <v>3:04</v>
       </c>
       <c r="H55" t="str">
-        <v>JESSIA</v>
+        <v>Lindsey Stirling</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/jessia/1399415802</v>
+        <v>https://music.apple.com/us/artist/lindsey-stirling/403025113</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/before-this-even-starts/1883698028</v>
+        <v>https://music.apple.com/us/album/surrender-from-your-friends-neighbors/1887371353</v>
       </c>
       <c r="L55" t="str">
-        <v>Before This Even Starts - JESSIA</v>
+        <v>Surrender (From Your Friends &amp; Neighbors) - Lindsey Stirling</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Roses</v>
+        <v>Before This Even Starts</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/roses/1883777517</v>
+        <v>https://music.apple.com/us/song/before-this-even-starts/1883698214</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-09</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Middle School Dropout - EP</v>
+        <v>Therapy &amp; Yoga - EP</v>
       </c>
       <c r="G56" t="str">
-        <v>3:10</v>
+        <v>2:44</v>
       </c>
       <c r="H56" t="str">
-        <v>Iris Copperman</v>
+        <v>JESSIA</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/jessia/1399415802</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/roses/1883777352</v>
+        <v>https://music.apple.com/us/album/before-this-even-starts/1883698028</v>
       </c>
       <c r="L56" t="str">
-        <v>Roses - Iris Copperman</v>
+        <v>Before This Even Starts - JESSIA</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Does Your Father Know You Dance Like That?</v>
+        <v>Roses</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/does-your-father-know-you-dance-like-that/1886621446</v>
+        <v>https://music.apple.com/us/song/roses/1883777517</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-09</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Does Your Father Know You Dance Like That? - Single</v>
+        <v>Middle School Dropout - EP</v>
       </c>
       <c r="G57" t="str">
-        <v>2:28</v>
+        <v>3:10</v>
       </c>
       <c r="H57" t="str">
-        <v>Steve Aoki</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/does-your-father-know-you-dance-like-that/1886621445</v>
+        <v>https://music.apple.com/us/album/roses/1883777352</v>
       </c>
       <c r="L57" t="str">
-        <v>Does Your Father Know You Dance Like That? - Steve Aoki</v>
+        <v>Roses - Iris Copperman</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loco</v>
+        <v>Does Your Father Know You Dance Like That?</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/loco/1888397210</v>
+        <v>https://music.apple.com/us/song/does-your-father-know-you-dance-like-that/1886621446</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-09</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Loco - Single</v>
+        <v>Does Your Father Know You Dance Like That? - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>2:34</v>
+        <v>2:28</v>
       </c>
       <c r="H58" t="str">
-        <v>Key Glock</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/key-glock/1199258326</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/loco/1888397209</v>
+        <v>https://music.apple.com/us/album/does-your-father-know-you-dance-like-that/1886621445</v>
       </c>
       <c r="L58" t="str">
-        <v>Loco - Key Glock</v>
+        <v>Does Your Father Know You Dance Like That? - Steve Aoki</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Hold It For Her</v>
+        <v>Loco</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/hold-it-for-her/1861380253</v>
+        <v>https://music.apple.com/us/song/loco/1888397210</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-09</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Porcelain</v>
+        <v>Loco - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="H59" t="str">
-        <v>Peach PRC</v>
+        <v>Key Glock</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/key-glock/1199258326</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/hold-it-for-her/1861380240</v>
+        <v>https://music.apple.com/us/album/loco/1888397209</v>
       </c>
       <c r="L59" t="str">
-        <v>Hold It For Her - Peach PRC</v>
+        <v>Loco - Key Glock</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ghost town...</v>
+        <v>Hold It For Her</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/ghost-town/1870971561</v>
+        <v>https://music.apple.com/us/song/hold-it-for-her/1861380253</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-09</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Porcelain</v>
       </c>
       <c r="G60" t="str">
-        <v>2:44</v>
+        <v>3:48</v>
       </c>
       <c r="H60" t="str">
-        <v>R3HAB</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/ghost-town/1870971550</v>
+        <v>https://music.apple.com/us/album/hold-it-for-her/1861380240</v>
       </c>
       <c r="L60" t="str">
-        <v>Ghost town... - R3HAB</v>
+        <v>Hold It For Her - Peach PRC</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>WASTE SOME TIME</v>
+        <v>Ghost town...</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/waste-some-time/1887768620</v>
+        <v>https://music.apple.com/us/song/ghost-town/1870971561</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-09</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>DAWN PATROL</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G61" t="str">
-        <v>3:26</v>
+        <v>2:44</v>
       </c>
       <c r="H61" t="str">
-        <v>Forrest Frank</v>
+        <v>R3HAB</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/waste-some-time/1887768606</v>
+        <v>https://music.apple.com/us/album/ghost-town/1870971550</v>
       </c>
       <c r="L61" t="str">
-        <v>WASTE SOME TIME - Forrest Frank</v>
+        <v>Ghost town... - R3HAB</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>control.</v>
+        <v>WASTE SOME TIME</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/control/1887392580</v>
+        <v>https://music.apple.com/us/song/waste-some-time/1887768620</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-09</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>control. - Single</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G62" t="str">
-        <v>2:50</v>
+        <v>3:26</v>
       </c>
       <c r="H62" t="str">
-        <v>Paco</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/paco/1513830139</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/control/1887392578</v>
+        <v>https://music.apple.com/us/album/waste-some-time/1887768606</v>
       </c>
       <c r="L62" t="str">
-        <v>control. - Paco</v>
+        <v>WASTE SOME TIME - Forrest Frank</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Wouldn't Try Again</v>
+        <v>control.</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/wouldnt-try-again/1889328836</v>
+        <v>https://music.apple.com/us/song/control/1887392580</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-09</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Wouldn't Try Again - Single</v>
+        <v>control. - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>2:45</v>
+        <v>2:50</v>
       </c>
       <c r="H63" t="str">
-        <v>Quail P</v>
+        <v>Paco</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/quail-p/1447409001</v>
+        <v>https://music.apple.com/us/artist/paco/1513830139</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/wouldnt-try-again/1889328830</v>
+        <v>https://music.apple.com/us/album/control/1887392578</v>
       </c>
       <c r="L63" t="str">
-        <v>Wouldn't Try Again - Quail P</v>
+        <v>control. - Paco</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>i need u</v>
+        <v>Wouldn't Try Again</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/i-need-u/1889349101</v>
+        <v>https://music.apple.com/us/song/wouldnt-try-again/1889328836</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-09</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>i need u - Single</v>
+        <v>Wouldn't Try Again - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:45</v>
+        <v>2:45</v>
       </c>
       <c r="H64" t="str">
-        <v>BUNT.</v>
+        <v>Quail P</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/quail-p/1447409001</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/i-need-u/1889349100</v>
+        <v>https://music.apple.com/us/album/wouldnt-try-again/1889328830</v>
       </c>
       <c r="L64" t="str">
-        <v>i need u - BUNT.</v>
+        <v>Wouldn't Try Again - Quail P</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Outlaw</v>
+        <v>i need u</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/outlaw/1877229747</v>
+        <v>https://music.apple.com/us/song/i-need-u/1889349101</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-09</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>EI8HT</v>
+        <v>i need u - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:35</v>
+        <v>3:45</v>
       </c>
       <c r="H65" t="str">
-        <v>Shinedown</v>
+        <v>BUNT.</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/outlaw/1877229738</v>
+        <v>https://music.apple.com/us/album/i-need-u/1889349100</v>
       </c>
       <c r="L65" t="str">
-        <v>Outlaw - Shinedown</v>
+        <v>i need u - BUNT.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>A.L.O.N.E.</v>
+        <v>Outlaw</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/a-l-o-n-e/1886537119</v>
+        <v>https://music.apple.com/us/song/outlaw/1877229747</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-09</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>ADDENDUM</v>
+        <v>EI8HT</v>
       </c>
       <c r="G66" t="str">
-        <v>3:24</v>
+        <v>3:35</v>
       </c>
       <c r="H66" t="str">
-        <v>HEALTH</v>
+        <v>Shinedown</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/health/317478211</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/a-l-o-n-e/1886536873</v>
+        <v>https://music.apple.com/us/album/outlaw/1877229738</v>
       </c>
       <c r="L66" t="str">
-        <v>A.L.O.N.E. - HEALTH</v>
+        <v>Outlaw - Shinedown</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Him</v>
+        <v>A.L.O.N.E.</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/him/1887319676</v>
+        <v>https://music.apple.com/us/song/a-l-o-n-e/1886537119</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-09</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Him - Single</v>
+        <v>ADDENDUM</v>
       </c>
       <c r="G67" t="str">
-        <v>2:07</v>
+        <v>3:24</v>
       </c>
       <c r="H67" t="str">
-        <v>Sheff G</v>
+        <v>HEALTH</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/health/317478211</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/him/1887319675</v>
+        <v>https://music.apple.com/us/album/a-l-o-n-e/1886536873</v>
       </c>
       <c r="L67" t="str">
-        <v>Him - Sheff G</v>
+        <v>A.L.O.N.E. - HEALTH</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>MVP (feat. Key Glock)</v>
+        <v>Him</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/mvp-feat-key-glock/1888298376</v>
+        <v>https://music.apple.com/us/song/him/1887319676</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-09</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>AREA 41</v>
+        <v>Him - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:08</v>
+        <v>2:07</v>
       </c>
       <c r="H68" t="str">
-        <v>41</v>
+        <v>Sheff G</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/mvp-feat-key-glock/1888298368</v>
+        <v>https://music.apple.com/us/album/him/1887319675</v>
       </c>
       <c r="L68" t="str">
-        <v>MVP (feat. Key Glock) - 41</v>
+        <v>Him - Sheff G</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>S.I.M.P.L.E</v>
+        <v>MVP (feat. Key Glock)</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/s-i-m-p-l-e/1885386665</v>
+        <v>https://music.apple.com/us/song/mvp-feat-key-glock/1888298376</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-09</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>DND</v>
+        <v>AREA 41</v>
       </c>
       <c r="G69" t="str">
-        <v>2:33</v>
+        <v>3:08</v>
       </c>
       <c r="H69" t="str">
-        <v>TheARTI$t</v>
+        <v>41</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/s-i-m-p-l-e/1885386569</v>
+        <v>https://music.apple.com/us/album/mvp-feat-key-glock/1888298368</v>
       </c>
       <c r="L69" t="str">
-        <v>S.I.M.P.L.E - TheARTI$t</v>
+        <v>MVP (feat. Key Glock) - 41</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>S.I.M.P.L.E</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/at-least-shes-beautiful/1884405874</v>
+        <v>https://music.apple.com/us/song/s-i-m-p-l-e/1885386665</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-09</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>At Least She's Beautiful - Single</v>
+        <v>DND</v>
       </c>
       <c r="G70" t="str">
-        <v>2:36</v>
+        <v>2:33</v>
       </c>
       <c r="H70" t="str">
-        <v>rjtheweirdo</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/at-least-shes-beautiful/1884405873</v>
+        <v>https://music.apple.com/us/album/s-i-m-p-l-e/1885386569</v>
       </c>
       <c r="L70" t="str">
-        <v>At Least She's Beautiful - rjtheweirdo</v>
+        <v>S.I.M.P.L.E - TheARTI$t</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Hella Good (feat. Bonnie McKee)</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/hella-good-feat-bonnie-mckee/1886001675</v>
+        <v>https://music.apple.com/us/song/at-least-shes-beautiful/1884405874</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-09</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Hella Good (feat. Bonnie McKee) - Single</v>
+        <v>At Least She's Beautiful - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:45</v>
+        <v>2:36</v>
       </c>
       <c r="H71" t="str">
-        <v>Trixie Mattel</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/trixie-mattel/960467089</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/hella-good-feat-bonnie-mckee/1886001667</v>
+        <v>https://music.apple.com/us/album/at-least-shes-beautiful/1884405873</v>
       </c>
       <c r="L71" t="str">
-        <v>Hella Good (feat. Bonnie McKee) - Trixie Mattel</v>
+        <v>At Least She's Beautiful - rjtheweirdo</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Show</v>
+        <v>Hella Good (feat. Bonnie McKee)</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/the-show/1889121528</v>
+        <v>https://music.apple.com/us/song/hella-good-feat-bonnie-mckee/1886001675</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-09</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>The Show - Single</v>
+        <v>Hella Good (feat. Bonnie McKee) - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:47</v>
+        <v>3:45</v>
       </c>
       <c r="H72" t="str">
-        <v>DPR IAN</v>
+        <v>Trixie Mattel</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/dpr-ian/1500739803</v>
+        <v>https://music.apple.com/us/artist/trixie-mattel/960467089</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/the-show/1889121369</v>
+        <v>https://music.apple.com/us/album/hella-good-feat-bonnie-mckee/1886001667</v>
       </c>
       <c r="L72" t="str">
-        <v>The Show - DPR IAN</v>
+        <v>Hella Good (feat. Bonnie McKee) - Trixie Mattel</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>His Eye Is On the Sparrow</v>
+        <v>The Show</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/his-eye-is-on-the-sparrow/1880392628</v>
+        <v>https://music.apple.com/us/song/the-show/1889121528</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-09</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Grandma's Gospel Favorites</v>
+        <v>The Show - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:20</v>
+        <v>2:47</v>
       </c>
       <c r="H73" t="str">
-        <v>Jason Mraz</v>
+        <v>DPR IAN</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/jason-mraz/156987</v>
+        <v>https://music.apple.com/us/artist/dpr-ian/1500739803</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/his-eye-is-on-the-sparrow/1880392609</v>
+        <v>https://music.apple.com/us/album/the-show/1889121369</v>
       </c>
       <c r="L73" t="str">
-        <v>His Eye Is On the Sparrow - Jason Mraz</v>
+        <v>The Show - DPR IAN</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Slowly</v>
+        <v>His Eye Is On the Sparrow</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/slowly/1869140941</v>
+        <v>https://music.apple.com/us/song/his-eye-is-on-the-sparrow/1880392628</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-09</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Change Of Plans</v>
+        <v>Grandma's Gospel Favorites</v>
       </c>
       <c r="G74" t="str">
-        <v>3:11</v>
+        <v>3:20</v>
       </c>
       <c r="H74" t="str">
-        <v>49 Winchester</v>
+        <v>Jason Mraz</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
+        <v>https://music.apple.com/us/artist/jason-mraz/156987</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/slowly/1869140544</v>
+        <v>https://music.apple.com/us/album/his-eye-is-on-the-sparrow/1880392609</v>
       </c>
       <c r="L74" t="str">
-        <v>Slowly - 49 Winchester</v>
+        <v>His Eye Is On the Sparrow - Jason Mraz</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>On Our Way Along</v>
+        <v>Slowly</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/on-our-way-along/1863814124</v>
+        <v>https://music.apple.com/us/song/slowly/1869140941</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-09</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>On Our Way Along - Single</v>
+        <v>Change Of Plans</v>
       </c>
       <c r="G75" t="str">
-        <v>4:21</v>
+        <v>3:11</v>
       </c>
       <c r="H75" t="str">
-        <v>Billy Ray Cyrus</v>
+        <v>49 Winchester</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/billy-ray-cyrus/1793659079</v>
+        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/on-our-way-along/1863813853</v>
+        <v>https://music.apple.com/us/album/slowly/1869140544</v>
       </c>
       <c r="L75" t="str">
-        <v>On Our Way Along - Billy Ray Cyrus</v>
+        <v>Slowly - 49 Winchester</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>COMING OF AGE</v>
+        <v>On Our Way Along</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/coming-of-age/1882886175</v>
+        <v>https://music.apple.com/us/song/on-our-way-along/1863814124</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-09</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>COMING OF AGE - Single</v>
+        <v>On Our Way Along - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>4:08</v>
+        <v>4:21</v>
       </c>
       <c r="H76" t="str">
-        <v>METTE</v>
+        <v>Billy Ray Cyrus</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/mette/1553768125</v>
+        <v>https://music.apple.com/us/artist/billy-ray-cyrus/1793659079</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/coming-of-age/1882886174</v>
+        <v>https://music.apple.com/us/album/on-our-way-along/1863813853</v>
       </c>
       <c r="L76" t="str">
-        <v>COMING OF AGE - METTE</v>
+        <v>On Our Way Along - Billy Ray Cyrus</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>the man with money in his hands</v>
+        <v>COMING OF AGE</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/the-man-with-money-in-his-hands/1887707057</v>
+        <v>https://music.apple.com/us/song/coming-of-age/1882886175</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-09</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>the man with money in his hands - Single</v>
+        <v>COMING OF AGE - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:57</v>
+        <v>4:08</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie Mazin</v>
+        <v>METTE</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
+        <v>https://music.apple.com/us/artist/mette/1553768125</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/the-man-with-money-in-his-hands/1887707053</v>
+        <v>https://music.apple.com/us/album/coming-of-age/1882886174</v>
       </c>
       <c r="L77" t="str">
-        <v>the man with money in his hands - Jessie Mazin</v>
+        <v>COMING OF AGE - METTE</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>WRANGLER</v>
+        <v>the man with money in his hands</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/wrangler/1876267962</v>
+        <v>https://music.apple.com/us/song/the-man-with-money-in-his-hands/1887707057</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-09</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>WHAT CAN I TELL U</v>
+        <v>the man with money in his hands - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:05</v>
+        <v>2:57</v>
       </c>
       <c r="H78" t="str">
-        <v>Claudia Valentina</v>
+        <v>Jessie Mazin</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/wrangler/1876267654</v>
+        <v>https://music.apple.com/us/album/the-man-with-money-in-his-hands/1887707053</v>
       </c>
       <c r="L78" t="str">
-        <v>WRANGLER - Claudia Valentina</v>
+        <v>the man with money in his hands - Jessie Mazin</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Rydly</v>
+        <v>WRANGLER</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/rydly/1878477155</v>
+        <v>https://music.apple.com/us/song/wrangler/1876267962</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-09</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>We Are Friends, Vol. 12 (Disk 2)</v>
+        <v>WHAT CAN I TELL U</v>
       </c>
       <c r="G79" t="str">
-        <v>6:52</v>
+        <v>2:05</v>
       </c>
       <c r="H79" t="str">
-        <v>deadmau5</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/rydly/1878476797</v>
+        <v>https://music.apple.com/us/album/wrangler/1876267654</v>
       </c>
       <c r="L79" t="str">
-        <v>Rydly - deadmau5</v>
+        <v>WRANGLER - Claudia Valentina</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>all the time</v>
+        <v>Rydly</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1874100418</v>
+        <v>https://music.apple.com/us/song/rydly/1878477155</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-09</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>ARCADE</v>
+        <v>We Are Friends, Vol. 12 (Disk 2)</v>
       </c>
       <c r="G80" t="str">
-        <v>3:01</v>
+        <v>6:52</v>
       </c>
       <c r="H80" t="str">
-        <v>Deb Never</v>
+        <v>deadmau5</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1874100412</v>
+        <v>https://music.apple.com/us/album/rydly/1878476797</v>
       </c>
       <c r="L80" t="str">
-        <v>all the time - Deb Never</v>
+        <v>Rydly - deadmau5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Misery</v>
+        <v>all the time</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/misery/1888294484</v>
+        <v>https://music.apple.com/us/song/all-the-time/1874100418</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-09</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Misery - Single</v>
+        <v>ARCADE</v>
       </c>
       <c r="G81" t="str">
-        <v>2:55</v>
+        <v>3:01</v>
       </c>
       <c r="H81" t="str">
-        <v>Alex Sampson</v>
+        <v>Deb Never</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/alex-sampson/1486112083</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/misery/1888294483</v>
+        <v>https://music.apple.com/us/album/all-the-time/1874100412</v>
       </c>
       <c r="L81" t="str">
-        <v>Misery - Alex Sampson</v>
+        <v>all the time - Deb Never</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Don't Fall</v>
+        <v>Misery</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/dont-fall/1884794995</v>
+        <v>https://music.apple.com/us/song/misery/1888294484</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-09</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Games - EP</v>
+        <v>Misery - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>4:20</v>
+        <v>2:55</v>
       </c>
       <c r="H82" t="str">
-        <v>Common People</v>
+        <v>Alex Sampson</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/alex-sampson/1486112083</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/dont-fall/1884794990</v>
+        <v>https://music.apple.com/us/album/misery/1888294483</v>
       </c>
       <c r="L82" t="str">
-        <v>Don't Fall - Common People</v>
+        <v>Misery - Alex Sampson</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Alternate Ending</v>
+        <v>Don't Fall</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/alternate-ending/1886010374</v>
+        <v>https://music.apple.com/us/song/dont-fall/1884794995</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-09</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Alternate Ending - Single</v>
+        <v>Games - EP</v>
       </c>
       <c r="G83" t="str">
-        <v>3:10</v>
+        <v>4:20</v>
       </c>
       <c r="H83" t="str">
-        <v>Thelma &amp; James</v>
+        <v>Common People</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/thelma-james/1787091600</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/alternate-ending/1886010053</v>
+        <v>https://music.apple.com/us/album/dont-fall/1884794990</v>
       </c>
       <c r="L83" t="str">
-        <v>Alternate Ending - Thelma &amp; James</v>
+        <v>Don't Fall - Common People</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>LuCkY</v>
+        <v>Alternate Ending</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/lucky/1888001208</v>
+        <v>https://music.apple.com/us/song/alternate-ending/1886010374</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-09</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>MOEWYA</v>
+        <v>Alternate Ending - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:17</v>
+        <v>3:10</v>
       </c>
       <c r="H84" t="str">
-        <v>MoeIsBetter</v>
+        <v>Thelma &amp; James</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/moeisbetter/1762833637</v>
+        <v>https://music.apple.com/us/artist/thelma-james/1787091600</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/lucky/1888001204</v>
+        <v>https://music.apple.com/us/album/alternate-ending/1886010053</v>
       </c>
       <c r="L84" t="str">
-        <v>LuCkY - MoeIsBetter</v>
+        <v>Alternate Ending - Thelma &amp; James</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Mutual</v>
+        <v>LuCkY</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/mutual/1882922798</v>
+        <v>https://music.apple.com/us/song/lucky/1888001208</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-09</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Mutual - Single</v>
+        <v>MOEWYA</v>
       </c>
       <c r="G85" t="str">
-        <v>3:49</v>
+        <v>2:17</v>
       </c>
       <c r="H85" t="str">
-        <v>PJ Morton</v>
+        <v>MoeIsBetter</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/pj-morton/44719201</v>
+        <v>https://music.apple.com/us/artist/moeisbetter/1762833637</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/mutual/1882922794</v>
+        <v>https://music.apple.com/us/album/lucky/1888001204</v>
       </c>
       <c r="L85" t="str">
-        <v>Mutual - PJ Morton</v>
+        <v>LuCkY - MoeIsBetter</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Waiting On</v>
+        <v>Mutual</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/waiting-on/1883846539</v>
+        <v>https://music.apple.com/us/song/mutual/1882922798</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-09</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Waiting On - Single</v>
+        <v>Mutual - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:11</v>
+        <v>3:49</v>
       </c>
       <c r="H86" t="str">
-        <v>Tniyah</v>
+        <v>PJ Morton</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/tniyah/513967453</v>
+        <v>https://music.apple.com/us/artist/pj-morton/44719201</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/waiting-on/1883846538</v>
+        <v>https://music.apple.com/us/album/mutual/1882922794</v>
       </c>
       <c r="L86" t="str">
-        <v>Waiting On - Tniyah</v>
+        <v>Mutual - PJ Morton</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>En La Montaña</v>
+        <v>Waiting On</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/en-la-monta%C3%B1a/1884092212</v>
+        <v>https://music.apple.com/us/song/waiting-on/1883846539</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-09</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>En La Montaña - Single</v>
+        <v>Waiting On - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:23</v>
+        <v>3:11</v>
       </c>
       <c r="H87" t="str">
-        <v>Nueva H</v>
+        <v>Tniyah</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/tniyah/513967453</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/en-la-monta%C3%B1a/1884092207</v>
+        <v>https://music.apple.com/us/album/waiting-on/1883846538</v>
       </c>
       <c r="L87" t="str">
-        <v>En La Montaña - Nueva H</v>
+        <v>Waiting On - Tniyah</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Falling Short</v>
+        <v>En La Montaña</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/falling-short/1884803703</v>
+        <v>https://music.apple.com/us/song/en-la-monta%C3%B1a/1884092212</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-09</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Falling Short - Single</v>
+        <v>En La Montaña - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:05</v>
+        <v>2:23</v>
       </c>
       <c r="H88" t="str">
-        <v>Hudson Macready</v>
+        <v>Nueva H</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/hudson-macready/1534530042</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/falling-short/1884803515</v>
+        <v>https://music.apple.com/us/album/en-la-monta%C3%B1a/1884092207</v>
       </c>
       <c r="L88" t="str">
-        <v>Falling Short - Hudson Macready</v>
+        <v>En La Montaña - Nueva H</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>When You Give It Up</v>
+        <v>Falling Short</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/when-you-give-it-up/1879883866</v>
+        <v>https://music.apple.com/us/song/falling-short/1884803703</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-09</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>When You Give It Up - Single</v>
+        <v>Falling Short - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>2:42</v>
+        <v>3:05</v>
       </c>
       <c r="H89" t="str">
-        <v>Chelsea Plank</v>
+        <v>Hudson Macready</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
+        <v>https://music.apple.com/us/artist/hudson-macready/1534530042</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/when-you-give-it-up/1879883863</v>
+        <v>https://music.apple.com/us/album/falling-short/1884803515</v>
       </c>
       <c r="L89" t="str">
-        <v>When You Give It Up - Chelsea Plank</v>
+        <v>Falling Short - Hudson Macready</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Wasted</v>
+        <v>When You Give It Up</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/wasted/1885578001</v>
+        <v>https://music.apple.com/us/song/when-you-give-it-up/1879883866</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-09</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Wasted - Single</v>
+        <v>When You Give It Up - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:18</v>
+        <v>2:42</v>
       </c>
       <c r="H90" t="str">
-        <v>Highly Suspect</v>
+        <v>Chelsea Plank</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/highly-suspect/419913603</v>
+        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/wasted/1885578000</v>
+        <v>https://music.apple.com/us/album/when-you-give-it-up/1879883863</v>
       </c>
       <c r="L90" t="str">
-        <v>Wasted - Highly Suspect</v>
+        <v>When You Give It Up - Chelsea Plank</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Burn</v>
+        <v>Wasted</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/burn/1883195616</v>
+        <v>https://music.apple.com/us/song/wasted/1885578001</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-09</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Burn - Single</v>
+        <v>Wasted - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>2:56</v>
+        <v>3:18</v>
       </c>
       <c r="H91" t="str">
-        <v>Cold Court</v>
+        <v>Highly Suspect</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/cold-court/1809708831</v>
+        <v>https://music.apple.com/us/artist/highly-suspect/419913603</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/burn/1883195615</v>
+        <v>https://music.apple.com/us/album/wasted/1885578000</v>
       </c>
       <c r="L91" t="str">
-        <v>Burn - Cold Court</v>
+        <v>Wasted - Highly Suspect</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Smash</v>
+        <v>Burn</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/smash/1884655608</v>
+        <v>https://music.apple.com/us/song/burn/1883195616</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-09</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Eternal BAM Nation</v>
+        <v>Burn - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>2:27</v>
+        <v>2:56</v>
       </c>
       <c r="H92" t="str">
-        <v>Born At Midnite</v>
+        <v>Cold Court</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/born-at-midnite/1497209280</v>
+        <v>https://music.apple.com/us/artist/cold-court/1809708831</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/smash/1884655462</v>
+        <v>https://music.apple.com/us/album/burn/1883195615</v>
       </c>
       <c r="L92" t="str">
-        <v>Smash - Born At Midnite</v>
+        <v>Burn - Cold Court</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Smile</v>
+        <v>Smash</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/smile/1859619683</v>
+        <v>https://music.apple.com/us/song/smash/1884655608</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-09</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Birding</v>
+        <v>Eternal BAM Nation</v>
       </c>
       <c r="G93" t="str">
-        <v>5:09</v>
+        <v>2:27</v>
       </c>
       <c r="H93" t="str">
-        <v>deary</v>
+        <v>Born At Midnite</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/deary/1641536096</v>
+        <v>https://music.apple.com/us/artist/born-at-midnite/1497209280</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/smile/1859619407</v>
+        <v>https://music.apple.com/us/album/smash/1884655462</v>
       </c>
       <c r="L93" t="str">
-        <v>Smile - deary</v>
+        <v>Smash - Born At Midnite</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Eshi</v>
+        <v>Smile</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/eshi/1880700566</v>
+        <v>https://music.apple.com/us/song/smile/1859619683</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-09</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Zero</v>
+        <v>Birding</v>
       </c>
       <c r="G94" t="str">
-        <v>3:12</v>
+        <v>5:09</v>
       </c>
       <c r="H94" t="str">
-        <v>Alewya</v>
+        <v>deary</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/alewya/1450971317</v>
+        <v>https://music.apple.com/us/artist/deary/1641536096</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/eshi/1880699673</v>
+        <v>https://music.apple.com/us/album/smile/1859619407</v>
       </c>
       <c r="L94" t="str">
-        <v>Eshi - Alewya</v>
+        <v>Smile - deary</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>NO HOMEGIRLS</v>
+        <v>Eshi</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/no-homegirls/1886801763</v>
+        <v>https://music.apple.com/us/song/eshi/1880700566</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-09</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>NO HOMEGIRLS - Single</v>
+        <v>Zero</v>
       </c>
       <c r="G95" t="str">
-        <v>2:05</v>
+        <v>3:12</v>
       </c>
       <c r="H95" t="str">
-        <v>BBYKOBE</v>
+        <v>Alewya</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/bbykobe/1693491560</v>
+        <v>https://music.apple.com/us/artist/alewya/1450971317</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/no-homegirls/1886801762</v>
+        <v>https://music.apple.com/us/album/eshi/1880699673</v>
       </c>
       <c r="L95" t="str">
-        <v>NO HOMEGIRLS - BBYKOBE</v>
+        <v>Eshi - Alewya</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>I Want You Back</v>
+        <v>NO HOMEGIRLS</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/i-want-you-back/1889281139</v>
+        <v>https://music.apple.com/us/song/no-homegirls/1886801763</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-09</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>I Want You Back - Single</v>
+        <v>NO HOMEGIRLS - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>3:18</v>
+        <v>2:05</v>
       </c>
       <c r="H96" t="str">
-        <v>Johnny Venus</v>
+        <v>BBYKOBE</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/johnny-venus/1777129720</v>
+        <v>https://music.apple.com/us/artist/bbykobe/1693491560</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/i-want-you-back/1889281136</v>
+        <v>https://music.apple.com/us/album/no-homegirls/1886801762</v>
       </c>
       <c r="L96" t="str">
-        <v>I Want You Back - Johnny Venus</v>
+        <v>NO HOMEGIRLS - BBYKOBE</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Needed You</v>
+        <v>I Want You Back</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/needed-you/1887702402</v>
+        <v>https://music.apple.com/us/song/i-want-you-back/1889281139</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-09</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Active Child</v>
+        <v>I Want You Back - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>3:17</v>
+        <v>3:18</v>
       </c>
       <c r="H97" t="str">
-        <v>Active Child</v>
+        <v>Johnny Venus</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/johnny-venus/1777129720</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/needed-you/1887701924</v>
+        <v>https://music.apple.com/us/album/i-want-you-back/1889281136</v>
       </c>
       <c r="L97" t="str">
-        <v>Needed You - Active Child</v>
+        <v>I Want You Back - Johnny Venus</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Finish Line</v>
+        <v>Needed You</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/finish-line/1887371855</v>
+        <v>https://music.apple.com/us/song/needed-you/1887702402</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-09</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Finish Line - Single</v>
+        <v>Active Child</v>
       </c>
       <c r="G98" t="str">
-        <v>3:18</v>
+        <v>3:17</v>
       </c>
       <c r="H98" t="str">
-        <v>Ally Salort</v>
+        <v>Active Child</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/finish-line/1887371854</v>
+        <v>https://music.apple.com/us/album/needed-you/1887701924</v>
       </c>
       <c r="L98" t="str">
-        <v>Finish Line - Ally Salort</v>
+        <v>Needed You - Active Child</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Daredevil</v>
+        <v>Finish Line</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/daredevil/1883231048</v>
+        <v>https://music.apple.com/us/song/finish-line/1887371855</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-09</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Daredevil - Single</v>
+        <v>Finish Line - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>4:16</v>
+        <v>3:18</v>
       </c>
       <c r="H99" t="str">
-        <v>Zach Hood</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/zach-hood/1518857330</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/daredevil/1883231047</v>
+        <v>https://music.apple.com/us/album/finish-line/1887371854</v>
       </c>
       <c r="L99" t="str">
-        <v>Daredevil - Zach Hood</v>
+        <v>Finish Line - Ally Salort</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Asleep On The Killing Floor</v>
+        <v>Daredevil</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/asleep-on-the-killing-floor/1869086163</v>
+        <v>https://music.apple.com/us/song/daredevil/1883231048</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-09</v>
@@ -4175,36 +4175,36 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Daredevil - Single</v>
       </c>
       <c r="G100" t="str">
-        <v>4:08</v>
+        <v>4:16</v>
       </c>
       <c r="H100" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Zach Hood</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/zach-hood/1518857330</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/asleep-on-the-killing-floor/1869085524</v>
+        <v>https://music.apple.com/us/album/daredevil/1883231047</v>
       </c>
       <c r="L100" t="str">
-        <v>Asleep On The Killing Floor - Corrosion of Conformity</v>
+        <v>Daredevil - Zach Hood</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>You Bastard</v>
+        <v>Asleep On The Killing Floor</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/you-bastard/1871211807</v>
+        <v>https://music.apple.com/us/song/asleep-on-the-killing-floor/1869086163</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-09</v>
@@ -4213,36 +4213,36 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>Neverending</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G101" t="str">
-        <v>4:19</v>
+        <v>4:08</v>
       </c>
       <c r="H101" t="str">
-        <v>Monolord</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/you-bastard/1871211801</v>
+        <v>https://music.apple.com/us/album/asleep-on-the-killing-floor/1869085524</v>
       </c>
       <c r="L101" t="str">
-        <v>You Bastard - Monolord</v>
+        <v>Asleep On The Killing Floor - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Vanilla Latte</v>
+        <v>You Bastard</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/vanilla-latte/1884524943</v>
+        <v>https://music.apple.com/us/song/you-bastard/1871211807</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-09</v>
@@ -4251,68 +4251,106 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Vanilla Latte - EP</v>
+        <v>Neverending</v>
       </c>
       <c r="G102" t="str">
-        <v>2:24</v>
+        <v>4:19</v>
       </c>
       <c r="H102" t="str">
-        <v>The Barbarians of California</v>
+        <v>Monolord</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/vanilla-latte/1884524941</v>
+        <v>https://music.apple.com/us/album/you-bastard/1871211801</v>
       </c>
       <c r="L102" t="str">
-        <v>Vanilla Latte - The Barbarians of California</v>
+        <v>You Bastard - Monolord</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
+        <v>Vanilla Latte</v>
+      </c>
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
+        <v>https://music.apple.com/us/song/vanilla-latte/1884524943</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v>Vanilla Latte - EP</v>
+      </c>
+      <c r="G103" t="str">
+        <v>2:24</v>
+      </c>
+      <c r="H103" t="str">
+        <v>The Barbarians of California</v>
+      </c>
+      <c r="I103" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J103" t="str">
+        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
+      </c>
+      <c r="K103" t="str">
+        <v>https://music.apple.com/us/album/vanilla-latte/1884524941</v>
+      </c>
+      <c r="L103" t="str">
+        <v>Vanilla Latte - The Barbarians of California</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
         <v>Nostalgia Kills</v>
       </c>
-      <c r="B103" t="str">
-        <v/>
-      </c>
-      <c r="C103" t="str">
+      <c r="B104" t="str">
+        <v/>
+      </c>
+      <c r="C104" t="str">
         <v>https://music.apple.com/us/song/nostalgia-kills/1887961043</v>
       </c>
-      <c r="D103" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
+      <c r="D104" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
         <v>Nostalgia Kills - Single</v>
       </c>
-      <c r="G103" t="str">
+      <c r="G104" t="str">
         <v>3:03</v>
       </c>
-      <c r="H103" t="str">
+      <c r="H104" t="str">
         <v>Static Dress</v>
       </c>
-      <c r="I103" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J103" t="str">
+      <c r="I104" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J104" t="str">
         <v>https://music.apple.com/us/artist/static-dress/1476714067</v>
       </c>
-      <c r="K103" t="str">
+      <c r="K104" t="str">
         <v>https://music.apple.com/us/album/nostalgia-kills/1887961038</v>
       </c>
-      <c r="L103" t="str">
+      <c r="L104" t="str">
         <v>Nostalgia Kills - Static Dress</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L104"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L95"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,344 +436,344 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>PINKY UP</v>
+        <v>Bottom Of Your Boots</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
+        <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>PINKY UP - Single</v>
+        <v>Dandelion</v>
       </c>
       <c r="G2" t="str">
-        <v>2:11</v>
+        <v>3:19</v>
       </c>
       <c r="H2" t="str">
-        <v>KATSEYE</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/katseye/1754284416</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/pinky-up/1888235065</v>
+        <v>https://music.apple.com/us/album/bottom-of-your-boots/1869436835</v>
       </c>
       <c r="L2" t="str">
-        <v>PINKY UP - KATSEYE</v>
+        <v>Bottom Of Your Boots - Ella Langley</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The More I Hope</v>
+        <v>Runway</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/the-more-i-hope/1882826389</v>
+        <v>https://music.apple.com/us/song/runway/1891472591</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Broken View</v>
+        <v>Runway - Single</v>
       </c>
       <c r="G3" t="str">
-        <v>4:06</v>
+        <v>2:51</v>
       </c>
       <c r="H3" t="str">
-        <v>Sam Barber</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/the-more-i-hope/1882826154</v>
+        <v>https://music.apple.com/us/album/runway/1891472590</v>
       </c>
       <c r="L3" t="str">
-        <v>The More I Hope - Sam Barber</v>
+        <v>Runway - Lady Gaga</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>the van</v>
+        <v>Back and Forth (feat. Missy Elliott)</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/the-van/1872842315</v>
+        <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Kehlani</v>
       </c>
       <c r="G4" t="str">
-        <v>2:58</v>
+        <v>3:34</v>
       </c>
       <c r="H4" t="str">
-        <v>Bleachers</v>
+        <v>Kehlani</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/the-van/1872842313</v>
+        <v>https://music.apple.com/us/album/back-and-forth-feat-missy-elliott/1885055310</v>
       </c>
       <c r="L4" t="str">
-        <v>the van - Bleachers</v>
+        <v>Back and Forth (feat. Missy Elliott) - Kehlani</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Reply To This</v>
+        <v>Mr. Know It All</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/reply-to-this/1888625007</v>
+        <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Whatever's Clever! (Expanded)</v>
+        <v>Mr. Know It All - Single</v>
       </c>
       <c r="G5" t="str">
-        <v>2:57</v>
+        <v>3:18</v>
       </c>
       <c r="H5" t="str">
-        <v>Charlie Puth</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/teddy-swims/1462541757</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/reply-to-this/1888624679</v>
+        <v>https://music.apple.com/us/album/mr-know-it-all/1889361601</v>
       </c>
       <c r="L5" t="str">
-        <v>Reply To This - Charlie Puth</v>
+        <v>Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Funny Friends</v>
+        <v>Bad Angel</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/funny-friends/1861531673</v>
+        <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Distracted</v>
+        <v>Bad Angel - Single</v>
       </c>
       <c r="G6" t="str">
-        <v>2:35</v>
+        <v>2:33</v>
       </c>
       <c r="H6" t="str">
-        <v>Thundercat</v>
+        <v>Anyma</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/funny-friends/1861531667</v>
+        <v>https://music.apple.com/us/album/bad-angel/1889611955</v>
       </c>
       <c r="L6" t="str">
-        <v>Funny Friends - Thundercat</v>
+        <v>Bad Angel - Anyma</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Turtleneck</v>
+        <v>Step (feat. Swizz Beatz)</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/turtleneck/1890056028</v>
+        <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Turtleneck - Single</v>
+        <v>10 Til' Midnight</v>
       </c>
       <c r="G7" t="str">
-        <v>1:35</v>
+        <v>3:34</v>
       </c>
       <c r="H7" t="str">
-        <v>Tank</v>
+        <v>Snoop Dogg</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/tank/3293014</v>
+        <v>https://music.apple.com/us/artist/snoop-dogg/21769</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/turtleneck/1890056027</v>
+        <v>https://music.apple.com/us/album/step-feat-swizz-beatz/1886977935</v>
       </c>
       <c r="L7" t="str">
-        <v>Turtleneck - Tank</v>
+        <v>Step (feat. Swizz Beatz) - Snoop Dogg</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>G.O.D. And The Broken Ribs</v>
+        <v>Sweet Hallelujah</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/g-o-d-and-the-broken-ribs/1883199709</v>
+        <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>G.O.D. And The Broken Ribs / Derecho Demonico - Single</v>
+        <v>Sweet Hallelujah - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>3:43</v>
+        <v>3:02</v>
       </c>
       <c r="H8" t="str">
-        <v>Jack White</v>
+        <v>Royel Otis</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/jack-white/826980</v>
+        <v>https://music.apple.com/us/artist/royel-otis/1537647213</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/g-o-d-and-the-broken-ribs/1883199707</v>
+        <v>https://music.apple.com/us/album/sweet-hallelujah/1886800353</v>
       </c>
       <c r="L8" t="str">
-        <v>G.O.D. And The Broken Ribs - Jack White</v>
+        <v>Sweet Hallelujah - Royel Otis</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>In A Life</v>
+        <v>Beauty Pageant</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/in-a-life/1888147404</v>
+        <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Easter Lily EP</v>
+        <v>Cruel World</v>
       </c>
       <c r="G9" t="str">
-        <v>4:33</v>
+        <v>3:15</v>
       </c>
       <c r="H9" t="str">
-        <v>U2</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/u2/78500</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/in-a-life/1888147400</v>
+        <v>https://music.apple.com/us/album/beauty-pageant/1859629846</v>
       </c>
       <c r="L9" t="str">
-        <v>In A Life - U2</v>
+        <v>Beauty Pageant - Holly Humberstone</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Buy Me A Car</v>
+        <v>PINKY UP</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/buy-me-a-car/1887659688</v>
+        <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Buy Me A Car - Single</v>
+        <v>PINKY UP - Single</v>
       </c>
       <c r="G10" t="str">
-        <v>3:29</v>
+        <v>2:11</v>
       </c>
       <c r="H10" t="str">
-        <v>Presley Regier</v>
+        <v>KATSEYE</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/katseye/1754284416</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/buy-me-a-car/1887659405</v>
+        <v>https://music.apple.com/us/album/pinky-up/1888235065</v>
       </c>
       <c r="L10" t="str">
-        <v>Buy Me A Car - Presley Regier</v>
+        <v>PINKY UP - KATSEYE</v>
       </c>
     </row>
     <row r="11">
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -816,3541 +816,3199 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CHICA 305</v>
+        <v>Ember</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/chica-305/1888292975</v>
+        <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>CHICA 305 - Single</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G12" t="str">
-        <v>3:08</v>
+        <v>3:25</v>
       </c>
       <c r="H12" t="str">
-        <v>John Summit</v>
+        <v>Iceage</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/chica-305/1888292973</v>
+        <v>https://music.apple.com/us/album/ember/1880484160</v>
       </c>
       <c r="L12" t="str">
-        <v>CHICA 305 - John Summit</v>
+        <v>Ember - Iceage</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Ember</v>
+        <v>Turnaround</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/ember/1880484164</v>
+        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>Turnaround / I'm Hooked - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>3:25</v>
+        <v>3:14</v>
       </c>
       <c r="H13" t="str">
-        <v>Iceage</v>
+        <v>54 Ultra</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/ember/1880484160</v>
+        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
       </c>
       <c r="L13" t="str">
-        <v>Ember - Iceage</v>
+        <v>Turnaround - 54 Ultra</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Jet Lag Mouth</v>
+        <v>Madwoman</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/jet-lag-mouth/1885012928</v>
+        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Jet Lag Mouth - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G14" t="str">
-        <v>2:32</v>
+        <v>3:59</v>
       </c>
       <c r="H14" t="str">
-        <v>In Color</v>
+        <v>Laufey</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/jet-lag-mouth/1885012927</v>
+        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
       </c>
       <c r="L14" t="str">
-        <v>Jet Lag Mouth - In Color</v>
+        <v>Madwoman - Laufey</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Turnaround</v>
+        <v>Come Clean (Mine)</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
+        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Turnaround / I'm Hooked - Single</v>
+        <v>Come Clean (Mine) - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>3:14</v>
+        <v>3:33</v>
       </c>
       <c r="H15" t="str">
-        <v>54 Ultra</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
+        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
       </c>
       <c r="L15" t="str">
-        <v>Turnaround - 54 Ultra</v>
+        <v>Come Clean (Mine) - Hilary Duff</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Home on the Range</v>
+        <v>One of Them</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/home-on-the-range/1870867490</v>
+        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>One of Them - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>1:37</v>
+        <v>3:24</v>
       </c>
       <c r="H16" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>DJ Khaled</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/home-on-the-range/1870867411</v>
+        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
       </c>
       <c r="L16" t="str">
-        <v>Home on the Range - Earl Sweatshirt</v>
+        <v>One of Them - DJ Khaled</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Back Home</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/back-home/1870867424</v>
+        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="G17" t="str">
-        <v>1:36</v>
+        <v>2:49</v>
       </c>
       <c r="H17" t="str">
-        <v>MIKE</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/back-home/1870867411</v>
+        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
       </c>
       <c r="L17" t="str">
-        <v>Back Home - MIKE</v>
+        <v>Chicken Talkin Bastard - Bossman Dlow</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Reputation</v>
+        <v>stuck</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/reputation/1888615203</v>
+        <v>https://music.apple.com/us/song/stuck/1875303118</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Reputation / Bobby - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G18" t="str">
-        <v>3:55</v>
+        <v>2:41</v>
       </c>
       <c r="H18" t="str">
-        <v>Ravyn Lenae</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/reputation/1888615202</v>
+        <v>https://music.apple.com/us/album/stuck/1875302904</v>
       </c>
       <c r="L18" t="str">
-        <v>Reputation - Ravyn Lenae</v>
+        <v>stuck - Saint Harison</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>MURAL</v>
+        <v>De Lejitos</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/mural/1885914724</v>
+        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>De Lejitos - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:26</v>
+        <v>3:27</v>
       </c>
       <c r="H19" t="str">
-        <v>Swae Lee</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/mural/1885914714</v>
+        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
       </c>
       <c r="L19" t="str">
-        <v>MURAL - Swae Lee</v>
+        <v>De Lejitos - Jay Wheeler</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Business &amp; Personal (second half)</v>
+        <v>Echo</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/business-personal-second-half/1889934787</v>
+        <v>https://music.apple.com/us/song/echo/1891104992</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Business &amp; Personal - Single</v>
+        <v>Echo - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>2:19</v>
+        <v>3:39</v>
       </c>
       <c r="H20" t="str">
-        <v>Latto</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/latto/419799506</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/business-personal-second-half/1889934634</v>
+        <v>https://music.apple.com/us/album/echo/1891104991</v>
       </c>
       <c r="L20" t="str">
-        <v>Business &amp; Personal (second half) - Latto</v>
+        <v>Echo - The Chainsmokers</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Beams</v>
+        <v>Where We Go</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/beams/1862570896</v>
+        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Where We Go - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>3:39</v>
+        <v>3:16</v>
       </c>
       <c r="H21" t="str">
-        <v>Arlo Parks</v>
+        <v>Marshmello</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/beams/1862570378</v>
+        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
       </c>
       <c r="L21" t="str">
-        <v>Beams - Arlo Parks</v>
+        <v>Where We Go - Marshmello</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Hysteria</v>
+        <v>Te hacen falta dos</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/hysteria/1887407036</v>
+        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Hysteria - Single</v>
+        <v>Apambichao</v>
       </c>
       <c r="G22" t="str">
-        <v>2:23</v>
+        <v>2:41</v>
       </c>
       <c r="H22" t="str">
-        <v>Bebe Rexha</v>
+        <v>Manuel Turizo</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
+        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/hysteria/1887407035</v>
+        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
       </c>
       <c r="L22" t="str">
-        <v>Hysteria - Bebe Rexha</v>
+        <v>Te hacen falta dos - Manuel Turizo</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Need Your Love</v>
+        <v>Of All People</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/need-your-love/1884740423</v>
+        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Need Your Love - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G23" t="str">
-        <v>3:58</v>
+        <v>2:34</v>
       </c>
       <c r="H23" t="str">
-        <v>OneRepublic</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/need-your-love/1884740422</v>
+        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
       </c>
       <c r="L23" t="str">
-        <v>Need Your Love - OneRepublic</v>
+        <v>Of All People - Foo Fighters</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>My Mouth Is Lonely For You (from Mother Mary)</v>
+        <v>idea 1</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/my-mouth-is-lonely-for-you-from-mother-mary/1886744205</v>
+        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>My Mouth Is Lonely For You (from Mother Mary) - Single</v>
+        <v>idea 1 - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>4:04</v>
+        <v>3:25</v>
       </c>
       <c r="H24" t="str">
-        <v>Anne Hathaway</v>
+        <v>Kelela</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/my-mouth-is-lonely-for-you-from-mother-mary/1886744203</v>
+        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
       </c>
       <c r="L24" t="str">
-        <v>My Mouth Is Lonely For You (from Mother Mary) - Anne Hathaway</v>
+        <v>idea 1 - Kelela</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SORRY! CRASH!</v>
+        <v>Attitude</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/sorry-crash/1886485698</v>
+        <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>Sweat</v>
       </c>
       <c r="G25" t="str">
-        <v>3:09</v>
+        <v>3:13</v>
       </c>
       <c r="H25" t="str">
-        <v>Ecca Vandal</v>
+        <v>Melanie C</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/sorry-crash/1886485694</v>
+        <v>https://music.apple.com/us/album/attitude/1840516706</v>
       </c>
       <c r="L25" t="str">
-        <v>SORRY! CRASH! - Ecca Vandal</v>
+        <v>Attitude - Melanie C</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Shine Again</v>
+        <v>Carrie Bradshaw</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/shine-again/1887991690</v>
+        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Shine Again - Single</v>
+        <v>Carrie Bradshaw - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>4:05</v>
+        <v>2:54</v>
       </c>
       <c r="H26" t="str">
-        <v>Weezer</v>
+        <v>Kylie Cantrall</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/shine-again/1887991688</v>
+        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
       </c>
       <c r="L26" t="str">
-        <v>Shine Again - Weezer</v>
+        <v>Carrie Bradshaw - Kylie Cantrall</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Choose Love</v>
+        <v>Work</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/choose-love/1877910665</v>
+        <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Long Long Road</v>
+        <v>Work - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>3:54</v>
+        <v>2:51</v>
       </c>
       <c r="H27" t="str">
-        <v>Ringo Starr</v>
+        <v>Pitbull</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/choose-love/1877910655</v>
+        <v>https://music.apple.com/us/album/work/1885916578</v>
       </c>
       <c r="L27" t="str">
-        <v>Choose Love - Ringo Starr</v>
+        <v>Work - Pitbull</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>BABYRECORDS.</v>
+        <v>Obvious</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/babyrecords/1888590545</v>
+        <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>BABYRECORDS. - Single</v>
+        <v>Obvious - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>2:29</v>
+        <v>3:05</v>
       </c>
       <c r="H28" t="str">
-        <v>Álvaro Díaz</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/babyrecords/1888590544</v>
+        <v>https://music.apple.com/us/album/obvious/1891759134</v>
       </c>
       <c r="L28" t="str">
-        <v>BABYRECORDS. - Álvaro Díaz</v>
+        <v>Obvious - Chris Brown</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Paperbag Boy</v>
+        <v>As Time Goes By</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/paperbag-boy/1889345415</v>
+        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Paperbag Boy - Single</v>
+        <v>CINEMATIC</v>
       </c>
       <c r="G29" t="str">
-        <v>3:11</v>
+        <v>5:06</v>
       </c>
       <c r="H29" t="str">
-        <v>Trippie Redd</v>
+        <v>Josh Groban</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/trippie-redd/1203172438</v>
+        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/paperbag-boy/1889345414</v>
+        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
       </c>
       <c r="L29" t="str">
-        <v>Paperbag Boy - Trippie Redd</v>
+        <v>As Time Goes By - Josh Groban</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>I AM</v>
+        <v>My Mess</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/i-am/1880890454</v>
+        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>CLARITY OF MIND</v>
+        <v>My Mess, My Heart, My Life.</v>
       </c>
       <c r="G30" t="str">
-        <v>3:12</v>
+        <v>3:11</v>
       </c>
       <c r="H30" t="str">
-        <v>OMAH LAY</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/i-am/1880890112</v>
+        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
       </c>
       <c r="L30" t="str">
-        <v>I AM - OMAH LAY</v>
+        <v>My Mess - Myles Smith</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Want Love</v>
+        <v>Going Shopping</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/want-love/1886384365</v>
+        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Want Love - Single</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G31" t="str">
-        <v>3:20</v>
+        <v>4:21</v>
       </c>
       <c r="H31" t="str">
-        <v>Mary J. Blige</v>
+        <v>The Strokes</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/want-love/1886384355</v>
+        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
       </c>
       <c r="L31" t="str">
-        <v>Want Love - Mary J. Blige</v>
+        <v>Going Shopping - The Strokes</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Live, Love, Learn</v>
+        <v>Choka Choka</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/live-love-learn/1884749128</v>
+        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Live, Love, Learn - Single</v>
+        <v>Choka Choka - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>4:19</v>
+        <v>2:11</v>
       </c>
       <c r="H32" t="str">
-        <v>Estelle</v>
+        <v>Anitta</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/estelle/27060010</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/live-love-learn/1884749126</v>
+        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
       </c>
       <c r="L32" t="str">
-        <v>Live, Love, Learn - Estelle</v>
+        <v>Choka Choka - Anitta</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Footlights</v>
+        <v>side slider</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/footlights/1885660551</v>
+        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Footlights - Single</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G33" t="str">
-        <v>4:24</v>
+        <v>3:47</v>
       </c>
       <c r="H33" t="str">
-        <v>Cody Johnson</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/footlights/1885660550</v>
+        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
       </c>
       <c r="L33" t="str">
-        <v>Footlights - Cody Johnson</v>
+        <v>side slider - Isaia Huron</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Remember to Forget</v>
+        <v>Woman I Am</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/remember-to-forget/1887886676</v>
+        <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Remember to Forget - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G34" t="str">
-        <v>3:39</v>
+        <v>3:31</v>
       </c>
       <c r="H34" t="str">
-        <v>Hailey Whitters</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/hailey-whitters/553410914</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/remember-to-forget/1887886674</v>
+        <v>https://music.apple.com/us/album/woman-i-am/1890182220</v>
       </c>
       <c r="L34" t="str">
-        <v>Remember to Forget - Hailey Whitters</v>
+        <v>Woman I Am - Skye Newman</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Sun Comes Up Tremendous</v>
+        <v>Bubee</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/sun-comes-up-tremendous/1883229766</v>
+        <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Sun Comes Up Tremendous - Single</v>
+        <v>Bubee - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:33</v>
+        <v>3:02</v>
       </c>
       <c r="H35" t="str">
-        <v>Disclosure</v>
+        <v>ILLIT</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/disclosure/520848228</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/sun-comes-up-tremendous/1883229765</v>
+        <v>https://music.apple.com/us/album/bubee/1885450328</v>
       </c>
       <c r="L35" t="str">
-        <v>Sun Comes Up Tremendous - Disclosure</v>
+        <v>Bubee - ILLIT</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Say So</v>
+        <v>Good Morning</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/say-so/1888326036</v>
+        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Say So - Single</v>
+        <v>24</v>
       </c>
       <c r="G36" t="str">
-        <v>3:21</v>
+        <v>3:02</v>
       </c>
       <c r="H36" t="str">
-        <v>Dan + Shay</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/say-so/1888325785</v>
+        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
       </c>
       <c r="L36" t="str">
-        <v>Say So - Dan + Shay</v>
+        <v>Good Morning - Alexis Ffrench</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Fantasy</v>
+        <v>Positano</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/fantasy/1880361475</v>
+        <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Lost, Found &amp; Forgotten...</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G37" t="str">
-        <v>4:07</v>
+        <v>3:27</v>
       </c>
       <c r="H37" t="str">
-        <v>Chris Stussy</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/fantasy/1880361449</v>
+        <v>https://music.apple.com/us/album/positano/1886736650</v>
       </c>
       <c r="L37" t="str">
-        <v>Fantasy - Chris Stussy</v>
+        <v>Positano - Stephan Moccio</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Favour</v>
+        <v>sophie</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/favour/1885941038</v>
+        <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Favour - Single</v>
+        <v>notes from the in between - EP</v>
       </c>
       <c r="G38" t="str">
-        <v>3:14</v>
+        <v>2:36</v>
       </c>
       <c r="H38" t="str">
-        <v>FISHER</v>
+        <v>kenzie</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/favour/1885941037</v>
+        <v>https://music.apple.com/us/album/sophie/1887348032</v>
       </c>
       <c r="L38" t="str">
-        <v>Favour - FISHER</v>
+        <v>sophie - kenzie</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dangerous Lover</v>
+        <v>kiss goodbye</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/dangerous-lover/1884781285</v>
+        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Dangerous Lover - Single</v>
+        <v>kiss goodbye / brb - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:24</v>
+        <v>2:43</v>
       </c>
       <c r="H39" t="str">
-        <v>Sekou</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/sekou/1685844750</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/dangerous-lover/1884781284</v>
+        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
       </c>
       <c r="L39" t="str">
-        <v>Dangerous Lover - Sekou</v>
+        <v>kiss goodbye - The Two Lips</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Foolsong</v>
+        <v>ENTRÉGAME</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/foolsong/1886215975</v>
+        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Foolsong - Single</v>
+        <v>RADIO VENEZUELA</v>
       </c>
       <c r="G40" t="str">
-        <v>3:18</v>
+        <v>3:08</v>
       </c>
       <c r="H40" t="str">
-        <v>aron!</v>
+        <v>Chino &amp; Nacho</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/foolsong/1886215974</v>
+        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
       </c>
       <c r="L40" t="str">
-        <v>Foolsong - aron!</v>
+        <v>ENTRÉGAME - Chino &amp; Nacho</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>I Don't Wanna Be</v>
+        <v>SOMETHING IN THE WATER</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/i-dont-wanna-be/1888501665</v>
+        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>I Don't Wanna Be - Single</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G41" t="str">
-        <v>3:16</v>
+        <v>2:39</v>
       </c>
       <c r="H41" t="str">
-        <v>Blake Rose</v>
+        <v>PARTY WAVE</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/blake-rose/1167991720</v>
+        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/i-dont-wanna-be/1888501664</v>
+        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
       </c>
       <c r="L41" t="str">
-        <v>I Don't Wanna Be - Blake Rose</v>
+        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lonesome Dove</v>
+        <v>Formation</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/lonesome-dove/1874700246</v>
+        <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Age of the Ram</v>
+        <v>Formation - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:04</v>
+        <v>2:36</v>
       </c>
       <c r="H42" t="str">
-        <v>Charley Crockett</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/lonesome-dove/1874700242</v>
+        <v>https://music.apple.com/us/album/formation/1882714060</v>
       </c>
       <c r="L42" t="str">
-        <v>Lonesome Dove - Charley Crockett</v>
+        <v>Formation - Adekunle Gold</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Cowgirl's Prayer</v>
+        <v>Who Will You Follow</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/cowgirls-prayer/1884167296</v>
+        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Cowgirl's Prayer - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G43" t="str">
-        <v>3:49</v>
+        <v>3:55</v>
       </c>
       <c r="H43" t="str">
-        <v>Danielle Bradbery</v>
+        <v>Evanescence</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/danielle-bradbery/624068729</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/cowgirls-prayer/1884167295</v>
+        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
       </c>
       <c r="L43" t="str">
-        <v>Cowgirl's Prayer - Danielle Bradbery</v>
+        <v>Who Will You Follow - Evanescence</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Hall of Fame</v>
+        <v>That's When You Know</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/hall-of-fame/1886576289</v>
+        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Hall of Fame - Single</v>
+        <v>That's When You Know - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:11</v>
+        <v>3:13</v>
       </c>
       <c r="H44" t="str">
-        <v>Chxrry</v>
+        <v>Kygo</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/chxrry/1520135642</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/hall-of-fame/1886576288</v>
+        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
       </c>
       <c r="L44" t="str">
-        <v>Hall of Fame - Chxrry</v>
+        <v>That's When You Know - Kygo</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>American Wedding</v>
+        <v>Drinking Game</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/american-wedding/1885995636</v>
+        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>American Wedding - Single</v>
+        <v>Drinking Game - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:11</v>
+        <v>2:50</v>
       </c>
       <c r="H45" t="str">
-        <v>flowerovlove</v>
+        <v>Warren Zeiders</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/american-wedding/1885995635</v>
+        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
       </c>
       <c r="L45" t="str">
-        <v>American Wedding - flowerovlove</v>
+        <v>Drinking Game - Warren Zeiders</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Fashion</v>
+        <v>Anything But Me</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/fashion/1887487303</v>
+        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Fashion - Single</v>
+        <v>In The Feeling</v>
       </c>
       <c r="G46" t="str">
-        <v>2:08</v>
+        <v>4:59</v>
       </c>
       <c r="H46" t="str">
-        <v>IVE</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/fashion/1887487297</v>
+        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
       </c>
       <c r="L46" t="str">
-        <v>Fashion - IVE</v>
+        <v>Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>heal</v>
+        <v>American Dream</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/heal/1880216061</v>
+        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Unfold</v>
+        <v>American Dream - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:59</v>
+        <v>4:27</v>
       </c>
       <c r="H47" t="str">
-        <v>MONSTA X</v>
+        <v>Alabama Shakes</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/monsta-x/992315362</v>
+        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/heal/1880216060</v>
+        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
       </c>
       <c r="L47" t="str">
-        <v>heal - MONSTA X</v>
+        <v>American Dream - Alabama Shakes</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Beautiful</v>
+        <v>Already There</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1887979307</v>
+        <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Beautiful - Single</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G48" t="str">
-        <v>3:35</v>
+        <v>3:50</v>
       </c>
       <c r="H48" t="str">
-        <v>Anyma</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1887979305</v>
+        <v>https://music.apple.com/us/album/already-there/1866700309</v>
       </c>
       <c r="L48" t="str">
-        <v>Beautiful - Anyma</v>
+        <v>Already There - Young the Giant</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Wildfire</v>
+        <v>ROCK BOTTOM</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/wildfire/1887444526</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>For All The Right Reasons, Vol. 1</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G49" t="str">
-        <v>3:11</v>
+        <v>2:47</v>
       </c>
       <c r="H49" t="str">
-        <v>Lekan</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/wildfire/1887444297</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
       </c>
       <c r="L49" t="str">
-        <v>Wildfire - Lekan</v>
+        <v>ROCK BOTTOM - Bilmuri</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Sliced by a Fingernail</v>
+        <v>Alone For A Year</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/sliced-by-a-fingernail/1879769225</v>
+        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Sliced by a Fingernail - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G50" t="str">
-        <v>4:08</v>
+        <v>3:22</v>
       </c>
       <c r="H50" t="str">
-        <v>Dry Cleaning</v>
+        <v>The Maine</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/dry-cleaning/1469164908</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/sliced-by-a-fingernail/1879769223</v>
+        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
       </c>
       <c r="L50" t="str">
-        <v>Sliced by a Fingernail - Dry Cleaning</v>
+        <v>Alone For A Year - The Maine</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>FENIAN (feat. Casiokids)</v>
+        <v>Bring Home My Man</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/fenian-feat-casiokids/1881565596</v>
+        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>FENIAN - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G51" t="str">
-        <v>3:14</v>
+        <v>4:22</v>
       </c>
       <c r="H51" t="str">
-        <v>Kneecap</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/fenian-feat-casiokids/1881565579</v>
+        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
       </c>
       <c r="L51" t="str">
-        <v>FENIAN (feat. Casiokids) - Kneecap</v>
+        <v>Bring Home My Man - Maya Hawke</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Sólo Tú</v>
+        <v>SUPERMAN</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/s%C3%B3lo-t%C3%BA/1887417656</v>
+        <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Sólo Tú - Single</v>
+        <v>SUPERMAN - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>2:37</v>
+        <v>3:24</v>
       </c>
       <c r="H52" t="str">
-        <v>Los Primos Del Este</v>
+        <v>South Arcade</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/los-primos-del-este/1462043487</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/s%C3%B3lo-t%C3%BA/1887417649</v>
+        <v>https://music.apple.com/us/album/superman/1890027995</v>
       </c>
       <c r="L52" t="str">
-        <v>Sólo Tú - Los Primos Del Este</v>
+        <v>SUPERMAN - South Arcade</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The Jesus I Know Now</v>
+        <v>1989</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/the-jesus-i-know-now/1887978274</v>
+        <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>The Jesus I Know Now - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>3:33</v>
+        <v>2:34</v>
       </c>
       <c r="H53" t="str">
-        <v>Brandon Lake</v>
+        <v>Nightly</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/brandon-lake/1050382282</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/the-jesus-i-know-now/1887978263</v>
+        <v>https://music.apple.com/us/album/1989/1887250154</v>
       </c>
       <c r="L53" t="str">
-        <v>The Jesus I Know Now - Brandon Lake</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Turnstile</v>
+        <v>waste your pain</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/turnstile/1867616937</v>
+        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>The Weight of the Woods</v>
+        <v>waste your pain - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>3:50</v>
+        <v>2:23</v>
       </c>
       <c r="H54" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/turnstile/1867616617</v>
+        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
       </c>
       <c r="L54" t="str">
-        <v>Turnstile - Dermot Kennedy</v>
+        <v>waste your pain - Cruz Beckham</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Surrender (From Your Friends &amp; Neighbors)</v>
+        <v>Strangers</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/surrender-from-your-friends-neighbors/1887371368</v>
+        <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Surrender (From Your Friends &amp; Neighbors) - Single</v>
+        <v>F**k, Marry, Kill</v>
       </c>
       <c r="G55" t="str">
-        <v>3:04</v>
+        <v>2:44</v>
       </c>
       <c r="H55" t="str">
-        <v>Lindsey Stirling</v>
+        <v>Tink</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/lindsey-stirling/403025113</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/surrender-from-your-friends-neighbors/1887371353</v>
+        <v>https://music.apple.com/us/album/strangers/1883252371</v>
       </c>
       <c r="L55" t="str">
-        <v>Surrender (From Your Friends &amp; Neighbors) - Lindsey Stirling</v>
+        <v>Strangers - Tink</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Before This Even Starts</v>
+        <v>Right In Front Of Me</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/before-this-even-starts/1883698214</v>
+        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Therapy &amp; Yoga - EP</v>
+        <v>Right In Front Of Me - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>2:44</v>
+        <v>2:45</v>
       </c>
       <c r="H56" t="str">
-        <v>JESSIA</v>
+        <v>Tiny Habits</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/jessia/1399415802</v>
+        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/before-this-even-starts/1883698028</v>
+        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
       </c>
       <c r="L56" t="str">
-        <v>Before This Even Starts - JESSIA</v>
+        <v>Right In Front Of Me - Tiny Habits</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Roses</v>
+        <v>SAME SH!T</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/roses/1883777517</v>
+        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Middle School Dropout - EP</v>
+        <v>SAME SH!T - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:10</v>
+        <v>3:13</v>
       </c>
       <c r="H57" t="str">
-        <v>Iris Copperman</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/roses/1883777352</v>
+        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
       </c>
       <c r="L57" t="str">
-        <v>Roses - Iris Copperman</v>
+        <v>SAME SH!T - Isaiah Rashad</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Does Your Father Know You Dance Like That?</v>
+        <v>Children of Light (feat. Max Cavalera)</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/does-your-father-know-you-dance-like-that/1886621446</v>
+        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Does Your Father Know You Dance Like That? - Single</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G58" t="str">
-        <v>2:28</v>
+        <v>4:12</v>
       </c>
       <c r="H58" t="str">
-        <v>Steve Aoki</v>
+        <v>Atreyu</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/does-your-father-know-you-dance-like-that/1886621445</v>
+        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
       </c>
       <c r="L58" t="str">
-        <v>Does Your Father Know You Dance Like That? - Steve Aoki</v>
+        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loco</v>
+        <v>Heal</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/loco/1888397210</v>
+        <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Loco - Single</v>
+        <v>Heal - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:34</v>
+        <v>3:26</v>
       </c>
       <c r="H59" t="str">
-        <v>Key Glock</v>
+        <v>HAYLA</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/key-glock/1199258326</v>
+        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/loco/1888397209</v>
+        <v>https://music.apple.com/us/album/heal/1884661625</v>
       </c>
       <c r="L59" t="str">
-        <v>Loco - Key Glock</v>
+        <v>Heal - HAYLA</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Hold It For Her</v>
+        <v>Free</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/hold-it-for-her/1861380253</v>
+        <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Porcelain</v>
+        <v>Songs I Wrote In New York - EP</v>
       </c>
       <c r="G60" t="str">
-        <v>3:48</v>
+        <v>4:13</v>
       </c>
       <c r="H60" t="str">
-        <v>Peach PRC</v>
+        <v>Simone Ashley</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/hold-it-for-her/1861380240</v>
+        <v>https://music.apple.com/us/album/free/1886600085</v>
       </c>
       <c r="L60" t="str">
-        <v>Hold It For Her - Peach PRC</v>
+        <v>Free - Simone Ashley</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Ghost town...</v>
+        <v>Cállate</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/ghost-town/1870971561</v>
+        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G61" t="str">
-        <v>2:44</v>
+        <v>1:59</v>
       </c>
       <c r="H61" t="str">
-        <v>R3HAB</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/ghost-town/1870971550</v>
+        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
       </c>
       <c r="L61" t="str">
-        <v>Ghost town... - R3HAB</v>
+        <v>Cállate - Dua Saleh</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>WASTE SOME TIME</v>
+        <v>Raindrops</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/waste-some-time/1887768620</v>
+        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>DAWN PATROL</v>
+        <v>Raindrops - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:26</v>
+        <v>3:34</v>
       </c>
       <c r="H62" t="str">
-        <v>Forrest Frank</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/waste-some-time/1887768606</v>
+        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
       </c>
       <c r="L62" t="str">
-        <v>WASTE SOME TIME - Forrest Frank</v>
+        <v>Raindrops - Rick Astley</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>control.</v>
+        <v>WORK OF ART</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/control/1887392580</v>
+        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>control. - Single</v>
+        <v>PRODIGY</v>
       </c>
       <c r="G63" t="str">
-        <v>2:50</v>
+        <v>2:27</v>
       </c>
       <c r="H63" t="str">
-        <v>Paco</v>
+        <v>Tkandz</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/paco/1513830139</v>
+        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/control/1887392578</v>
+        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
       </c>
       <c r="L63" t="str">
-        <v>control. - Paco</v>
+        <v>WORK OF ART - Tkandz</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Wouldn't Try Again</v>
+        <v>Damn Good Actress</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/wouldnt-try-again/1889328836</v>
+        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Wouldn't Try Again - Single</v>
+        <v>Damn Good Actress - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>2:45</v>
+        <v>2:49</v>
       </c>
       <c r="H64" t="str">
-        <v>Quail P</v>
+        <v>Tiffany Stringer</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/quail-p/1447409001</v>
+        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/wouldnt-try-again/1889328830</v>
+        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
       </c>
       <c r="L64" t="str">
-        <v>Wouldn't Try Again - Quail P</v>
+        <v>Damn Good Actress - Tiffany Stringer</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>i need u</v>
+        <v>Ricota</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/i-need-u/1889349101</v>
+        <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>i need u - Single</v>
+        <v>Ricota - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:45</v>
+        <v>2:25</v>
       </c>
       <c r="H65" t="str">
-        <v>BUNT.</v>
+        <v>ZULAN</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/i-need-u/1889349100</v>
+        <v>https://music.apple.com/us/album/ricota/1889387732</v>
       </c>
       <c r="L65" t="str">
-        <v>i need u - BUNT.</v>
+        <v>Ricota - ZULAN</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Outlaw</v>
+        <v>Kissing The Ground</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/outlaw/1877229747</v>
+        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>EI8HT</v>
+        <v>Kissing The Ground - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:35</v>
+        <v>3:50</v>
       </c>
       <c r="H66" t="str">
-        <v>Shinedown</v>
+        <v>Nell Mescal</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/outlaw/1877229738</v>
+        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
       </c>
       <c r="L66" t="str">
-        <v>Outlaw - Shinedown</v>
+        <v>Kissing The Ground - Nell Mescal</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>A.L.O.N.E.</v>
+        <v>Joy</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/a-l-o-n-e/1886537119</v>
+        <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>ADDENDUM</v>
+        <v>All In Now</v>
       </c>
       <c r="G67" t="str">
-        <v>3:24</v>
+        <v>3:41</v>
       </c>
       <c r="H67" t="str">
-        <v>HEALTH</v>
+        <v>Dogstar</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/health/317478211</v>
+        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/a-l-o-n-e/1886536873</v>
+        <v>https://music.apple.com/us/album/joy/1877978262</v>
       </c>
       <c r="L67" t="str">
-        <v>A.L.O.N.E. - HEALTH</v>
+        <v>Joy - Dogstar</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Him</v>
+        <v>Amor Bonito</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/him/1887319676</v>
+        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Him - Single</v>
+        <v>PUERTA ABIERTA</v>
       </c>
       <c r="G68" t="str">
-        <v>2:07</v>
+        <v>2:44</v>
       </c>
       <c r="H68" t="str">
-        <v>Sheff G</v>
+        <v>Kany García</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/him/1887319675</v>
+        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
       </c>
       <c r="L68" t="str">
-        <v>Him - Sheff G</v>
+        <v>Amor Bonito - Kany García</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>MVP (feat. Key Glock)</v>
+        <v>Patchwork</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/mvp-feat-key-glock/1888298376</v>
+        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>AREA 41</v>
+        <v>Patchwork - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:08</v>
+        <v>3:07</v>
       </c>
       <c r="H69" t="str">
-        <v>41</v>
+        <v>Carlita</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/carlita/599607197</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/mvp-feat-key-glock/1888298368</v>
+        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
       </c>
       <c r="L69" t="str">
-        <v>MVP (feat. Key Glock) - 41</v>
+        <v>Patchwork - Carlita</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>S.I.M.P.L.E</v>
+        <v>She's A Devil</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/s-i-m-p-l-e/1885386665</v>
+        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>DND</v>
+        <v>She's A Devil - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:33</v>
+        <v>3:24</v>
       </c>
       <c r="H70" t="str">
-        <v>TheARTI$t</v>
+        <v>Layton Giordani</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/s-i-m-p-l-e/1885386569</v>
+        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
       </c>
       <c r="L70" t="str">
-        <v>S.I.M.P.L.E - TheARTI$t</v>
+        <v>She's A Devil - Layton Giordani</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/at-least-shes-beautiful/1884405874</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>At Least She's Beautiful - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:36</v>
+        <v>2:52</v>
       </c>
       <c r="H71" t="str">
-        <v>rjtheweirdo</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/at-least-shes-beautiful/1884405873</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
       </c>
       <c r="L71" t="str">
-        <v>At Least She's Beautiful - rjtheweirdo</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Hella Good (feat. Bonnie McKee)</v>
+        <v>Time</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/hella-good-feat-bonnie-mckee/1886001675</v>
+        <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Hella Good (feat. Bonnie McKee) - Single</v>
+        <v>Time - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:45</v>
+        <v>3:20</v>
       </c>
       <c r="H72" t="str">
-        <v>Trixie Mattel</v>
+        <v>David Leonard</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/trixie-mattel/960467089</v>
+        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/hella-good-feat-bonnie-mckee/1886001667</v>
+        <v>https://music.apple.com/us/album/time/1880476790</v>
       </c>
       <c r="L72" t="str">
-        <v>Hella Good (feat. Bonnie McKee) - Trixie Mattel</v>
+        <v>Time - David Leonard</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Show</v>
+        <v>Andamos Ready</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/the-show/1889121528</v>
+        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>The Show - Single</v>
+        <v>Andamos Ready - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:47</v>
+        <v>3:10</v>
       </c>
       <c r="H73" t="str">
-        <v>DPR IAN</v>
+        <v>Los Tucanes de Tijuana</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/dpr-ian/1500739803</v>
+        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/the-show/1889121369</v>
+        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
       </c>
       <c r="L73" t="str">
-        <v>The Show - DPR IAN</v>
+        <v>Andamos Ready - Los Tucanes de Tijuana</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>His Eye Is On the Sparrow</v>
+        <v>Van y Vienen</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/his-eye-is-on-the-sparrow/1880392628</v>
+        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Grandma's Gospel Favorites</v>
+        <v>Van y Vienen - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>3:20</v>
+        <v>2:46</v>
       </c>
       <c r="H74" t="str">
-        <v>Jason Mraz</v>
+        <v>El Fantasma</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/jason-mraz/156987</v>
+        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/his-eye-is-on-the-sparrow/1880392609</v>
+        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
       </c>
       <c r="L74" t="str">
-        <v>His Eye Is On the Sparrow - Jason Mraz</v>
+        <v>Van y Vienen - El Fantasma</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Slowly</v>
+        <v>No Vuelvas</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/slowly/1869140941</v>
+        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Change Of Plans</v>
+        <v>No Vuelvas - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:11</v>
+        <v>3:46</v>
       </c>
       <c r="H75" t="str">
-        <v>49 Winchester</v>
+        <v>Majo Aguilar</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
+        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/slowly/1869140544</v>
+        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
       </c>
       <c r="L75" t="str">
-        <v>Slowly - 49 Winchester</v>
+        <v>No Vuelvas - Majo Aguilar</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>On Our Way Along</v>
+        <v>RUNNIN</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/on-our-way-along/1863814124</v>
+        <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>On Our Way Along - Single</v>
+        <v>RUNNIN - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>4:21</v>
+        <v>2:40</v>
       </c>
       <c r="H76" t="str">
-        <v>Billy Ray Cyrus</v>
+        <v>RUA YOUNG</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/billy-ray-cyrus/1793659079</v>
+        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/on-our-way-along/1863813853</v>
+        <v>https://music.apple.com/us/album/runnin/1886581868</v>
       </c>
       <c r="L76" t="str">
-        <v>On Our Way Along - Billy Ray Cyrus</v>
+        <v>RUNNIN - RUA YOUNG</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>COMING OF AGE</v>
+        <v>Talk You Through It</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/coming-of-age/1882886175</v>
+        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>COMING OF AGE - Single</v>
+        <v>Talk You Through It - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>4:08</v>
+        <v>3:33</v>
       </c>
       <c r="H77" t="str">
-        <v>METTE</v>
+        <v>Kenyon Dixon</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/mette/1553768125</v>
+        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/coming-of-age/1882886174</v>
+        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
       </c>
       <c r="L77" t="str">
-        <v>COMING OF AGE - METTE</v>
+        <v>Talk You Through It - Kenyon Dixon</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>the man with money in his hands</v>
+        <v>Partners in Crime</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/the-man-with-money-in-his-hands/1887707057</v>
+        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>the man with money in his hands - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G78" t="str">
-        <v>2:57</v>
+        <v>3:50</v>
       </c>
       <c r="H78" t="str">
-        <v>Jessie Mazin</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/jessie-mazin/1887707056</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/the-man-with-money-in-his-hands/1887707053</v>
+        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
       </c>
       <c r="L78" t="str">
-        <v>the man with money in his hands - Jessie Mazin</v>
+        <v>Partners in Crime - Social Distortion</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>WRANGLER</v>
+        <v>Change your mind</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/wrangler/1876267962</v>
+        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>WHAT CAN I TELL U</v>
+        <v>Change your mind - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:05</v>
+        <v>3:21</v>
       </c>
       <c r="H79" t="str">
-        <v>Claudia Valentina</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/wrangler/1876267654</v>
+        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
       </c>
       <c r="L79" t="str">
-        <v>WRANGLER - Claudia Valentina</v>
+        <v>Change your mind - Casper Sage</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Rydly</v>
+        <v>Bones to Ashes, Dark to Light</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/rydly/1878477155</v>
+        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>We Are Friends, Vol. 12 (Disk 2)</v>
+        <v>Bones to Ashes, Dark to Light - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>6:52</v>
+        <v>3:29</v>
       </c>
       <c r="H80" t="str">
-        <v>deadmau5</v>
+        <v>The Franklin Electric</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
+        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/rydly/1878476797</v>
+        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
       </c>
       <c r="L80" t="str">
-        <v>Rydly - deadmau5</v>
+        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>all the time</v>
+        <v>Venus in the Zinnia</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/all-the-time/1874100418</v>
+        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>ARCADE</v>
+        <v>Train on the Island</v>
       </c>
       <c r="G81" t="str">
-        <v>3:01</v>
+        <v>3:17</v>
       </c>
       <c r="H81" t="str">
-        <v>Deb Never</v>
+        <v>Aldous Harding</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/all-the-time/1874100412</v>
+        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
       </c>
       <c r="L81" t="str">
-        <v>all the time - Deb Never</v>
+        <v>Venus in the Zinnia - Aldous Harding</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Misery</v>
+        <v>Lover</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/misery/1888294484</v>
+        <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Misery - Single</v>
+        <v>Lover - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:55</v>
+        <v>3:26</v>
       </c>
       <c r="H82" t="str">
-        <v>Alex Sampson</v>
+        <v>Juke Ross</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/alex-sampson/1486112083</v>
+        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/misery/1888294483</v>
+        <v>https://music.apple.com/us/album/lover/1878758400</v>
       </c>
       <c r="L82" t="str">
-        <v>Misery - Alex Sampson</v>
+        <v>Lover - Juke Ross</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Don't Fall</v>
+        <v>pink moon</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/dont-fall/1884794995</v>
+        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Games - EP</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G83" t="str">
-        <v>4:20</v>
+        <v>3:21</v>
       </c>
       <c r="H83" t="str">
-        <v>Common People</v>
+        <v>runo plum</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/dont-fall/1884794990</v>
+        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
       </c>
       <c r="L83" t="str">
-        <v>Don't Fall - Common People</v>
+        <v>pink moon - runo plum</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Alternate Ending</v>
+        <v>Summer</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/alternate-ending/1886010374</v>
+        <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Alternate Ending - Single</v>
+        <v>Summer - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H84" t="str">
-        <v>Thelma &amp; James</v>
+        <v>Tasha</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/thelma-james/1787091600</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/alternate-ending/1886010053</v>
+        <v>https://music.apple.com/us/album/summer/1884645989</v>
       </c>
       <c r="L84" t="str">
-        <v>Alternate Ending - Thelma &amp; James</v>
+        <v>Summer - Tasha</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>LuCkY</v>
+        <v>Lizzie mcguire</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/lucky/1888001208</v>
+        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>MOEWYA</v>
+        <v>Tearless, thoughtless</v>
       </c>
       <c r="G85" t="str">
-        <v>2:17</v>
+        <v>4:20</v>
       </c>
       <c r="H85" t="str">
-        <v>MoeIsBetter</v>
+        <v>Nara's Room</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/moeisbetter/1762833637</v>
+        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/lucky/1888001204</v>
+        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
       </c>
       <c r="L85" t="str">
-        <v>LuCkY - MoeIsBetter</v>
+        <v>Lizzie mcguire - Nara's Room</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Mutual</v>
+        <v>Fabienk</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/mutual/1882922798</v>
+        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Mutual - Single</v>
+        <v>Vol.II</v>
       </c>
       <c r="G86" t="str">
-        <v>3:49</v>
+        <v>6:31</v>
       </c>
       <c r="H86" t="str">
-        <v>PJ Morton</v>
+        <v>Angine de Poitrine</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/pj-morton/44719201</v>
+        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/mutual/1882922794</v>
+        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
       </c>
       <c r="L86" t="str">
-        <v>Mutual - PJ Morton</v>
+        <v>Fabienk - Angine de Poitrine</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Waiting On</v>
+        <v>My Girl</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/waiting-on/1883846539</v>
+        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Waiting On - Single</v>
+        <v>Soren - EP</v>
       </c>
       <c r="G87" t="str">
-        <v>3:11</v>
+        <v>3:45</v>
       </c>
       <c r="H87" t="str">
-        <v>Tniyah</v>
+        <v>Orca</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/tniyah/513967453</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/waiting-on/1883846538</v>
+        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
       </c>
       <c r="L87" t="str">
-        <v>Waiting On - Tniyah</v>
+        <v>My Girl - Orca</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>En La Montaña</v>
+        <v>Bone Structure</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/en-la-monta%C3%B1a/1884092212</v>
+        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>En La Montaña - Single</v>
+        <v>Bone Structure - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>2:23</v>
+        <v>3:01</v>
       </c>
       <c r="H88" t="str">
-        <v>Nueva H</v>
+        <v>Dolder</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/en-la-monta%C3%B1a/1884092207</v>
+        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
       </c>
       <c r="L88" t="str">
-        <v>En La Montaña - Nueva H</v>
+        <v>Bone Structure - Dolder</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Falling Short</v>
+        <v>Turning Into Us</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/falling-short/1884803703</v>
+        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Falling Short - Single</v>
+        <v>Turning Into Us - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:05</v>
+        <v>3:30</v>
       </c>
       <c r="H89" t="str">
-        <v>Hudson Macready</v>
+        <v>Rhys Rutherford</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/hudson-macready/1534530042</v>
+        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/falling-short/1884803515</v>
+        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
       </c>
       <c r="L89" t="str">
-        <v>Falling Short - Hudson Macready</v>
+        <v>Turning Into Us - Rhys Rutherford</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>When You Give It Up</v>
+        <v>Bother Me (feat. Victony)</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/when-you-give-it-up/1879883866</v>
+        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>When You Give It Up - Single</v>
+        <v>Bother Me (feat. Victony) - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>2:42</v>
+        <v>3:00</v>
       </c>
       <c r="H90" t="str">
-        <v>Chelsea Plank</v>
+        <v>Osé</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-plank/1246169844</v>
+        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/when-you-give-it-up/1879883863</v>
+        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
       </c>
       <c r="L90" t="str">
-        <v>When You Give It Up - Chelsea Plank</v>
+        <v>Bother Me (feat. Victony) - Osé</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Wasted</v>
+        <v>Fright</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/wasted/1885578001</v>
+        <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Wasted - Single</v>
+        <v>Fright - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:18</v>
+        <v>2:25</v>
       </c>
       <c r="H91" t="str">
-        <v>Highly Suspect</v>
+        <v>Creepy Nuts</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/highly-suspect/419913603</v>
+        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/wasted/1885578000</v>
+        <v>https://music.apple.com/us/album/fright/1890396429</v>
       </c>
       <c r="L91" t="str">
-        <v>Wasted - Highly Suspect</v>
+        <v>Fright - Creepy Nuts</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Burn</v>
+        <v>Smoking In Bed</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/burn/1883195616</v>
+        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Burn - Single</v>
+        <v>Smoking In Bed - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>2:56</v>
+        <v>3:24</v>
       </c>
       <c r="H92" t="str">
-        <v>Cold Court</v>
+        <v>The Bends</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/cold-court/1809708831</v>
+        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/burn/1883195615</v>
+        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
       </c>
       <c r="L92" t="str">
-        <v>Burn - Cold Court</v>
+        <v>Smoking In Bed - The Bends</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Smash</v>
+        <v>The Dissonant Void</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/smash/1884655608</v>
+        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Eternal BAM Nation</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G93" t="str">
-        <v>2:27</v>
+        <v>2:47</v>
       </c>
       <c r="H93" t="str">
-        <v>Born At Midnite</v>
+        <v>At The Gates</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/born-at-midnite/1497209280</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/smash/1884655462</v>
+        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
       </c>
       <c r="L93" t="str">
-        <v>Smash - Born At Midnite</v>
+        <v>The Dissonant Void - At The Gates</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Smile</v>
+        <v>Nine Days Of Rain</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/smile/1859619683</v>
+        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Birding</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G94" t="str">
-        <v>5:09</v>
+        <v>3:51</v>
       </c>
       <c r="H94" t="str">
-        <v>deary</v>
+        <v>Melvins</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/deary/1641536096</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/smile/1859619407</v>
+        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
       </c>
       <c r="L94" t="str">
-        <v>Smile - deary</v>
+        <v>Nine Days Of Rain - Melvins</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Eshi</v>
+        <v>Invocation of the Dreamer</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/eshi/1880700566</v>
+        <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Zero</v>
+        <v>Khemmis</v>
       </c>
       <c r="G95" t="str">
-        <v>3:12</v>
+        <v>4:46</v>
       </c>
       <c r="H95" t="str">
-        <v>Alewya</v>
+        <v>Khemmis</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/alewya/1450971317</v>
+        <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/eshi/1880699673</v>
+        <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
       </c>
       <c r="L95" t="str">
-        <v>Eshi - Alewya</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>NO HOMEGIRLS</v>
-      </c>
-      <c r="B96" t="str">
-        <v/>
-      </c>
-      <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/no-homegirls/1886801763</v>
-      </c>
-      <c r="D96" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E96" t="str">
-        <v/>
-      </c>
-      <c r="F96" t="str">
-        <v>NO HOMEGIRLS - Single</v>
-      </c>
-      <c r="G96" t="str">
-        <v>2:05</v>
-      </c>
-      <c r="H96" t="str">
-        <v>BBYKOBE</v>
-      </c>
-      <c r="I96" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/bbykobe/1693491560</v>
-      </c>
-      <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/no-homegirls/1886801762</v>
-      </c>
-      <c r="L96" t="str">
-        <v>NO HOMEGIRLS - BBYKOBE</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>I Want You Back</v>
-      </c>
-      <c r="B97" t="str">
-        <v/>
-      </c>
-      <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/i-want-you-back/1889281139</v>
-      </c>
-      <c r="D97" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E97" t="str">
-        <v/>
-      </c>
-      <c r="F97" t="str">
-        <v>I Want You Back - Single</v>
-      </c>
-      <c r="G97" t="str">
-        <v>3:18</v>
-      </c>
-      <c r="H97" t="str">
-        <v>Johnny Venus</v>
-      </c>
-      <c r="I97" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/johnny-venus/1777129720</v>
-      </c>
-      <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/i-want-you-back/1889281136</v>
-      </c>
-      <c r="L97" t="str">
-        <v>I Want You Back - Johnny Venus</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>Needed You</v>
-      </c>
-      <c r="B98" t="str">
-        <v/>
-      </c>
-      <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/needed-you/1887702402</v>
-      </c>
-      <c r="D98" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E98" t="str">
-        <v/>
-      </c>
-      <c r="F98" t="str">
-        <v>Active Child</v>
-      </c>
-      <c r="G98" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H98" t="str">
-        <v>Active Child</v>
-      </c>
-      <c r="I98" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
-      </c>
-      <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/needed-you/1887701924</v>
-      </c>
-      <c r="L98" t="str">
-        <v>Needed You - Active Child</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Finish Line</v>
-      </c>
-      <c r="B99" t="str">
-        <v/>
-      </c>
-      <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/finish-line/1887371855</v>
-      </c>
-      <c r="D99" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E99" t="str">
-        <v/>
-      </c>
-      <c r="F99" t="str">
-        <v>Finish Line - Single</v>
-      </c>
-      <c r="G99" t="str">
-        <v>3:18</v>
-      </c>
-      <c r="H99" t="str">
-        <v>Ally Salort</v>
-      </c>
-      <c r="I99" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
-      </c>
-      <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/finish-line/1887371854</v>
-      </c>
-      <c r="L99" t="str">
-        <v>Finish Line - Ally Salort</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>Daredevil</v>
-      </c>
-      <c r="B100" t="str">
-        <v/>
-      </c>
-      <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/daredevil/1883231048</v>
-      </c>
-      <c r="D100" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E100" t="str">
-        <v/>
-      </c>
-      <c r="F100" t="str">
-        <v>Daredevil - Single</v>
-      </c>
-      <c r="G100" t="str">
-        <v>4:16</v>
-      </c>
-      <c r="H100" t="str">
-        <v>Zach Hood</v>
-      </c>
-      <c r="I100" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/zach-hood/1518857330</v>
-      </c>
-      <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/daredevil/1883231047</v>
-      </c>
-      <c r="L100" t="str">
-        <v>Daredevil - Zach Hood</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Asleep On The Killing Floor</v>
-      </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/asleep-on-the-killing-floor/1869086163</v>
-      </c>
-      <c r="D101" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
-        <v>Good God / Baad Man</v>
-      </c>
-      <c r="G101" t="str">
-        <v>4:08</v>
-      </c>
-      <c r="H101" t="str">
-        <v>Corrosion of Conformity</v>
-      </c>
-      <c r="I101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
-      </c>
-      <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/asleep-on-the-killing-floor/1869085524</v>
-      </c>
-      <c r="L101" t="str">
-        <v>Asleep On The Killing Floor - Corrosion of Conformity</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>You Bastard</v>
-      </c>
-      <c r="B102" t="str">
-        <v/>
-      </c>
-      <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/you-bastard/1871211807</v>
-      </c>
-      <c r="D102" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v>Neverending</v>
-      </c>
-      <c r="G102" t="str">
-        <v>4:19</v>
-      </c>
-      <c r="H102" t="str">
-        <v>Monolord</v>
-      </c>
-      <c r="I102" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
-      </c>
-      <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/you-bastard/1871211801</v>
-      </c>
-      <c r="L102" t="str">
-        <v>You Bastard - Monolord</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Vanilla Latte</v>
-      </c>
-      <c r="B103" t="str">
-        <v/>
-      </c>
-      <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/vanilla-latte/1884524943</v>
-      </c>
-      <c r="D103" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
-        <v>Vanilla Latte - EP</v>
-      </c>
-      <c r="G103" t="str">
-        <v>2:24</v>
-      </c>
-      <c r="H103" t="str">
-        <v>The Barbarians of California</v>
-      </c>
-      <c r="I103" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
-      </c>
-      <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/vanilla-latte/1884524941</v>
-      </c>
-      <c r="L103" t="str">
-        <v>Vanilla Latte - The Barbarians of California</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Nostalgia Kills</v>
-      </c>
-      <c r="B104" t="str">
-        <v/>
-      </c>
-      <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/nostalgia-kills/1887961043</v>
-      </c>
-      <c r="D104" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E104" t="str">
-        <v/>
-      </c>
-      <c r="F104" t="str">
-        <v>Nostalgia Kills - Single</v>
-      </c>
-      <c r="G104" t="str">
-        <v>3:03</v>
-      </c>
-      <c r="H104" t="str">
-        <v>Static Dress</v>
-      </c>
-      <c r="I104" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/static-dress/1476714067</v>
-      </c>
-      <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/nostalgia-kills/1887961038</v>
-      </c>
-      <c r="L104" t="str">
-        <v>Nostalgia Kills - Static Dress</v>
+        <v>Invocation of the Dreamer - Khemmis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L104"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L95"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1918,13 +1918,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>SOMETHING IN THE WATER</v>
+        <v>EL SENTRITA</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
+        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-10</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>DAWN PATROL</v>
+        <v>ETERNO</v>
       </c>
       <c r="G41" t="str">
-        <v>2:39</v>
+        <v>2:57</v>
       </c>
       <c r="H41" t="str">
-        <v>PARTY WAVE</v>
+        <v>Calle 24</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
+        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
+        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
       </c>
       <c r="L41" t="str">
-        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
+        <v>EL SENTRITA - Calle 24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Formation</v>
+        <v>SOMETHING IN THE WATER</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/formation/1882714068</v>
+        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-10</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Formation - Single</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G42" t="str">
-        <v>2:36</v>
+        <v>2:39</v>
       </c>
       <c r="H42" t="str">
-        <v>Adekunle Gold</v>
+        <v>PARTY WAVE</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/formation/1882714060</v>
+        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
       </c>
       <c r="L42" t="str">
-        <v>Formation - Adekunle Gold</v>
+        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Who Will You Follow</v>
+        <v>Formation</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
+        <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-10</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Sanctuary</v>
+        <v>Formation - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:55</v>
+        <v>2:36</v>
       </c>
       <c r="H43" t="str">
-        <v>Evanescence</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
+        <v>https://music.apple.com/us/album/formation/1882714060</v>
       </c>
       <c r="L43" t="str">
-        <v>Who Will You Follow - Evanescence</v>
+        <v>Formation - Adekunle Gold</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>That's When You Know</v>
+        <v>Who Will You Follow</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
+        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-10</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>That's When You Know - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G44" t="str">
-        <v>3:13</v>
+        <v>3:55</v>
       </c>
       <c r="H44" t="str">
-        <v>Kygo</v>
+        <v>Evanescence</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
+        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
       </c>
       <c r="L44" t="str">
-        <v>That's When You Know - Kygo</v>
+        <v>Who Will You Follow - Evanescence</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Drinking Game</v>
+        <v>That's When You Know</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
+        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-10</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Drinking Game - Single</v>
+        <v>That's When You Know - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>2:50</v>
+        <v>3:13</v>
       </c>
       <c r="H45" t="str">
-        <v>Warren Zeiders</v>
+        <v>Kygo</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
+        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
       </c>
       <c r="L45" t="str">
-        <v>Drinking Game - Warren Zeiders</v>
+        <v>That's When You Know - Kygo</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Anything But Me</v>
+        <v>Drinking Game</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
+        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-10</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>In The Feeling</v>
+        <v>Drinking Game - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>4:59</v>
+        <v>2:50</v>
       </c>
       <c r="H46" t="str">
-        <v>Owen Riegling</v>
+        <v>Warren Zeiders</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
+        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
       </c>
       <c r="L46" t="str">
-        <v>Anything But Me - Owen Riegling</v>
+        <v>Drinking Game - Warren Zeiders</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>American Dream</v>
+        <v>Anything But Me</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
+        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-10</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>American Dream - Single</v>
+        <v>In The Feeling</v>
       </c>
       <c r="G47" t="str">
-        <v>4:27</v>
+        <v>4:59</v>
       </c>
       <c r="H47" t="str">
-        <v>Alabama Shakes</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
+        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
       </c>
       <c r="L47" t="str">
-        <v>American Dream - Alabama Shakes</v>
+        <v>Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Already There</v>
+        <v>American Dream</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/already-there/1866700770</v>
+        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-10</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Victory Garden</v>
+        <v>American Dream - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>3:50</v>
+        <v>4:27</v>
       </c>
       <c r="H48" t="str">
-        <v>Young the Giant</v>
+        <v>Alabama Shakes</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/already-there/1866700309</v>
+        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
       </c>
       <c r="L48" t="str">
-        <v>Already There - Young the Giant</v>
+        <v>American Dream - Alabama Shakes</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ROCK BOTTOM</v>
+        <v>Already There</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
+        <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-10</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>KINDA HARD</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G49" t="str">
-        <v>2:47</v>
+        <v>3:50</v>
       </c>
       <c r="H49" t="str">
-        <v>Bilmuri</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
+        <v>https://music.apple.com/us/album/already-there/1866700309</v>
       </c>
       <c r="L49" t="str">
-        <v>ROCK BOTTOM - Bilmuri</v>
+        <v>Already There - Young the Giant</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Alone For A Year</v>
+        <v>ROCK BOTTOM</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-10</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Joy Next Door</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G50" t="str">
-        <v>3:22</v>
+        <v>2:47</v>
       </c>
       <c r="H50" t="str">
-        <v>The Maine</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
       </c>
       <c r="L50" t="str">
-        <v>Alone For A Year - The Maine</v>
+        <v>ROCK BOTTOM - Bilmuri</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Bring Home My Man</v>
+        <v>Alone For A Year</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
+        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-10</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G51" t="str">
-        <v>4:22</v>
+        <v>3:22</v>
       </c>
       <c r="H51" t="str">
-        <v>Maya Hawke</v>
+        <v>The Maine</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
+        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
       </c>
       <c r="L51" t="str">
-        <v>Bring Home My Man - Maya Hawke</v>
+        <v>Alone For A Year - The Maine</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SUPERMAN</v>
+        <v>Bring Home My Man</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/superman/1890027996</v>
+        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-10</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>SUPERMAN - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G52" t="str">
-        <v>3:24</v>
+        <v>4:22</v>
       </c>
       <c r="H52" t="str">
-        <v>South Arcade</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/superman/1890027995</v>
+        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
       </c>
       <c r="L52" t="str">
-        <v>SUPERMAN - South Arcade</v>
+        <v>Bring Home My Man - Maya Hawke</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>1989</v>
+        <v>SUPERMAN</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/1989/1887250155</v>
+        <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-10</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>1989 - Single</v>
+        <v>SUPERMAN - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>2:34</v>
+        <v>3:24</v>
       </c>
       <c r="H53" t="str">
-        <v>Nightly</v>
+        <v>South Arcade</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/1989/1887250154</v>
+        <v>https://music.apple.com/us/album/superman/1890027995</v>
       </c>
       <c r="L53" t="str">
-        <v>1989 - Nightly</v>
+        <v>SUPERMAN - South Arcade</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>waste your pain</v>
+        <v>1989</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
+        <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-10</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>waste your pain - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>2:23</v>
+        <v>2:34</v>
       </c>
       <c r="H54" t="str">
-        <v>Cruz Beckham</v>
+        <v>Nightly</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
+        <v>https://music.apple.com/us/album/1989/1887250154</v>
       </c>
       <c r="L54" t="str">
-        <v>waste your pain - Cruz Beckham</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Strangers</v>
+        <v>waste your pain</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/strangers/1883252372</v>
+        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-10</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>F**k, Marry, Kill</v>
+        <v>waste your pain - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>2:44</v>
+        <v>2:23</v>
       </c>
       <c r="H55" t="str">
-        <v>Tink</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/strangers/1883252371</v>
+        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
       </c>
       <c r="L55" t="str">
-        <v>Strangers - Tink</v>
+        <v>waste your pain - Cruz Beckham</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Right In Front Of Me</v>
+        <v>Strangers</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
+        <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-10</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Right In Front Of Me - Single</v>
+        <v>F**k, Marry, Kill</v>
       </c>
       <c r="G56" t="str">
-        <v>2:45</v>
+        <v>2:44</v>
       </c>
       <c r="H56" t="str">
-        <v>Tiny Habits</v>
+        <v>Tink</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
+        <v>https://music.apple.com/us/album/strangers/1883252371</v>
       </c>
       <c r="L56" t="str">
-        <v>Right In Front Of Me - Tiny Habits</v>
+        <v>Strangers - Tink</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>SAME SH!T</v>
+        <v>Right In Front Of Me</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
+        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-10</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>SAME SH!T - Single</v>
+        <v>Right In Front Of Me - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:13</v>
+        <v>2:45</v>
       </c>
       <c r="H57" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Tiny Habits</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
+        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
       </c>
       <c r="L57" t="str">
-        <v>SAME SH!T - Isaiah Rashad</v>
+        <v>Right In Front Of Me - Tiny Habits</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Children of Light (feat. Max Cavalera)</v>
+        <v>SAME SH!T</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
+        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-10</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>The End is Not the End</v>
+        <v>SAME SH!T - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>4:12</v>
+        <v>3:13</v>
       </c>
       <c r="H58" t="str">
-        <v>Atreyu</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
+        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
       </c>
       <c r="L58" t="str">
-        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
+        <v>SAME SH!T - Isaiah Rashad</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Heal</v>
+        <v>Children of Light (feat. Max Cavalera)</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/heal/1884661632</v>
+        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-10</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Heal - Single</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G59" t="str">
-        <v>3:26</v>
+        <v>4:12</v>
       </c>
       <c r="H59" t="str">
-        <v>HAYLA</v>
+        <v>Atreyu</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/heal/1884661625</v>
+        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
       </c>
       <c r="L59" t="str">
-        <v>Heal - HAYLA</v>
+        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Free</v>
+        <v>Heal</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/free/1886600087</v>
+        <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-10</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Songs I Wrote In New York - EP</v>
+        <v>Heal - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>4:13</v>
+        <v>3:26</v>
       </c>
       <c r="H60" t="str">
-        <v>Simone Ashley</v>
+        <v>HAYLA</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
+        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/free/1886600085</v>
+        <v>https://music.apple.com/us/album/heal/1884661625</v>
       </c>
       <c r="L60" t="str">
-        <v>Free - Simone Ashley</v>
+        <v>Heal - HAYLA</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Cállate</v>
+        <v>Free</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
+        <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-10</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Songs I Wrote In New York - EP</v>
       </c>
       <c r="G61" t="str">
-        <v>1:59</v>
+        <v>4:13</v>
       </c>
       <c r="H61" t="str">
-        <v>Dua Saleh</v>
+        <v>Simone Ashley</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
+        <v>https://music.apple.com/us/album/free/1886600085</v>
       </c>
       <c r="L61" t="str">
-        <v>Cállate - Dua Saleh</v>
+        <v>Free - Simone Ashley</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Raindrops</v>
+        <v>Cállate</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
+        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-10</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Raindrops - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G62" t="str">
-        <v>3:34</v>
+        <v>1:59</v>
       </c>
       <c r="H62" t="str">
-        <v>Rick Astley</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
+        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
       </c>
       <c r="L62" t="str">
-        <v>Raindrops - Rick Astley</v>
+        <v>Cállate - Dua Saleh</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>WORK OF ART</v>
+        <v>Raindrops</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
+        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-10</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>PRODIGY</v>
+        <v>Raindrops - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H63" t="str">
-        <v>Tkandz</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
+        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
+        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
       </c>
       <c r="L63" t="str">
-        <v>WORK OF ART - Tkandz</v>
+        <v>Raindrops - Rick Astley</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Damn Good Actress</v>
+        <v>WORK OF ART</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
+        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-10</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Damn Good Actress - Single</v>
+        <v>PRODIGY</v>
       </c>
       <c r="G64" t="str">
-        <v>2:49</v>
+        <v>2:27</v>
       </c>
       <c r="H64" t="str">
-        <v>Tiffany Stringer</v>
+        <v>Tkandz</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
+        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
+        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
       </c>
       <c r="L64" t="str">
-        <v>Damn Good Actress - Tiffany Stringer</v>
+        <v>WORK OF ART - Tkandz</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ricota</v>
+        <v>Scottie Pippen</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/ricota/1889387735</v>
+        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-10</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Ricota - Single</v>
+        <v>Scottie Pippen - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>2:25</v>
+        <v>2:34</v>
       </c>
       <c r="H65" t="str">
-        <v>ZULAN</v>
+        <v>SUNSHINE BENZI</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
+        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/ricota/1889387732</v>
+        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
       </c>
       <c r="L65" t="str">
-        <v>Ricota - ZULAN</v>
+        <v>Scottie Pippen - SUNSHINE BENZI</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Kissing The Ground</v>
+        <v>Damn Good Actress</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
+        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-10</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Kissing The Ground - Single</v>
+        <v>Damn Good Actress - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:50</v>
+        <v>2:49</v>
       </c>
       <c r="H66" t="str">
-        <v>Nell Mescal</v>
+        <v>Tiffany Stringer</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
+        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
+        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
       </c>
       <c r="L66" t="str">
-        <v>Kissing The Ground - Nell Mescal</v>
+        <v>Damn Good Actress - Tiffany Stringer</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Joy</v>
+        <v>Ricota</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/joy/1877978274</v>
+        <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-10</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>All In Now</v>
+        <v>Ricota - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:41</v>
+        <v>2:25</v>
       </c>
       <c r="H67" t="str">
-        <v>Dogstar</v>
+        <v>ZULAN</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
+        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/joy/1877978262</v>
+        <v>https://music.apple.com/us/album/ricota/1889387732</v>
       </c>
       <c r="L67" t="str">
-        <v>Joy - Dogstar</v>
+        <v>Ricota - ZULAN</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Amor Bonito</v>
+        <v>Kissing The Ground</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
+        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-10</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>PUERTA ABIERTA</v>
+        <v>Kissing The Ground - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:44</v>
+        <v>3:50</v>
       </c>
       <c r="H68" t="str">
-        <v>Kany García</v>
+        <v>Nell Mescal</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
+        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
       </c>
       <c r="L68" t="str">
-        <v>Amor Bonito - Kany García</v>
+        <v>Kissing The Ground - Nell Mescal</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Patchwork</v>
+        <v>Joy</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
+        <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-10</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Patchwork - Single</v>
+        <v>All In Now</v>
       </c>
       <c r="G69" t="str">
-        <v>3:07</v>
+        <v>3:41</v>
       </c>
       <c r="H69" t="str">
-        <v>Carlita</v>
+        <v>Dogstar</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/carlita/599607197</v>
+        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
+        <v>https://music.apple.com/us/album/joy/1877978262</v>
       </c>
       <c r="L69" t="str">
-        <v>Patchwork - Carlita</v>
+        <v>Joy - Dogstar</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>She's A Devil</v>
+        <v>Amor Bonito</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
+        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-10</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>She's A Devil - Single</v>
+        <v>PUERTA ABIERTA</v>
       </c>
       <c r="G70" t="str">
-        <v>3:24</v>
+        <v>2:44</v>
       </c>
       <c r="H70" t="str">
-        <v>Layton Giordani</v>
+        <v>Kany García</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
+        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
       </c>
       <c r="L70" t="str">
-        <v>She's A Devil - Layton Giordani</v>
+        <v>Amor Bonito - Kany García</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Do It All Alone</v>
+        <v>Patchwork</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
+        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-10</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Patchwork - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:52</v>
+        <v>3:07</v>
       </c>
       <c r="H71" t="str">
-        <v>Rend Collective</v>
+        <v>Carlita</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/carlita/599607197</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
+        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
       </c>
       <c r="L71" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Patchwork - Carlita</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Time</v>
+        <v>She's A Devil</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/time/1880476913</v>
+        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-10</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Time - Single</v>
+        <v>She's A Devil - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:20</v>
+        <v>3:24</v>
       </c>
       <c r="H72" t="str">
-        <v>David Leonard</v>
+        <v>Layton Giordani</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
+        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/time/1880476790</v>
+        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
       </c>
       <c r="L72" t="str">
-        <v>Time - David Leonard</v>
+        <v>She's A Devil - Layton Giordani</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Andamos Ready</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-10</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Andamos Ready - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:10</v>
+        <v>2:52</v>
       </c>
       <c r="H73" t="str">
-        <v>Los Tucanes de Tijuana</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
       </c>
       <c r="L73" t="str">
-        <v>Andamos Ready - Los Tucanes de Tijuana</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Van y Vienen</v>
+        <v>Time</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
+        <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-10</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Van y Vienen - Single</v>
+        <v>Time - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:46</v>
+        <v>3:20</v>
       </c>
       <c r="H74" t="str">
-        <v>El Fantasma</v>
+        <v>David Leonard</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
+        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
+        <v>https://music.apple.com/us/album/time/1880476790</v>
       </c>
       <c r="L74" t="str">
-        <v>Van y Vienen - El Fantasma</v>
+        <v>Time - David Leonard</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>No Vuelvas</v>
+        <v>Andamos Ready</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
+        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-10</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>No Vuelvas - Single</v>
+        <v>Andamos Ready - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:46</v>
+        <v>3:10</v>
       </c>
       <c r="H75" t="str">
-        <v>Majo Aguilar</v>
+        <v>Los Tucanes de Tijuana</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
+        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
+        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
       </c>
       <c r="L75" t="str">
-        <v>No Vuelvas - Majo Aguilar</v>
+        <v>Andamos Ready - Los Tucanes de Tijuana</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>RUNNIN</v>
+        <v>Van y Vienen</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/runnin/1886581872</v>
+        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-10</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>RUNNIN - Single</v>
+        <v>Van y Vienen - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:40</v>
+        <v>2:46</v>
       </c>
       <c r="H76" t="str">
-        <v>RUA YOUNG</v>
+        <v>El Fantasma</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
+        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/runnin/1886581868</v>
+        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
       </c>
       <c r="L76" t="str">
-        <v>RUNNIN - RUA YOUNG</v>
+        <v>Van y Vienen - El Fantasma</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Talk You Through It</v>
+        <v>No Vuelvas</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
+        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-10</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Talk You Through It - Single</v>
+        <v>No Vuelvas - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:33</v>
+        <v>3:46</v>
       </c>
       <c r="H77" t="str">
-        <v>Kenyon Dixon</v>
+        <v>Majo Aguilar</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
+        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
+        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
       </c>
       <c r="L77" t="str">
-        <v>Talk You Through It - Kenyon Dixon</v>
+        <v>No Vuelvas - Majo Aguilar</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Partners in Crime</v>
+        <v>RUNNIN</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
+        <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-10</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Born to Kill</v>
+        <v>RUNNIN - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:50</v>
+        <v>2:40</v>
       </c>
       <c r="H78" t="str">
-        <v>Social Distortion</v>
+        <v>RUA YOUNG</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
+        <v>https://music.apple.com/us/album/runnin/1886581868</v>
       </c>
       <c r="L78" t="str">
-        <v>Partners in Crime - Social Distortion</v>
+        <v>RUNNIN - RUA YOUNG</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Change your mind</v>
+        <v>Talk You Through It</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
+        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-10</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Change your mind - Single</v>
+        <v>Talk You Through It - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:21</v>
+        <v>3:33</v>
       </c>
       <c r="H79" t="str">
-        <v>Casper Sage</v>
+        <v>Kenyon Dixon</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
+        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
       </c>
       <c r="L79" t="str">
-        <v>Change your mind - Casper Sage</v>
+        <v>Talk You Through It - Kenyon Dixon</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Bones to Ashes, Dark to Light</v>
+        <v>Partners in Crime</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
+        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-10</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Bones to Ashes, Dark to Light - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G80" t="str">
-        <v>3:29</v>
+        <v>3:50</v>
       </c>
       <c r="H80" t="str">
-        <v>The Franklin Electric</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
+        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
       </c>
       <c r="L80" t="str">
-        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
+        <v>Partners in Crime - Social Distortion</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Venus in the Zinnia</v>
+        <v>Change your mind</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
+        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-10</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Train on the Island</v>
+        <v>Change your mind - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H81" t="str">
-        <v>Aldous Harding</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
+        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
       </c>
       <c r="L81" t="str">
-        <v>Venus in the Zinnia - Aldous Harding</v>
+        <v>Change your mind - Casper Sage</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lover</v>
+        <v>Bones to Ashes, Dark to Light</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/lover/1878758405</v>
+        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-10</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Lover - Single</v>
+        <v>Bones to Ashes, Dark to Light - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:26</v>
+        <v>3:29</v>
       </c>
       <c r="H82" t="str">
-        <v>Juke Ross</v>
+        <v>The Franklin Electric</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
+        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/lover/1878758400</v>
+        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
       </c>
       <c r="L82" t="str">
-        <v>Lover - Juke Ross</v>
+        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>pink moon</v>
+        <v>Venus in the Zinnia</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
+        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-10</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Train on the Island</v>
       </c>
       <c r="G83" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H83" t="str">
-        <v>runo plum</v>
+        <v>Aldous Harding</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
+        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
       </c>
       <c r="L83" t="str">
-        <v>pink moon - runo plum</v>
+        <v>Venus in the Zinnia - Aldous Harding</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Summer</v>
+        <v>Lover</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/summer/1884646207</v>
+        <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-10</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Summer - Single</v>
+        <v>Lover - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H84" t="str">
-        <v>Tasha</v>
+        <v>Juke Ross</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/summer/1884645989</v>
+        <v>https://music.apple.com/us/album/lover/1878758400</v>
       </c>
       <c r="L84" t="str">
-        <v>Summer - Tasha</v>
+        <v>Lover - Juke Ross</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Lizzie mcguire</v>
+        <v>pink moon</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
+        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-10</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Tearless, thoughtless</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G85" t="str">
-        <v>4:20</v>
+        <v>3:21</v>
       </c>
       <c r="H85" t="str">
-        <v>Nara's Room</v>
+        <v>runo plum</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
+        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
       </c>
       <c r="L85" t="str">
-        <v>Lizzie mcguire - Nara's Room</v>
+        <v>pink moon - runo plum</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Fabienk</v>
+        <v>Summer</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
+        <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-10</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Vol.II</v>
+        <v>Summer - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>6:31</v>
+        <v>3:21</v>
       </c>
       <c r="H86" t="str">
-        <v>Angine de Poitrine</v>
+        <v>Tasha</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
+        <v>https://music.apple.com/us/album/summer/1884645989</v>
       </c>
       <c r="L86" t="str">
-        <v>Fabienk - Angine de Poitrine</v>
+        <v>Summer - Tasha</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>My Girl</v>
+        <v>Lizzie mcguire</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
+        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-10</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Soren - EP</v>
+        <v>Tearless, thoughtless</v>
       </c>
       <c r="G87" t="str">
-        <v>3:45</v>
+        <v>4:20</v>
       </c>
       <c r="H87" t="str">
-        <v>Orca</v>
+        <v>Nara's Room</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
+        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
       </c>
       <c r="L87" t="str">
-        <v>My Girl - Orca</v>
+        <v>Lizzie mcguire - Nara's Room</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bone Structure</v>
+        <v>Fabienk</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
+        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-10</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Bone Structure - Single</v>
+        <v>Vol.II</v>
       </c>
       <c r="G88" t="str">
-        <v>3:01</v>
+        <v>6:31</v>
       </c>
       <c r="H88" t="str">
-        <v>Dolder</v>
+        <v>Angine de Poitrine</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
+        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
       </c>
       <c r="L88" t="str">
-        <v>Bone Structure - Dolder</v>
+        <v>Fabienk - Angine de Poitrine</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Turning Into Us</v>
+        <v>My Girl</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
+        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-10</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Turning Into Us - Single</v>
+        <v>Soren - EP</v>
       </c>
       <c r="G89" t="str">
-        <v>3:30</v>
+        <v>3:45</v>
       </c>
       <c r="H89" t="str">
-        <v>Rhys Rutherford</v>
+        <v>Orca</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
+        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
       </c>
       <c r="L89" t="str">
-        <v>Turning Into Us - Rhys Rutherford</v>
+        <v>My Girl - Orca</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Bother Me (feat. Victony)</v>
+        <v>Bone Structure</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
+        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-10</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Bother Me (feat. Victony) - Single</v>
+        <v>Bone Structure - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:00</v>
+        <v>3:01</v>
       </c>
       <c r="H90" t="str">
-        <v>Osé</v>
+        <v>Dolder</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
+        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
       </c>
       <c r="L90" t="str">
-        <v>Bother Me (feat. Victony) - Osé</v>
+        <v>Bone Structure - Dolder</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Fright</v>
+        <v>Turning Into Us</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/fright/1890396431</v>
+        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-10</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Fright - Single</v>
+        <v>Turning Into Us - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>2:25</v>
+        <v>3:30</v>
       </c>
       <c r="H91" t="str">
-        <v>Creepy Nuts</v>
+        <v>Rhys Rutherford</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
+        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/fright/1890396429</v>
+        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
       </c>
       <c r="L91" t="str">
-        <v>Fright - Creepy Nuts</v>
+        <v>Turning Into Us - Rhys Rutherford</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Smoking In Bed</v>
+        <v>Bother Me (feat. Victony)</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
+        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-10</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Smoking In Bed - Single</v>
+        <v>Bother Me (feat. Victony) - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:24</v>
+        <v>3:00</v>
       </c>
       <c r="H92" t="str">
-        <v>The Bends</v>
+        <v>Osé</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
+        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
+        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
       </c>
       <c r="L92" t="str">
-        <v>Smoking In Bed - The Bends</v>
+        <v>Bother Me (feat. Victony) - Osé</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Dissonant Void</v>
+        <v>Fright</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+        <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-10</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Fright - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>2:47</v>
+        <v>2:25</v>
       </c>
       <c r="H93" t="str">
-        <v>At The Gates</v>
+        <v>Creepy Nuts</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+        <v>https://music.apple.com/us/album/fright/1890396429</v>
       </c>
       <c r="L93" t="str">
-        <v>The Dissonant Void - At The Gates</v>
+        <v>Fright - Creepy Nuts</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Nine Days Of Rain</v>
+        <v>Smoking In Bed</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-10</v>
@@ -3947,68 +3947,144 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Smoking In Bed - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:51</v>
+        <v>3:24</v>
       </c>
       <c r="H94" t="str">
-        <v>Melvins</v>
+        <v>The Bends</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
       </c>
       <c r="L94" t="str">
-        <v>Nine Days Of Rain - Melvins</v>
+        <v>Smoking In Bed - The Bends</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
+        <v>The Dissonant Void</v>
+      </c>
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
+        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v>The Ghost of a Future Dead</v>
+      </c>
+      <c r="G95" t="str">
+        <v>2:47</v>
+      </c>
+      <c r="H95" t="str">
+        <v>At The Gates</v>
+      </c>
+      <c r="I95" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J95" t="str">
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+      </c>
+      <c r="K95" t="str">
+        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+      </c>
+      <c r="L95" t="str">
+        <v>The Dissonant Void - At The Gates</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Nine Days Of Rain</v>
+      </c>
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
+        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v>Savage Imperial Death March</v>
+      </c>
+      <c r="G96" t="str">
+        <v>3:51</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Melvins</v>
+      </c>
+      <c r="I96" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J96" t="str">
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
+      </c>
+      <c r="K96" t="str">
+        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Nine Days Of Rain - Melvins</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
         <v>Invocation of the Dreamer</v>
       </c>
-      <c r="B95" t="str">
-        <v/>
-      </c>
-      <c r="C95" t="str">
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
-      <c r="D95" t="str">
-        <v>2026-04-10</v>
-      </c>
-      <c r="E95" t="str">
-        <v/>
-      </c>
-      <c r="F95" t="str">
+      <c r="D97" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="G95" t="str">
+      <c r="G97" t="str">
         <v>4:46</v>
       </c>
-      <c r="H95" t="str">
+      <c r="H97" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="I95" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J95" t="str">
+      <c r="I97" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J97" t="str">
         <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
       </c>
-      <c r="K95" t="str">
+      <c r="K97" t="str">
         <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
       </c>
-      <c r="L95" t="str">
+      <c r="L97" t="str">
         <v>Invocation of the Dreamer - Khemmis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L95"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L97"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L98"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1272,13 +1272,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>idea 1</v>
+        <v>Waves of You</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
+        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-10</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>idea 1 - Single</v>
+        <v>Waves of You - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>3:25</v>
+        <v>3:15</v>
       </c>
       <c r="H24" t="str">
-        <v>Kelela</v>
+        <v>After Hours</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
+        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
       </c>
       <c r="L24" t="str">
-        <v>idea 1 - Kelela</v>
+        <v>Waves of You - After Hours</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Attitude</v>
+        <v>idea 1</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/attitude/1840517116</v>
+        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-10</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Sweat</v>
+        <v>idea 1 - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H25" t="str">
-        <v>Melanie C</v>
+        <v>Kelela</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/attitude/1840516706</v>
+        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
       </c>
       <c r="L25" t="str">
-        <v>Attitude - Melanie C</v>
+        <v>idea 1 - Kelela</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Carrie Bradshaw</v>
+        <v>Attitude</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
+        <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-10</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Carrie Bradshaw - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G26" t="str">
-        <v>2:54</v>
+        <v>3:13</v>
       </c>
       <c r="H26" t="str">
-        <v>Kylie Cantrall</v>
+        <v>Melanie C</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
+        <v>https://music.apple.com/us/album/attitude/1840516706</v>
       </c>
       <c r="L26" t="str">
-        <v>Carrie Bradshaw - Kylie Cantrall</v>
+        <v>Attitude - Melanie C</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Work</v>
+        <v>Carrie Bradshaw</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/work/1885916583</v>
+        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-10</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Work - Single</v>
+        <v>Carrie Bradshaw - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H27" t="str">
-        <v>Pitbull</v>
+        <v>Kylie Cantrall</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/work/1885916578</v>
+        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
       </c>
       <c r="L27" t="str">
-        <v>Work - Pitbull</v>
+        <v>Carrie Bradshaw - Kylie Cantrall</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Obvious</v>
+        <v>Work</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/obvious/1891759136</v>
+        <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-10</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Obvious - Single</v>
+        <v>Work - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>3:05</v>
+        <v>2:51</v>
       </c>
       <c r="H28" t="str">
-        <v>Chris Brown</v>
+        <v>Pitbull</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/obvious/1891759134</v>
+        <v>https://music.apple.com/us/album/work/1885916578</v>
       </c>
       <c r="L28" t="str">
-        <v>Obvious - Chris Brown</v>
+        <v>Work - Pitbull</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>As Time Goes By</v>
+        <v>Obvious</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
+        <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-10</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>CINEMATIC</v>
+        <v>Obvious - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>5:06</v>
+        <v>3:05</v>
       </c>
       <c r="H29" t="str">
-        <v>Josh Groban</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
+        <v>https://music.apple.com/us/album/obvious/1891759134</v>
       </c>
       <c r="L29" t="str">
-        <v>As Time Goes By - Josh Groban</v>
+        <v>Obvious - Chris Brown</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>My Mess</v>
+        <v>As Time Goes By</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
+        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-10</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>CINEMATIC</v>
       </c>
       <c r="G30" t="str">
-        <v>3:11</v>
+        <v>5:06</v>
       </c>
       <c r="H30" t="str">
-        <v>Myles Smith</v>
+        <v>Josh Groban</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
+        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
       </c>
       <c r="L30" t="str">
-        <v>My Mess - Myles Smith</v>
+        <v>As Time Goes By - Josh Groban</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Going Shopping</v>
+        <v>My Mess</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
+        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-10</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Reality Awaits</v>
+        <v>My Mess, My Heart, My Life.</v>
       </c>
       <c r="G31" t="str">
-        <v>4:21</v>
+        <v>3:11</v>
       </c>
       <c r="H31" t="str">
-        <v>The Strokes</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
+        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
       </c>
       <c r="L31" t="str">
-        <v>Going Shopping - The Strokes</v>
+        <v>My Mess - Myles Smith</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Choka Choka</v>
+        <v>Going Shopping</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
+        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-10</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Choka Choka - Single</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G32" t="str">
-        <v>2:11</v>
+        <v>4:21</v>
       </c>
       <c r="H32" t="str">
-        <v>Anitta</v>
+        <v>The Strokes</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
+        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
       </c>
       <c r="L32" t="str">
-        <v>Choka Choka - Anitta</v>
+        <v>Going Shopping - The Strokes</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>side slider</v>
+        <v>Choka Choka</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
+        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-10</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Choka Choka - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:47</v>
+        <v>2:11</v>
       </c>
       <c r="H33" t="str">
-        <v>Isaia Huron</v>
+        <v>Anitta</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
+        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
       </c>
       <c r="L33" t="str">
-        <v>side slider - Isaia Huron</v>
+        <v>Choka Choka - Anitta</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Woman I Am</v>
+        <v>side slider</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
+        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-10</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>SE9</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G34" t="str">
-        <v>3:31</v>
+        <v>3:47</v>
       </c>
       <c r="H34" t="str">
-        <v>Skye Newman</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/woman-i-am/1890182220</v>
+        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
       </c>
       <c r="L34" t="str">
-        <v>Woman I Am - Skye Newman</v>
+        <v>side slider - Isaia Huron</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Bubee</v>
+        <v>Woman I Am</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/bubee/1885450942</v>
+        <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-10</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Bubee - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G35" t="str">
-        <v>3:02</v>
+        <v>3:31</v>
       </c>
       <c r="H35" t="str">
-        <v>ILLIT</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/bubee/1885450328</v>
+        <v>https://music.apple.com/us/album/woman-i-am/1890182220</v>
       </c>
       <c r="L35" t="str">
-        <v>Bubee - ILLIT</v>
+        <v>Woman I Am - Skye Newman</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Good Morning</v>
+        <v>Bubee</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
+        <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-10</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>24</v>
+        <v>Bubee - Single</v>
       </c>
       <c r="G36" t="str">
         <v>3:02</v>
       </c>
       <c r="H36" t="str">
-        <v>Alexis Ffrench</v>
+        <v>ILLIT</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
+        <v>https://music.apple.com/us/album/bubee/1885450328</v>
       </c>
       <c r="L36" t="str">
-        <v>Good Morning - Alexis Ffrench</v>
+        <v>Bubee - ILLIT</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Positano</v>
+        <v>Good Morning</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/positano/1886736661</v>
+        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-10</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>24</v>
       </c>
       <c r="G37" t="str">
-        <v>3:27</v>
+        <v>3:02</v>
       </c>
       <c r="H37" t="str">
-        <v>Stephan Moccio</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/positano/1886736650</v>
+        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
       </c>
       <c r="L37" t="str">
-        <v>Positano - Stephan Moccio</v>
+        <v>Good Morning - Alexis Ffrench</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>sophie</v>
+        <v>Positano</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/sophie/1887348036</v>
+        <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-10</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>notes from the in between - EP</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G38" t="str">
-        <v>2:36</v>
+        <v>3:27</v>
       </c>
       <c r="H38" t="str">
-        <v>kenzie</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/sophie/1887348032</v>
+        <v>https://music.apple.com/us/album/positano/1886736650</v>
       </c>
       <c r="L38" t="str">
-        <v>sophie - kenzie</v>
+        <v>Positano - Stephan Moccio</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>kiss goodbye</v>
+        <v>sophie</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
+        <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-10</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>kiss goodbye / brb - Single</v>
+        <v>notes from the in between - EP</v>
       </c>
       <c r="G39" t="str">
-        <v>2:43</v>
+        <v>2:36</v>
       </c>
       <c r="H39" t="str">
-        <v>The Two Lips</v>
+        <v>kenzie</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
+        <v>https://music.apple.com/us/album/sophie/1887348032</v>
       </c>
       <c r="L39" t="str">
-        <v>kiss goodbye - The Two Lips</v>
+        <v>sophie - kenzie</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENTRÉGAME</v>
+        <v>kiss goodbye</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
+        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-10</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>RADIO VENEZUELA</v>
+        <v>kiss goodbye / brb - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:08</v>
+        <v>2:43</v>
       </c>
       <c r="H40" t="str">
-        <v>Chino &amp; Nacho</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
+        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
       </c>
       <c r="L40" t="str">
-        <v>ENTRÉGAME - Chino &amp; Nacho</v>
+        <v>kiss goodbye - The Two Lips</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>EL SENTRITA</v>
+        <v>ENTRÉGAME</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
+        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-10</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>ETERNO</v>
+        <v>RADIO VENEZUELA</v>
       </c>
       <c r="G41" t="str">
-        <v>2:57</v>
+        <v>3:08</v>
       </c>
       <c r="H41" t="str">
-        <v>Calle 24</v>
+        <v>Chino &amp; Nacho</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
+        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
+        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
       </c>
       <c r="L41" t="str">
-        <v>EL SENTRITA - Calle 24</v>
+        <v>ENTRÉGAME - Chino &amp; Nacho</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SOMETHING IN THE WATER</v>
+        <v>EL SENTRITA</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
+        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-10</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>DAWN PATROL</v>
+        <v>ETERNO</v>
       </c>
       <c r="G42" t="str">
-        <v>2:39</v>
+        <v>2:57</v>
       </c>
       <c r="H42" t="str">
-        <v>PARTY WAVE</v>
+        <v>Calle 24</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
+        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
+        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
       </c>
       <c r="L42" t="str">
-        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
+        <v>EL SENTRITA - Calle 24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Formation</v>
+        <v>SOMETHING IN THE WATER</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/formation/1882714068</v>
+        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-10</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Formation - Single</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G43" t="str">
-        <v>2:36</v>
+        <v>2:39</v>
       </c>
       <c r="H43" t="str">
-        <v>Adekunle Gold</v>
+        <v>PARTY WAVE</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/formation/1882714060</v>
+        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
       </c>
       <c r="L43" t="str">
-        <v>Formation - Adekunle Gold</v>
+        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Who Will You Follow</v>
+        <v>Formation</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
+        <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-10</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Sanctuary</v>
+        <v>Formation - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:55</v>
+        <v>2:36</v>
       </c>
       <c r="H44" t="str">
-        <v>Evanescence</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
+        <v>https://music.apple.com/us/album/formation/1882714060</v>
       </c>
       <c r="L44" t="str">
-        <v>Who Will You Follow - Evanescence</v>
+        <v>Formation - Adekunle Gold</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>That's When You Know</v>
+        <v>Who Will You Follow</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
+        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-10</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>That's When You Know - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G45" t="str">
-        <v>3:13</v>
+        <v>3:55</v>
       </c>
       <c r="H45" t="str">
-        <v>Kygo</v>
+        <v>Evanescence</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
+        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
       </c>
       <c r="L45" t="str">
-        <v>That's When You Know - Kygo</v>
+        <v>Who Will You Follow - Evanescence</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Drinking Game</v>
+        <v>That's When You Know</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
+        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-10</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Drinking Game - Single</v>
+        <v>That's When You Know - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>2:50</v>
+        <v>3:13</v>
       </c>
       <c r="H46" t="str">
-        <v>Warren Zeiders</v>
+        <v>Kygo</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
+        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
       </c>
       <c r="L46" t="str">
-        <v>Drinking Game - Warren Zeiders</v>
+        <v>That's When You Know - Kygo</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Anything But Me</v>
+        <v>Drinking Game</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
+        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-10</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>In The Feeling</v>
+        <v>Drinking Game - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>4:59</v>
+        <v>2:50</v>
       </c>
       <c r="H47" t="str">
-        <v>Owen Riegling</v>
+        <v>Warren Zeiders</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
+        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
       </c>
       <c r="L47" t="str">
-        <v>Anything But Me - Owen Riegling</v>
+        <v>Drinking Game - Warren Zeiders</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>American Dream</v>
+        <v>Anything But Me</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
+        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-10</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>American Dream - Single</v>
+        <v>In The Feeling</v>
       </c>
       <c r="G48" t="str">
-        <v>4:27</v>
+        <v>4:59</v>
       </c>
       <c r="H48" t="str">
-        <v>Alabama Shakes</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
+        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
       </c>
       <c r="L48" t="str">
-        <v>American Dream - Alabama Shakes</v>
+        <v>Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Already There</v>
+        <v>American Dream</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/already-there/1866700770</v>
+        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-10</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Victory Garden</v>
+        <v>American Dream - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:50</v>
+        <v>4:27</v>
       </c>
       <c r="H49" t="str">
-        <v>Young the Giant</v>
+        <v>Alabama Shakes</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/already-there/1866700309</v>
+        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
       </c>
       <c r="L49" t="str">
-        <v>Already There - Young the Giant</v>
+        <v>American Dream - Alabama Shakes</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ROCK BOTTOM</v>
+        <v>Already There</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
+        <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-10</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>KINDA HARD</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G50" t="str">
-        <v>2:47</v>
+        <v>3:50</v>
       </c>
       <c r="H50" t="str">
-        <v>Bilmuri</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
+        <v>https://music.apple.com/us/album/already-there/1866700309</v>
       </c>
       <c r="L50" t="str">
-        <v>ROCK BOTTOM - Bilmuri</v>
+        <v>Already There - Young the Giant</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Alone For A Year</v>
+        <v>ROCK BOTTOM</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-10</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Joy Next Door</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G51" t="str">
-        <v>3:22</v>
+        <v>2:47</v>
       </c>
       <c r="H51" t="str">
-        <v>The Maine</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
       </c>
       <c r="L51" t="str">
-        <v>Alone For A Year - The Maine</v>
+        <v>ROCK BOTTOM - Bilmuri</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Bring Home My Man</v>
+        <v>Alone For A Year</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
+        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-10</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G52" t="str">
-        <v>4:22</v>
+        <v>3:22</v>
       </c>
       <c r="H52" t="str">
-        <v>Maya Hawke</v>
+        <v>The Maine</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
+        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
       </c>
       <c r="L52" t="str">
-        <v>Bring Home My Man - Maya Hawke</v>
+        <v>Alone For A Year - The Maine</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SUPERMAN</v>
+        <v>Bring Home My Man</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/superman/1890027996</v>
+        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-10</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>SUPERMAN - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G53" t="str">
-        <v>3:24</v>
+        <v>4:22</v>
       </c>
       <c r="H53" t="str">
-        <v>South Arcade</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/superman/1890027995</v>
+        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
       </c>
       <c r="L53" t="str">
-        <v>SUPERMAN - South Arcade</v>
+        <v>Bring Home My Man - Maya Hawke</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>1989</v>
+        <v>SUPERMAN</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/1989/1887250155</v>
+        <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-10</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>1989 - Single</v>
+        <v>SUPERMAN - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>2:34</v>
+        <v>3:24</v>
       </c>
       <c r="H54" t="str">
-        <v>Nightly</v>
+        <v>South Arcade</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/1989/1887250154</v>
+        <v>https://music.apple.com/us/album/superman/1890027995</v>
       </c>
       <c r="L54" t="str">
-        <v>1989 - Nightly</v>
+        <v>SUPERMAN - South Arcade</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>waste your pain</v>
+        <v>1989</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
+        <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-10</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>waste your pain - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>2:23</v>
+        <v>2:34</v>
       </c>
       <c r="H55" t="str">
-        <v>Cruz Beckham</v>
+        <v>Nightly</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
+        <v>https://music.apple.com/us/album/1989/1887250154</v>
       </c>
       <c r="L55" t="str">
-        <v>waste your pain - Cruz Beckham</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Strangers</v>
+        <v>waste your pain</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/strangers/1883252372</v>
+        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-10</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>F**k, Marry, Kill</v>
+        <v>waste your pain - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>2:44</v>
+        <v>2:23</v>
       </c>
       <c r="H56" t="str">
-        <v>Tink</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/strangers/1883252371</v>
+        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
       </c>
       <c r="L56" t="str">
-        <v>Strangers - Tink</v>
+        <v>waste your pain - Cruz Beckham</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Right In Front Of Me</v>
+        <v>Strangers</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
+        <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-10</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Right In Front Of Me - Single</v>
+        <v>F**k, Marry, Kill</v>
       </c>
       <c r="G57" t="str">
-        <v>2:45</v>
+        <v>2:44</v>
       </c>
       <c r="H57" t="str">
-        <v>Tiny Habits</v>
+        <v>Tink</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
+        <v>https://music.apple.com/us/album/strangers/1883252371</v>
       </c>
       <c r="L57" t="str">
-        <v>Right In Front Of Me - Tiny Habits</v>
+        <v>Strangers - Tink</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SAME SH!T</v>
+        <v>Right In Front Of Me</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
+        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-10</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>SAME SH!T - Single</v>
+        <v>Right In Front Of Me - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:13</v>
+        <v>2:45</v>
       </c>
       <c r="H58" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Tiny Habits</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
+        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
       </c>
       <c r="L58" t="str">
-        <v>SAME SH!T - Isaiah Rashad</v>
+        <v>Right In Front Of Me - Tiny Habits</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Children of Light (feat. Max Cavalera)</v>
+        <v>SAME SH!T</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
+        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-10</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>The End is Not the End</v>
+        <v>SAME SH!T - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>4:12</v>
+        <v>3:13</v>
       </c>
       <c r="H59" t="str">
-        <v>Atreyu</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
+        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
       </c>
       <c r="L59" t="str">
-        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
+        <v>SAME SH!T - Isaiah Rashad</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Heal</v>
+        <v>Children of Light (feat. Max Cavalera)</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/heal/1884661632</v>
+        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-10</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Heal - Single</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G60" t="str">
-        <v>3:26</v>
+        <v>4:12</v>
       </c>
       <c r="H60" t="str">
-        <v>HAYLA</v>
+        <v>Atreyu</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/heal/1884661625</v>
+        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
       </c>
       <c r="L60" t="str">
-        <v>Heal - HAYLA</v>
+        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Free</v>
+        <v>Heal</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/free/1886600087</v>
+        <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-10</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Songs I Wrote In New York - EP</v>
+        <v>Heal - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>4:13</v>
+        <v>3:26</v>
       </c>
       <c r="H61" t="str">
-        <v>Simone Ashley</v>
+        <v>HAYLA</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
+        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/free/1886600085</v>
+        <v>https://music.apple.com/us/album/heal/1884661625</v>
       </c>
       <c r="L61" t="str">
-        <v>Free - Simone Ashley</v>
+        <v>Heal - HAYLA</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Cállate</v>
+        <v>Free</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
+        <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-10</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Songs I Wrote In New York - EP</v>
       </c>
       <c r="G62" t="str">
-        <v>1:59</v>
+        <v>4:13</v>
       </c>
       <c r="H62" t="str">
-        <v>Dua Saleh</v>
+        <v>Simone Ashley</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
+        <v>https://music.apple.com/us/album/free/1886600085</v>
       </c>
       <c r="L62" t="str">
-        <v>Cállate - Dua Saleh</v>
+        <v>Free - Simone Ashley</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Raindrops</v>
+        <v>Cállate</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
+        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-10</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Raindrops - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G63" t="str">
-        <v>3:34</v>
+        <v>1:59</v>
       </c>
       <c r="H63" t="str">
-        <v>Rick Astley</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
+        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
       </c>
       <c r="L63" t="str">
-        <v>Raindrops - Rick Astley</v>
+        <v>Cállate - Dua Saleh</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>WORK OF ART</v>
+        <v>Raindrops</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
+        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-10</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>PRODIGY</v>
+        <v>Raindrops - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H64" t="str">
-        <v>Tkandz</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
+        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
+        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
       </c>
       <c r="L64" t="str">
-        <v>WORK OF ART - Tkandz</v>
+        <v>Raindrops - Rick Astley</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Scottie Pippen</v>
+        <v>WORK OF ART</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
+        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-10</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Scottie Pippen - Single</v>
+        <v>PRODIGY</v>
       </c>
       <c r="G65" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H65" t="str">
-        <v>SUNSHINE BENZI</v>
+        <v>Tkandz</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
+        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
+        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
       </c>
       <c r="L65" t="str">
-        <v>Scottie Pippen - SUNSHINE BENZI</v>
+        <v>WORK OF ART - Tkandz</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Damn Good Actress</v>
+        <v>Scottie Pippen</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
+        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-10</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Damn Good Actress - Single</v>
+        <v>Scottie Pippen - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>2:49</v>
+        <v>2:34</v>
       </c>
       <c r="H66" t="str">
-        <v>Tiffany Stringer</v>
+        <v>SUNSHINE BENZI</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
+        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
+        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
       </c>
       <c r="L66" t="str">
-        <v>Damn Good Actress - Tiffany Stringer</v>
+        <v>Scottie Pippen - SUNSHINE BENZI</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Ricota</v>
+        <v>Damn Good Actress</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/ricota/1889387735</v>
+        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-10</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Ricota - Single</v>
+        <v>Damn Good Actress - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:25</v>
+        <v>2:49</v>
       </c>
       <c r="H67" t="str">
-        <v>ZULAN</v>
+        <v>Tiffany Stringer</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
+        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/ricota/1889387732</v>
+        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
       </c>
       <c r="L67" t="str">
-        <v>Ricota - ZULAN</v>
+        <v>Damn Good Actress - Tiffany Stringer</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Kissing The Ground</v>
+        <v>Ricota</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
+        <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-10</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Kissing The Ground - Single</v>
+        <v>Ricota - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:50</v>
+        <v>2:25</v>
       </c>
       <c r="H68" t="str">
-        <v>Nell Mescal</v>
+        <v>ZULAN</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
+        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
+        <v>https://music.apple.com/us/album/ricota/1889387732</v>
       </c>
       <c r="L68" t="str">
-        <v>Kissing The Ground - Nell Mescal</v>
+        <v>Ricota - ZULAN</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Joy</v>
+        <v>Kissing The Ground</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/joy/1877978274</v>
+        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-10</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>All In Now</v>
+        <v>Kissing The Ground - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:41</v>
+        <v>3:50</v>
       </c>
       <c r="H69" t="str">
-        <v>Dogstar</v>
+        <v>Nell Mescal</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
+        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/joy/1877978262</v>
+        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
       </c>
       <c r="L69" t="str">
-        <v>Joy - Dogstar</v>
+        <v>Kissing The Ground - Nell Mescal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Amor Bonito</v>
+        <v>Joy</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
+        <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-10</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>PUERTA ABIERTA</v>
+        <v>All In Now</v>
       </c>
       <c r="G70" t="str">
-        <v>2:44</v>
+        <v>3:41</v>
       </c>
       <c r="H70" t="str">
-        <v>Kany García</v>
+        <v>Dogstar</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
+        <v>https://music.apple.com/us/album/joy/1877978262</v>
       </c>
       <c r="L70" t="str">
-        <v>Amor Bonito - Kany García</v>
+        <v>Joy - Dogstar</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Patchwork</v>
+        <v>Amor Bonito</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
+        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-10</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Patchwork - Single</v>
+        <v>PUERTA ABIERTA</v>
       </c>
       <c r="G71" t="str">
-        <v>3:07</v>
+        <v>2:44</v>
       </c>
       <c r="H71" t="str">
-        <v>Carlita</v>
+        <v>Kany García</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/carlita/599607197</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
+        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
       </c>
       <c r="L71" t="str">
-        <v>Patchwork - Carlita</v>
+        <v>Amor Bonito - Kany García</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>She's A Devil</v>
+        <v>Patchwork</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
+        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-10</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>She's A Devil - Single</v>
+        <v>Patchwork - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:24</v>
+        <v>3:07</v>
       </c>
       <c r="H72" t="str">
-        <v>Layton Giordani</v>
+        <v>Carlita</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
+        <v>https://music.apple.com/us/artist/carlita/599607197</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
+        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
       </c>
       <c r="L72" t="str">
-        <v>She's A Devil - Layton Giordani</v>
+        <v>Patchwork - Carlita</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Do It All Alone</v>
+        <v>She's A Devil</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
+        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-10</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>She's A Devil - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:52</v>
+        <v>3:24</v>
       </c>
       <c r="H73" t="str">
-        <v>Rend Collective</v>
+        <v>Layton Giordani</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
+        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
       </c>
       <c r="L73" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>She's A Devil - Layton Giordani</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Time</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/time/1880476913</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-10</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Time - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>3:20</v>
+        <v>2:52</v>
       </c>
       <c r="H74" t="str">
-        <v>David Leonard</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/time/1880476790</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
       </c>
       <c r="L74" t="str">
-        <v>Time - David Leonard</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Andamos Ready</v>
+        <v>Time</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
+        <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-10</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Andamos Ready - Single</v>
+        <v>Time - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:10</v>
+        <v>3:20</v>
       </c>
       <c r="H75" t="str">
-        <v>Los Tucanes de Tijuana</v>
+        <v>David Leonard</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
+        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
+        <v>https://music.apple.com/us/album/time/1880476790</v>
       </c>
       <c r="L75" t="str">
-        <v>Andamos Ready - Los Tucanes de Tijuana</v>
+        <v>Time - David Leonard</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Van y Vienen</v>
+        <v>Andamos Ready</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
+        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-10</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Van y Vienen - Single</v>
+        <v>Andamos Ready - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:46</v>
+        <v>3:10</v>
       </c>
       <c r="H76" t="str">
-        <v>El Fantasma</v>
+        <v>Los Tucanes de Tijuana</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
+        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
+        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
       </c>
       <c r="L76" t="str">
-        <v>Van y Vienen - El Fantasma</v>
+        <v>Andamos Ready - Los Tucanes de Tijuana</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>No Vuelvas</v>
+        <v>Van y Vienen</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
+        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-10</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>No Vuelvas - Single</v>
+        <v>Van y Vienen - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:46</v>
+        <v>2:46</v>
       </c>
       <c r="H77" t="str">
-        <v>Majo Aguilar</v>
+        <v>El Fantasma</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
+        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
+        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
       </c>
       <c r="L77" t="str">
-        <v>No Vuelvas - Majo Aguilar</v>
+        <v>Van y Vienen - El Fantasma</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>RUNNIN</v>
+        <v>No Vuelvas</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/runnin/1886581872</v>
+        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-10</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>RUNNIN - Single</v>
+        <v>No Vuelvas - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:40</v>
+        <v>3:46</v>
       </c>
       <c r="H78" t="str">
-        <v>RUA YOUNG</v>
+        <v>Majo Aguilar</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
+        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/runnin/1886581868</v>
+        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
       </c>
       <c r="L78" t="str">
-        <v>RUNNIN - RUA YOUNG</v>
+        <v>No Vuelvas - Majo Aguilar</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Talk You Through It</v>
+        <v>RUNNIN</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
+        <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-10</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Talk You Through It - Single</v>
+        <v>RUNNIN - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:33</v>
+        <v>2:40</v>
       </c>
       <c r="H79" t="str">
-        <v>Kenyon Dixon</v>
+        <v>RUA YOUNG</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
+        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
+        <v>https://music.apple.com/us/album/runnin/1886581868</v>
       </c>
       <c r="L79" t="str">
-        <v>Talk You Through It - Kenyon Dixon</v>
+        <v>RUNNIN - RUA YOUNG</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Partners in Crime</v>
+        <v>Talk You Through It</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
+        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-10</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Born to Kill</v>
+        <v>Talk You Through It - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:50</v>
+        <v>3:33</v>
       </c>
       <c r="H80" t="str">
-        <v>Social Distortion</v>
+        <v>Kenyon Dixon</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
+        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
       </c>
       <c r="L80" t="str">
-        <v>Partners in Crime - Social Distortion</v>
+        <v>Talk You Through It - Kenyon Dixon</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Change your mind</v>
+        <v>Partners in Crime</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
+        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-10</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Change your mind - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G81" t="str">
-        <v>3:21</v>
+        <v>3:50</v>
       </c>
       <c r="H81" t="str">
-        <v>Casper Sage</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
+        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
       </c>
       <c r="L81" t="str">
-        <v>Change your mind - Casper Sage</v>
+        <v>Partners in Crime - Social Distortion</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Bones to Ashes, Dark to Light</v>
+        <v>Change your mind</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
+        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-10</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Bones to Ashes, Dark to Light - Single</v>
+        <v>Change your mind - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:29</v>
+        <v>3:21</v>
       </c>
       <c r="H82" t="str">
-        <v>The Franklin Electric</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
+        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
       </c>
       <c r="L82" t="str">
-        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
+        <v>Change your mind - Casper Sage</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Venus in the Zinnia</v>
+        <v>Bones to Ashes, Dark to Light</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
+        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-10</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Train on the Island</v>
+        <v>Bones to Ashes, Dark to Light - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:17</v>
+        <v>3:29</v>
       </c>
       <c r="H83" t="str">
-        <v>Aldous Harding</v>
+        <v>The Franklin Electric</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
+        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
+        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
       </c>
       <c r="L83" t="str">
-        <v>Venus in the Zinnia - Aldous Harding</v>
+        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Lover</v>
+        <v>Venus in the Zinnia</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/lover/1878758405</v>
+        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-10</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Lover - Single</v>
+        <v>Train on the Island</v>
       </c>
       <c r="G84" t="str">
-        <v>3:26</v>
+        <v>3:17</v>
       </c>
       <c r="H84" t="str">
-        <v>Juke Ross</v>
+        <v>Aldous Harding</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
+        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/lover/1878758400</v>
+        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
       </c>
       <c r="L84" t="str">
-        <v>Lover - Juke Ross</v>
+        <v>Venus in the Zinnia - Aldous Harding</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>pink moon</v>
+        <v>Lover</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
+        <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-10</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Lover - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H85" t="str">
-        <v>runo plum</v>
+        <v>Juke Ross</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
+        <v>https://music.apple.com/us/album/lover/1878758400</v>
       </c>
       <c r="L85" t="str">
-        <v>pink moon - runo plum</v>
+        <v>Lover - Juke Ross</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Summer</v>
+        <v>pink moon</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/summer/1884646207</v>
+        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-10</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Summer - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G86" t="str">
         <v>3:21</v>
       </c>
       <c r="H86" t="str">
-        <v>Tasha</v>
+        <v>runo plum</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/summer/1884645989</v>
+        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
       </c>
       <c r="L86" t="str">
-        <v>Summer - Tasha</v>
+        <v>pink moon - runo plum</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Lizzie mcguire</v>
+        <v>Summer</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
+        <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-10</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Tearless, thoughtless</v>
+        <v>Summer - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>4:20</v>
+        <v>3:21</v>
       </c>
       <c r="H87" t="str">
-        <v>Nara's Room</v>
+        <v>Tasha</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
+        <v>https://music.apple.com/us/album/summer/1884645989</v>
       </c>
       <c r="L87" t="str">
-        <v>Lizzie mcguire - Nara's Room</v>
+        <v>Summer - Tasha</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Fabienk</v>
+        <v>Lizzie mcguire</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
+        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-10</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Vol.II</v>
+        <v>Tearless, thoughtless</v>
       </c>
       <c r="G88" t="str">
-        <v>6:31</v>
+        <v>4:20</v>
       </c>
       <c r="H88" t="str">
-        <v>Angine de Poitrine</v>
+        <v>Nara's Room</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
+        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
+        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
       </c>
       <c r="L88" t="str">
-        <v>Fabienk - Angine de Poitrine</v>
+        <v>Lizzie mcguire - Nara's Room</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>My Girl</v>
+        <v>Fabienk</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
+        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-10</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Soren - EP</v>
+        <v>Vol.II</v>
       </c>
       <c r="G89" t="str">
-        <v>3:45</v>
+        <v>6:31</v>
       </c>
       <c r="H89" t="str">
-        <v>Orca</v>
+        <v>Angine de Poitrine</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
+        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
       </c>
       <c r="L89" t="str">
-        <v>My Girl - Orca</v>
+        <v>Fabienk - Angine de Poitrine</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Bone Structure</v>
+        <v>My Girl</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
+        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-10</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Bone Structure - Single</v>
+        <v>Soren - EP</v>
       </c>
       <c r="G90" t="str">
-        <v>3:01</v>
+        <v>3:45</v>
       </c>
       <c r="H90" t="str">
-        <v>Dolder</v>
+        <v>Orca</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
+        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
       </c>
       <c r="L90" t="str">
-        <v>Bone Structure - Dolder</v>
+        <v>My Girl - Orca</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Turning Into Us</v>
+        <v>Bone Structure</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
+        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-10</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Turning Into Us - Single</v>
+        <v>Bone Structure - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H91" t="str">
-        <v>Rhys Rutherford</v>
+        <v>Dolder</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
+        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
       </c>
       <c r="L91" t="str">
-        <v>Turning Into Us - Rhys Rutherford</v>
+        <v>Bone Structure - Dolder</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Bother Me (feat. Victony)</v>
+        <v>Turning Into Us</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
+        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-10</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Bother Me (feat. Victony) - Single</v>
+        <v>Turning Into Us - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:00</v>
+        <v>3:30</v>
       </c>
       <c r="H92" t="str">
-        <v>Osé</v>
+        <v>Rhys Rutherford</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
+        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
+        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
       </c>
       <c r="L92" t="str">
-        <v>Bother Me (feat. Victony) - Osé</v>
+        <v>Turning Into Us - Rhys Rutherford</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Fright</v>
+        <v>Bother Me (feat. Victony)</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/fright/1890396431</v>
+        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-10</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Fright - Single</v>
+        <v>Bother Me (feat. Victony) - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>2:25</v>
+        <v>3:00</v>
       </c>
       <c r="H93" t="str">
-        <v>Creepy Nuts</v>
+        <v>Osé</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
+        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/fright/1890396429</v>
+        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
       </c>
       <c r="L93" t="str">
-        <v>Fright - Creepy Nuts</v>
+        <v>Bother Me (feat. Victony) - Osé</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Smoking In Bed</v>
+        <v>Fright</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
+        <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-10</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Smoking In Bed - Single</v>
+        <v>Fright - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:24</v>
+        <v>2:25</v>
       </c>
       <c r="H94" t="str">
-        <v>The Bends</v>
+        <v>Creepy Nuts</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
+        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
+        <v>https://music.apple.com/us/album/fright/1890396429</v>
       </c>
       <c r="L94" t="str">
-        <v>Smoking In Bed - The Bends</v>
+        <v>Fright - Creepy Nuts</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>The Dissonant Void</v>
+        <v>Smoking In Bed</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-10</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Smoking In Bed - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>2:47</v>
+        <v>3:24</v>
       </c>
       <c r="H95" t="str">
-        <v>At The Gates</v>
+        <v>The Bends</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
       </c>
       <c r="L95" t="str">
-        <v>The Dissonant Void - At The Gates</v>
+        <v>Smoking In Bed - The Bends</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Nine Days Of Rain</v>
+        <v>The Dissonant Void</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-10</v>
@@ -4023,68 +4023,106 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G96" t="str">
-        <v>3:51</v>
+        <v>2:47</v>
       </c>
       <c r="H96" t="str">
-        <v>Melvins</v>
+        <v>At The Gates</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
       </c>
       <c r="L96" t="str">
-        <v>Nine Days Of Rain - Melvins</v>
+        <v>The Dissonant Void - At The Gates</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
+        <v>Nine Days Of Rain</v>
+      </c>
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
+        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v>Savage Imperial Death March</v>
+      </c>
+      <c r="G97" t="str">
+        <v>3:51</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Melvins</v>
+      </c>
+      <c r="I97" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J97" t="str">
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
+      </c>
+      <c r="K97" t="str">
+        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Nine Days Of Rain - Melvins</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>Invocation of the Dreamer</v>
       </c>
-      <c r="B97" t="str">
-        <v/>
-      </c>
-      <c r="C97" t="str">
+      <c r="B98" t="str">
+        <v/>
+      </c>
+      <c r="C98" t="str">
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
-      <c r="D97" t="str">
-        <v>2026-04-10</v>
-      </c>
-      <c r="E97" t="str">
-        <v/>
-      </c>
-      <c r="F97" t="str">
+      <c r="D98" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="G97" t="str">
+      <c r="G98" t="str">
         <v>4:46</v>
       </c>
-      <c r="H97" t="str">
+      <c r="H98" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="I97" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J97" t="str">
+      <c r="I98" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J98" t="str">
         <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
       </c>
-      <c r="K97" t="str">
+      <c r="K98" t="str">
         <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
       </c>
-      <c r="L97" t="str">
+      <c r="L98" t="str">
         <v>Invocation of the Dreamer - Khemmis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
@@ -474,7 +474,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Runway</v>
+        <v>RUNWAY</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Runway - Single</v>
+        <v>RUNWAY - Single</v>
       </c>
       <c r="G3" t="str">
         <v>2:51</v>
@@ -507,7 +507,7 @@
         <v>https://music.apple.com/us/album/runway/1891472590</v>
       </c>
       <c r="L3" t="str">
-        <v>Runway - Lady Gaga</v>
+        <v>RUNWAY - Lady Gaga</v>
       </c>
     </row>
     <row r="4">
@@ -1480,7 +1480,7 @@
         <v>Obvious - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:05</v>
+        <v>3:06</v>
       </c>
       <c r="H29" t="str">
         <v>Chris Brown</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/runway/1891472591</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/madwoman/1873116853</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/stuck/1875303118</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/echo/1891104992</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E98" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/runway/1891472591</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/madwoman/1873116853</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/stuck/1875303118</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/echo/1891104992</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E98" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/runway/1891472591</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/madwoman/1873116853</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/stuck/1875303118</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/echo/1891104992</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E98" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L100"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Bottom Of Your Boots</v>
+        <v>i just get worse</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-13</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Dandelion</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>3:19</v>
+        <v>3:25</v>
       </c>
       <c r="H2" t="str">
-        <v>Ella Langley</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/bottom-of-your-boots/1869436835</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L2" t="str">
-        <v>Bottom Of Your Boots - Ella Langley</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>RUNWAY</v>
+        <v>Bottom Of Your Boots</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/runway/1891472591</v>
+        <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-13</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>RUNWAY - Single</v>
+        <v>Dandelion</v>
       </c>
       <c r="G3" t="str">
-        <v>2:51</v>
+        <v>3:19</v>
       </c>
       <c r="H3" t="str">
-        <v>Lady Gaga</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/runway/1891472590</v>
+        <v>https://music.apple.com/us/album/bottom-of-your-boots/1869436835</v>
       </c>
       <c r="L3" t="str">
-        <v>RUNWAY - Lady Gaga</v>
+        <v>Bottom Of Your Boots - Ella Langley</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Back and Forth (feat. Missy Elliott)</v>
+        <v>RUNWAY</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
+        <v>https://music.apple.com/us/song/runway/1891472591</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-13</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>Kehlani</v>
+        <v>RUNWAY - Single</v>
       </c>
       <c r="G4" t="str">
-        <v>3:34</v>
+        <v>2:51</v>
       </c>
       <c r="H4" t="str">
-        <v>Kehlani</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/back-and-forth-feat-missy-elliott/1885055310</v>
+        <v>https://music.apple.com/us/album/runway/1891472590</v>
       </c>
       <c r="L4" t="str">
-        <v>Back and Forth (feat. Missy Elliott) - Kehlani</v>
+        <v>RUNWAY - Lady Gaga</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Mr. Know It All</v>
+        <v>Back and Forth (feat. Missy Elliott)</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
+        <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-13</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Mr. Know It All - Single</v>
+        <v>Kehlani</v>
       </c>
       <c r="G5" t="str">
-        <v>3:18</v>
+        <v>3:34</v>
       </c>
       <c r="H5" t="str">
-        <v>Teddy Swims</v>
+        <v>Kehlani</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/teddy-swims/1462541757</v>
+        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/mr-know-it-all/1889361601</v>
+        <v>https://music.apple.com/us/album/back-and-forth-feat-missy-elliott/1885055310</v>
       </c>
       <c r="L5" t="str">
-        <v>Mr. Know It All - Teddy Swims</v>
+        <v>Back and Forth (feat. Missy Elliott) - Kehlani</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Bad Angel</v>
+        <v>Mr. Know It All</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
+        <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-13</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Bad Angel - Single</v>
+        <v>Mr. Know It All - Single</v>
       </c>
       <c r="G6" t="str">
-        <v>2:33</v>
+        <v>3:18</v>
       </c>
       <c r="H6" t="str">
-        <v>Anyma</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
+        <v>https://music.apple.com/us/artist/teddy-swims/1462541757</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/bad-angel/1889611955</v>
+        <v>https://music.apple.com/us/album/mr-know-it-all/1889361601</v>
       </c>
       <c r="L6" t="str">
-        <v>Bad Angel - Anyma</v>
+        <v>Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Step (feat. Swizz Beatz)</v>
+        <v>Bad Angel</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
+        <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-13</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>10 Til' Midnight</v>
+        <v>Bad Angel - Single</v>
       </c>
       <c r="G7" t="str">
-        <v>3:34</v>
+        <v>2:33</v>
       </c>
       <c r="H7" t="str">
-        <v>Snoop Dogg</v>
+        <v>Anyma</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/snoop-dogg/21769</v>
+        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/step-feat-swizz-beatz/1886977935</v>
+        <v>https://music.apple.com/us/album/bad-angel/1889611955</v>
       </c>
       <c r="L7" t="str">
-        <v>Step (feat. Swizz Beatz) - Snoop Dogg</v>
+        <v>Bad Angel - Anyma</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Sweet Hallelujah</v>
+        <v>Step (feat. Swizz Beatz)</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
+        <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-13</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Sweet Hallelujah - Single</v>
+        <v>10 Til' Midnight</v>
       </c>
       <c r="G8" t="str">
-        <v>3:02</v>
+        <v>3:34</v>
       </c>
       <c r="H8" t="str">
-        <v>Royel Otis</v>
+        <v>Snoop Dogg</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/royel-otis/1537647213</v>
+        <v>https://music.apple.com/us/artist/snoop-dogg/21769</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/sweet-hallelujah/1886800353</v>
+        <v>https://music.apple.com/us/album/step-feat-swizz-beatz/1886977935</v>
       </c>
       <c r="L8" t="str">
-        <v>Sweet Hallelujah - Royel Otis</v>
+        <v>Step (feat. Swizz Beatz) - Snoop Dogg</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Beauty Pageant</v>
+        <v>Sweet Hallelujah</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
+        <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-13</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Cruel World</v>
+        <v>Sweet Hallelujah - Single</v>
       </c>
       <c r="G9" t="str">
-        <v>3:15</v>
+        <v>3:02</v>
       </c>
       <c r="H9" t="str">
-        <v>Holly Humberstone</v>
+        <v>Royel Otis</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/royel-otis/1537647213</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/beauty-pageant/1859629846</v>
+        <v>https://music.apple.com/us/album/sweet-hallelujah/1886800353</v>
       </c>
       <c r="L9" t="str">
-        <v>Beauty Pageant - Holly Humberstone</v>
+        <v>Sweet Hallelujah - Royel Otis</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>PINKY UP</v>
+        <v>Beauty Pageant</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
+        <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-13</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>PINKY UP - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G10" t="str">
-        <v>2:11</v>
+        <v>3:15</v>
       </c>
       <c r="H10" t="str">
-        <v>KATSEYE</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/katseye/1754284416</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/pinky-up/1888235065</v>
+        <v>https://music.apple.com/us/album/beauty-pageant/1859629846</v>
       </c>
       <c r="L10" t="str">
-        <v>PINKY UP - KATSEYE</v>
+        <v>Beauty Pageant - Holly Humberstone</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Sick Of Love</v>
+        <v>PINKY UP</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
+        <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-13</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>The Afterparty</v>
+        <v>PINKY UP - Single</v>
       </c>
       <c r="G11" t="str">
-        <v>3:36</v>
+        <v>2:11</v>
       </c>
       <c r="H11" t="str">
-        <v>Lykke Li</v>
+        <v>KATSEYE</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/katseye/1754284416</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/sick-of-love/1857952252</v>
+        <v>https://music.apple.com/us/album/pinky-up/1888235065</v>
       </c>
       <c r="L11" t="str">
-        <v>Sick Of Love - Lykke Li</v>
+        <v>PINKY UP - KATSEYE</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ember</v>
+        <v>Sick Of Love</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/ember/1880484164</v>
+        <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-13</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G12" t="str">
-        <v>3:25</v>
+        <v>3:36</v>
       </c>
       <c r="H12" t="str">
-        <v>Iceage</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/ember/1880484160</v>
+        <v>https://music.apple.com/us/album/sick-of-love/1857952252</v>
       </c>
       <c r="L12" t="str">
-        <v>Ember - Iceage</v>
+        <v>Sick Of Love - Lykke Li</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Turnaround</v>
+        <v>Ember</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
+        <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-13</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Turnaround / I'm Hooked - Single</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G13" t="str">
-        <v>3:14</v>
+        <v>3:25</v>
       </c>
       <c r="H13" t="str">
-        <v>54 Ultra</v>
+        <v>Iceage</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
+        <v>https://music.apple.com/us/album/ember/1880484160</v>
       </c>
       <c r="L13" t="str">
-        <v>Turnaround - 54 Ultra</v>
+        <v>Ember - Iceage</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Madwoman</v>
+        <v>Turnaround</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
+        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-13</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Turnaround / I'm Hooked - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>3:59</v>
+        <v>3:14</v>
       </c>
       <c r="H14" t="str">
-        <v>Laufey</v>
+        <v>54 Ultra</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
+        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
       </c>
       <c r="L14" t="str">
-        <v>Madwoman - Laufey</v>
+        <v>Turnaround - 54 Ultra</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Come Clean (Mine)</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-13</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Come Clean (Mine) - Single</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>3:33</v>
+        <v>3:05</v>
       </c>
       <c r="H15" t="str">
-        <v>Hilary Duff</v>
+        <v>Labrinth</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L15" t="str">
-        <v>Come Clean (Mine) - Hilary Duff</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>One of Them</v>
+        <v>Madwoman</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
+        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-13</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>One of Them - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G16" t="str">
-        <v>3:24</v>
+        <v>3:59</v>
       </c>
       <c r="H16" t="str">
-        <v>DJ Khaled</v>
+        <v>Laufey</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
+        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
       </c>
       <c r="L16" t="str">
-        <v>One of Them - DJ Khaled</v>
+        <v>Madwoman - Laufey</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>Come Clean (Mine)</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
+        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-13</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>Come Clean (Mine) - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>2:49</v>
+        <v>3:33</v>
       </c>
       <c r="H17" t="str">
-        <v>Bossman Dlow</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
+        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
       </c>
       <c r="L17" t="str">
-        <v>Chicken Talkin Bastard - Bossman Dlow</v>
+        <v>Come Clean (Mine) - Hilary Duff</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>stuck</v>
+        <v>One of Them</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/stuck/1875303118</v>
+        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-13</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>ghosted - EP</v>
+        <v>One of Them - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>2:41</v>
+        <v>3:24</v>
       </c>
       <c r="H18" t="str">
-        <v>Saint Harison</v>
+        <v>DJ Khaled</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/stuck/1875302904</v>
+        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
       </c>
       <c r="L18" t="str">
-        <v>stuck - Saint Harison</v>
+        <v>One of Them - DJ Khaled</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>De Lejitos</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
+        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-13</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>De Lejitos - Single</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="G19" t="str">
-        <v>3:27</v>
+        <v>2:49</v>
       </c>
       <c r="H19" t="str">
-        <v>Jay Wheeler</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
+        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
       </c>
       <c r="L19" t="str">
-        <v>De Lejitos - Jay Wheeler</v>
+        <v>Chicken Talkin Bastard - Bossman Dlow</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Echo</v>
+        <v>stuck</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/echo/1891104992</v>
+        <v>https://music.apple.com/us/song/stuck/1875303118</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-13</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Echo - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G20" t="str">
-        <v>3:39</v>
+        <v>2:41</v>
       </c>
       <c r="H20" t="str">
-        <v>The Chainsmokers</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/echo/1891104991</v>
+        <v>https://music.apple.com/us/album/stuck/1875302904</v>
       </c>
       <c r="L20" t="str">
-        <v>Echo - The Chainsmokers</v>
+        <v>stuck - Saint Harison</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Where We Go</v>
+        <v>De Lejitos</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
+        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-13</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Where We Go - Single</v>
+        <v>De Lejitos - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>3:16</v>
+        <v>3:27</v>
       </c>
       <c r="H21" t="str">
-        <v>Marshmello</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
+        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
       </c>
       <c r="L21" t="str">
-        <v>Where We Go - Marshmello</v>
+        <v>De Lejitos - Jay Wheeler</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Te hacen falta dos</v>
+        <v>Echo</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
+        <v>https://music.apple.com/us/song/echo/1891104992</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-13</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Apambichao</v>
+        <v>Echo - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>2:41</v>
+        <v>3:39</v>
       </c>
       <c r="H22" t="str">
-        <v>Manuel Turizo</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
+        <v>https://music.apple.com/us/album/echo/1891104991</v>
       </c>
       <c r="L22" t="str">
-        <v>Te hacen falta dos - Manuel Turizo</v>
+        <v>Echo - The Chainsmokers</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Of All People</v>
+        <v>Where We Go</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
+        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-13</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Where We Go - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>2:34</v>
+        <v>3:16</v>
       </c>
       <c r="H23" t="str">
-        <v>Foo Fighters</v>
+        <v>Marshmello</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
+        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
       </c>
       <c r="L23" t="str">
-        <v>Of All People - Foo Fighters</v>
+        <v>Where We Go - Marshmello</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Waves of You</v>
+        <v>Te hacen falta dos</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
+        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-13</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Waves of You - Single</v>
+        <v>Apambichao</v>
       </c>
       <c r="G24" t="str">
-        <v>3:15</v>
+        <v>2:41</v>
       </c>
       <c r="H24" t="str">
-        <v>After Hours</v>
+        <v>Manuel Turizo</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
+        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
+        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
       </c>
       <c r="L24" t="str">
-        <v>Waves of You - After Hours</v>
+        <v>Te hacen falta dos - Manuel Turizo</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>idea 1</v>
+        <v>Of All People</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
+        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-13</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>idea 1 - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G25" t="str">
-        <v>3:25</v>
+        <v>2:34</v>
       </c>
       <c r="H25" t="str">
-        <v>Kelela</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
+        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
       </c>
       <c r="L25" t="str">
-        <v>idea 1 - Kelela</v>
+        <v>Of All People - Foo Fighters</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Attitude</v>
+        <v>Waves of You</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/attitude/1840517116</v>
+        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-13</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Sweat</v>
+        <v>Waves of You - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>3:13</v>
+        <v>3:15</v>
       </c>
       <c r="H26" t="str">
-        <v>Melanie C</v>
+        <v>After Hours</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/attitude/1840516706</v>
+        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
       </c>
       <c r="L26" t="str">
-        <v>Attitude - Melanie C</v>
+        <v>Waves of You - After Hours</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Carrie Bradshaw</v>
+        <v>idea 1</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
+        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-13</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Carrie Bradshaw - Single</v>
+        <v>idea 1 - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:54</v>
+        <v>3:25</v>
       </c>
       <c r="H27" t="str">
-        <v>Kylie Cantrall</v>
+        <v>Kelela</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
+        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
       </c>
       <c r="L27" t="str">
-        <v>Carrie Bradshaw - Kylie Cantrall</v>
+        <v>idea 1 - Kelela</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Work</v>
+        <v>Attitude</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/work/1885916583</v>
+        <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-13</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Work - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G28" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H28" t="str">
-        <v>Pitbull</v>
+        <v>Melanie C</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/work/1885916578</v>
+        <v>https://music.apple.com/us/album/attitude/1840516706</v>
       </c>
       <c r="L28" t="str">
-        <v>Work - Pitbull</v>
+        <v>Attitude - Melanie C</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Obvious</v>
+        <v>Carrie Bradshaw</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/obvious/1891759136</v>
+        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-13</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Obvious - Single</v>
+        <v>Carrie Bradshaw - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:06</v>
+        <v>2:54</v>
       </c>
       <c r="H29" t="str">
-        <v>Chris Brown</v>
+        <v>Kylie Cantrall</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/obvious/1891759134</v>
+        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
       </c>
       <c r="L29" t="str">
-        <v>Obvious - Chris Brown</v>
+        <v>Carrie Bradshaw - Kylie Cantrall</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>As Time Goes By</v>
+        <v>Work</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
+        <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-13</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>CINEMATIC</v>
+        <v>Work - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>5:06</v>
+        <v>2:51</v>
       </c>
       <c r="H30" t="str">
-        <v>Josh Groban</v>
+        <v>Pitbull</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
+        <v>https://music.apple.com/us/album/work/1885916578</v>
       </c>
       <c r="L30" t="str">
-        <v>As Time Goes By - Josh Groban</v>
+        <v>Work - Pitbull</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>My Mess</v>
+        <v>Obvious</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
+        <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-13</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>Obvious - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>3:11</v>
+        <v>3:06</v>
       </c>
       <c r="H31" t="str">
-        <v>Myles Smith</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
+        <v>https://music.apple.com/us/album/obvious/1891759134</v>
       </c>
       <c r="L31" t="str">
-        <v>My Mess - Myles Smith</v>
+        <v>Obvious - Chris Brown</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Going Shopping</v>
+        <v>As Time Goes By</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
+        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-13</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Reality Awaits</v>
+        <v>CINEMATIC</v>
       </c>
       <c r="G32" t="str">
-        <v>4:21</v>
+        <v>5:06</v>
       </c>
       <c r="H32" t="str">
-        <v>The Strokes</v>
+        <v>Josh Groban</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
+        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
       </c>
       <c r="L32" t="str">
-        <v>Going Shopping - The Strokes</v>
+        <v>As Time Goes By - Josh Groban</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Choka Choka</v>
+        <v>My Mess</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
+        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-13</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Choka Choka - Single</v>
+        <v>My Mess, My Heart, My Life.</v>
       </c>
       <c r="G33" t="str">
-        <v>2:11</v>
+        <v>3:11</v>
       </c>
       <c r="H33" t="str">
-        <v>Anitta</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
+        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
       </c>
       <c r="L33" t="str">
-        <v>Choka Choka - Anitta</v>
+        <v>My Mess - Myles Smith</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>side slider</v>
+        <v>Going Shopping</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
+        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-13</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G34" t="str">
-        <v>3:47</v>
+        <v>4:21</v>
       </c>
       <c r="H34" t="str">
-        <v>Isaia Huron</v>
+        <v>The Strokes</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
+        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
       </c>
       <c r="L34" t="str">
-        <v>side slider - Isaia Huron</v>
+        <v>Going Shopping - The Strokes</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Woman I Am</v>
+        <v>Choka Choka</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
+        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-13</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>SE9</v>
+        <v>Choka Choka - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:31</v>
+        <v>2:11</v>
       </c>
       <c r="H35" t="str">
-        <v>Skye Newman</v>
+        <v>Anitta</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/woman-i-am/1890182220</v>
+        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
       </c>
       <c r="L35" t="str">
-        <v>Woman I Am - Skye Newman</v>
+        <v>Choka Choka - Anitta</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Bubee</v>
+        <v>side slider</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/bubee/1885450942</v>
+        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-13</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Bubee - Single</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G36" t="str">
-        <v>3:02</v>
+        <v>3:47</v>
       </c>
       <c r="H36" t="str">
-        <v>ILLIT</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/bubee/1885450328</v>
+        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
       </c>
       <c r="L36" t="str">
-        <v>Bubee - ILLIT</v>
+        <v>side slider - Isaia Huron</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Good Morning</v>
+        <v>Woman I Am</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
+        <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-13</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>24</v>
+        <v>SE9</v>
       </c>
       <c r="G37" t="str">
-        <v>3:02</v>
+        <v>3:31</v>
       </c>
       <c r="H37" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
+        <v>https://music.apple.com/us/album/woman-i-am/1890182220</v>
       </c>
       <c r="L37" t="str">
-        <v>Good Morning - Alexis Ffrench</v>
+        <v>Woman I Am - Skye Newman</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Positano</v>
+        <v>Bubee</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/positano/1886736661</v>
+        <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-13</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>Bubee - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>3:27</v>
+        <v>3:02</v>
       </c>
       <c r="H38" t="str">
-        <v>Stephan Moccio</v>
+        <v>ILLIT</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/positano/1886736650</v>
+        <v>https://music.apple.com/us/album/bubee/1885450328</v>
       </c>
       <c r="L38" t="str">
-        <v>Positano - Stephan Moccio</v>
+        <v>Bubee - ILLIT</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>sophie</v>
+        <v>Good Morning</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/sophie/1887348036</v>
+        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-13</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>notes from the in between - EP</v>
+        <v>24</v>
       </c>
       <c r="G39" t="str">
-        <v>2:36</v>
+        <v>3:02</v>
       </c>
       <c r="H39" t="str">
-        <v>kenzie</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/sophie/1887348032</v>
+        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
       </c>
       <c r="L39" t="str">
-        <v>sophie - kenzie</v>
+        <v>Good Morning - Alexis Ffrench</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>kiss goodbye</v>
+        <v>Positano</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
+        <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-13</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>kiss goodbye / brb - Single</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G40" t="str">
-        <v>2:43</v>
+        <v>3:27</v>
       </c>
       <c r="H40" t="str">
-        <v>The Two Lips</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
+        <v>https://music.apple.com/us/album/positano/1886736650</v>
       </c>
       <c r="L40" t="str">
-        <v>kiss goodbye - The Two Lips</v>
+        <v>Positano - Stephan Moccio</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENTRÉGAME</v>
+        <v>sophie</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
+        <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-13</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>RADIO VENEZUELA</v>
+        <v>notes from the in between - EP</v>
       </c>
       <c r="G41" t="str">
-        <v>3:08</v>
+        <v>2:36</v>
       </c>
       <c r="H41" t="str">
-        <v>Chino &amp; Nacho</v>
+        <v>kenzie</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
+        <v>https://music.apple.com/us/album/sophie/1887348032</v>
       </c>
       <c r="L41" t="str">
-        <v>ENTRÉGAME - Chino &amp; Nacho</v>
+        <v>sophie - kenzie</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>EL SENTRITA</v>
+        <v>kiss goodbye</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
+        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-13</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>ETERNO</v>
+        <v>kiss goodbye / brb - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>2:57</v>
+        <v>2:43</v>
       </c>
       <c r="H42" t="str">
-        <v>Calle 24</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
+        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
       </c>
       <c r="L42" t="str">
-        <v>EL SENTRITA - Calle 24</v>
+        <v>kiss goodbye - The Two Lips</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>SOMETHING IN THE WATER</v>
+        <v>ENTRÉGAME</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
+        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-13</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>DAWN PATROL</v>
+        <v>RADIO VENEZUELA</v>
       </c>
       <c r="G43" t="str">
-        <v>2:39</v>
+        <v>3:08</v>
       </c>
       <c r="H43" t="str">
-        <v>PARTY WAVE</v>
+        <v>Chino &amp; Nacho</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
+        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
+        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
       </c>
       <c r="L43" t="str">
-        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
+        <v>ENTRÉGAME - Chino &amp; Nacho</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Formation</v>
+        <v>EL SENTRITA</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/formation/1882714068</v>
+        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-13</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Formation - Single</v>
+        <v>ETERNO</v>
       </c>
       <c r="G44" t="str">
-        <v>2:36</v>
+        <v>2:57</v>
       </c>
       <c r="H44" t="str">
-        <v>Adekunle Gold</v>
+        <v>Calle 24</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/formation/1882714060</v>
+        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
       </c>
       <c r="L44" t="str">
-        <v>Formation - Adekunle Gold</v>
+        <v>EL SENTRITA - Calle 24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Who Will You Follow</v>
+        <v>SOMETHING IN THE WATER</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
+        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-13</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Sanctuary</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G45" t="str">
-        <v>3:55</v>
+        <v>2:39</v>
       </c>
       <c r="H45" t="str">
-        <v>Evanescence</v>
+        <v>PARTY WAVE</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
+        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
       </c>
       <c r="L45" t="str">
-        <v>Who Will You Follow - Evanescence</v>
+        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>That's When You Know</v>
+        <v>Formation</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
+        <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-13</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>That's When You Know - Single</v>
+        <v>Formation - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:13</v>
+        <v>2:36</v>
       </c>
       <c r="H46" t="str">
-        <v>Kygo</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
+        <v>https://music.apple.com/us/album/formation/1882714060</v>
       </c>
       <c r="L46" t="str">
-        <v>That's When You Know - Kygo</v>
+        <v>Formation - Adekunle Gold</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Drinking Game</v>
+        <v>Who Will You Follow</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
+        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-13</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Drinking Game - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G47" t="str">
-        <v>2:50</v>
+        <v>3:55</v>
       </c>
       <c r="H47" t="str">
-        <v>Warren Zeiders</v>
+        <v>Evanescence</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
+        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
       </c>
       <c r="L47" t="str">
-        <v>Drinking Game - Warren Zeiders</v>
+        <v>Who Will You Follow - Evanescence</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Anything But Me</v>
+        <v>That's When You Know</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
+        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-13</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>In The Feeling</v>
+        <v>That's When You Know - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>4:59</v>
+        <v>3:13</v>
       </c>
       <c r="H48" t="str">
-        <v>Owen Riegling</v>
+        <v>Kygo</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
+        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
       </c>
       <c r="L48" t="str">
-        <v>Anything But Me - Owen Riegling</v>
+        <v>That's When You Know - Kygo</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>American Dream</v>
+        <v>Drinking Game</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
+        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-13</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>American Dream - Single</v>
+        <v>Drinking Game - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>4:27</v>
+        <v>2:50</v>
       </c>
       <c r="H49" t="str">
-        <v>Alabama Shakes</v>
+        <v>Warren Zeiders</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
+        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
+        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
       </c>
       <c r="L49" t="str">
-        <v>American Dream - Alabama Shakes</v>
+        <v>Drinking Game - Warren Zeiders</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Already There</v>
+        <v>Anything But Me</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/already-there/1866700770</v>
+        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-13</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Victory Garden</v>
+        <v>In The Feeling</v>
       </c>
       <c r="G50" t="str">
-        <v>3:50</v>
+        <v>4:59</v>
       </c>
       <c r="H50" t="str">
-        <v>Young the Giant</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/already-there/1866700309</v>
+        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
       </c>
       <c r="L50" t="str">
-        <v>Already There - Young the Giant</v>
+        <v>Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ROCK BOTTOM</v>
+        <v>American Dream</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
+        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-13</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>KINDA HARD</v>
+        <v>American Dream - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>2:47</v>
+        <v>4:27</v>
       </c>
       <c r="H51" t="str">
-        <v>Bilmuri</v>
+        <v>Alabama Shakes</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
+        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
       </c>
       <c r="L51" t="str">
-        <v>ROCK BOTTOM - Bilmuri</v>
+        <v>American Dream - Alabama Shakes</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Alone For A Year</v>
+        <v>Already There</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
+        <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-13</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Joy Next Door</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G52" t="str">
-        <v>3:22</v>
+        <v>3:50</v>
       </c>
       <c r="H52" t="str">
-        <v>The Maine</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
+        <v>https://music.apple.com/us/album/already-there/1866700309</v>
       </c>
       <c r="L52" t="str">
-        <v>Alone For A Year - The Maine</v>
+        <v>Already There - Young the Giant</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Bring Home My Man</v>
+        <v>ROCK BOTTOM</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-13</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G53" t="str">
-        <v>4:22</v>
+        <v>2:47</v>
       </c>
       <c r="H53" t="str">
-        <v>Maya Hawke</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
       </c>
       <c r="L53" t="str">
-        <v>Bring Home My Man - Maya Hawke</v>
+        <v>ROCK BOTTOM - Bilmuri</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SUPERMAN</v>
+        <v>Alone For A Year</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/superman/1890027996</v>
+        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-13</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>SUPERMAN - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G54" t="str">
-        <v>3:24</v>
+        <v>3:22</v>
       </c>
       <c r="H54" t="str">
-        <v>South Arcade</v>
+        <v>The Maine</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/superman/1890027995</v>
+        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
       </c>
       <c r="L54" t="str">
-        <v>SUPERMAN - South Arcade</v>
+        <v>Alone For A Year - The Maine</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>1989</v>
+        <v>Bring Home My Man</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/1989/1887250155</v>
+        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-13</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>1989 - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G55" t="str">
-        <v>2:34</v>
+        <v>4:22</v>
       </c>
       <c r="H55" t="str">
-        <v>Nightly</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/1989/1887250154</v>
+        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
       </c>
       <c r="L55" t="str">
-        <v>1989 - Nightly</v>
+        <v>Bring Home My Man - Maya Hawke</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>waste your pain</v>
+        <v>SUPERMAN</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
+        <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-13</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>waste your pain - Single</v>
+        <v>SUPERMAN - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>2:23</v>
+        <v>3:24</v>
       </c>
       <c r="H56" t="str">
-        <v>Cruz Beckham</v>
+        <v>South Arcade</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
+        <v>https://music.apple.com/us/album/superman/1890027995</v>
       </c>
       <c r="L56" t="str">
-        <v>waste your pain - Cruz Beckham</v>
+        <v>SUPERMAN - South Arcade</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Strangers</v>
+        <v>1989</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/strangers/1883252372</v>
+        <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-13</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>F**k, Marry, Kill</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:44</v>
+        <v>2:34</v>
       </c>
       <c r="H57" t="str">
-        <v>Tink</v>
+        <v>Nightly</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/strangers/1883252371</v>
+        <v>https://music.apple.com/us/album/1989/1887250154</v>
       </c>
       <c r="L57" t="str">
-        <v>Strangers - Tink</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Right In Front Of Me</v>
+        <v>waste your pain</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
+        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-13</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Right In Front Of Me - Single</v>
+        <v>waste your pain - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>2:45</v>
+        <v>2:23</v>
       </c>
       <c r="H58" t="str">
-        <v>Tiny Habits</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
+        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
       </c>
       <c r="L58" t="str">
-        <v>Right In Front Of Me - Tiny Habits</v>
+        <v>waste your pain - Cruz Beckham</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SAME SH!T</v>
+        <v>Strangers</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
+        <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-13</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>SAME SH!T - Single</v>
+        <v>F**k, Marry, Kill</v>
       </c>
       <c r="G59" t="str">
-        <v>3:13</v>
+        <v>2:44</v>
       </c>
       <c r="H59" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Tink</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
+        <v>https://music.apple.com/us/album/strangers/1883252371</v>
       </c>
       <c r="L59" t="str">
-        <v>SAME SH!T - Isaiah Rashad</v>
+        <v>Strangers - Tink</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Children of Light (feat. Max Cavalera)</v>
+        <v>Right In Front Of Me</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
+        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-13</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>The End is Not the End</v>
+        <v>Right In Front Of Me - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>4:12</v>
+        <v>2:45</v>
       </c>
       <c r="H60" t="str">
-        <v>Atreyu</v>
+        <v>Tiny Habits</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
+        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
       </c>
       <c r="L60" t="str">
-        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
+        <v>Right In Front Of Me - Tiny Habits</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Heal</v>
+        <v>SAME SH!T</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/heal/1884661632</v>
+        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-13</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Heal - Single</v>
+        <v>SAME SH!T - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:26</v>
+        <v>3:13</v>
       </c>
       <c r="H61" t="str">
-        <v>HAYLA</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/heal/1884661625</v>
+        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
       </c>
       <c r="L61" t="str">
-        <v>Heal - HAYLA</v>
+        <v>SAME SH!T - Isaiah Rashad</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Free</v>
+        <v>Children of Light (feat. Max Cavalera)</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/free/1886600087</v>
+        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-13</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Songs I Wrote In New York - EP</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G62" t="str">
-        <v>4:13</v>
+        <v>4:12</v>
       </c>
       <c r="H62" t="str">
-        <v>Simone Ashley</v>
+        <v>Atreyu</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/free/1886600085</v>
+        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
       </c>
       <c r="L62" t="str">
-        <v>Free - Simone Ashley</v>
+        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Cállate</v>
+        <v>Heal</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
+        <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-13</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Heal - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>1:59</v>
+        <v>3:26</v>
       </c>
       <c r="H63" t="str">
-        <v>Dua Saleh</v>
+        <v>HAYLA</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
+        <v>https://music.apple.com/us/album/heal/1884661625</v>
       </c>
       <c r="L63" t="str">
-        <v>Cállate - Dua Saleh</v>
+        <v>Heal - HAYLA</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Raindrops</v>
+        <v>Free</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
+        <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-13</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Raindrops - Single</v>
+        <v>Songs I Wrote In New York - EP</v>
       </c>
       <c r="G64" t="str">
-        <v>3:34</v>
+        <v>4:13</v>
       </c>
       <c r="H64" t="str">
-        <v>Rick Astley</v>
+        <v>Simone Ashley</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
+        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
+        <v>https://music.apple.com/us/album/free/1886600085</v>
       </c>
       <c r="L64" t="str">
-        <v>Raindrops - Rick Astley</v>
+        <v>Free - Simone Ashley</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>WORK OF ART</v>
+        <v>Cállate</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
+        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-13</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>PRODIGY</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G65" t="str">
-        <v>2:27</v>
+        <v>1:59</v>
       </c>
       <c r="H65" t="str">
-        <v>Tkandz</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
+        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
       </c>
       <c r="L65" t="str">
-        <v>WORK OF ART - Tkandz</v>
+        <v>Cállate - Dua Saleh</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Scottie Pippen</v>
+        <v>Raindrops</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
+        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-13</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Scottie Pippen - Single</v>
+        <v>Raindrops - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>2:34</v>
+        <v>3:34</v>
       </c>
       <c r="H66" t="str">
-        <v>SUNSHINE BENZI</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
+        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
+        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
       </c>
       <c r="L66" t="str">
-        <v>Scottie Pippen - SUNSHINE BENZI</v>
+        <v>Raindrops - Rick Astley</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Damn Good Actress</v>
+        <v>WORK OF ART</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
+        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-13</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Damn Good Actress - Single</v>
+        <v>PRODIGY</v>
       </c>
       <c r="G67" t="str">
-        <v>2:49</v>
+        <v>2:27</v>
       </c>
       <c r="H67" t="str">
-        <v>Tiffany Stringer</v>
+        <v>Tkandz</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
+        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
+        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
       </c>
       <c r="L67" t="str">
-        <v>Damn Good Actress - Tiffany Stringer</v>
+        <v>WORK OF ART - Tkandz</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ricota</v>
+        <v>Scottie Pippen</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/ricota/1889387735</v>
+        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-13</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Ricota - Single</v>
+        <v>Scottie Pippen - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:25</v>
+        <v>2:34</v>
       </c>
       <c r="H68" t="str">
-        <v>ZULAN</v>
+        <v>SUNSHINE BENZI</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
+        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/ricota/1889387732</v>
+        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
       </c>
       <c r="L68" t="str">
-        <v>Ricota - ZULAN</v>
+        <v>Scottie Pippen - SUNSHINE BENZI</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Kissing The Ground</v>
+        <v>Damn Good Actress</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
+        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-13</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Kissing The Ground - Single</v>
+        <v>Damn Good Actress - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:50</v>
+        <v>2:49</v>
       </c>
       <c r="H69" t="str">
-        <v>Nell Mescal</v>
+        <v>Tiffany Stringer</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
+        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
+        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
       </c>
       <c r="L69" t="str">
-        <v>Kissing The Ground - Nell Mescal</v>
+        <v>Damn Good Actress - Tiffany Stringer</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Joy</v>
+        <v>Ricota</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/joy/1877978274</v>
+        <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-13</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>All In Now</v>
+        <v>Ricota - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:41</v>
+        <v>2:25</v>
       </c>
       <c r="H70" t="str">
-        <v>Dogstar</v>
+        <v>ZULAN</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
+        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/joy/1877978262</v>
+        <v>https://music.apple.com/us/album/ricota/1889387732</v>
       </c>
       <c r="L70" t="str">
-        <v>Joy - Dogstar</v>
+        <v>Ricota - ZULAN</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Amor Bonito</v>
+        <v>Kissing The Ground</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
+        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-13</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>PUERTA ABIERTA</v>
+        <v>Kissing The Ground - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:44</v>
+        <v>3:50</v>
       </c>
       <c r="H71" t="str">
-        <v>Kany García</v>
+        <v>Nell Mescal</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
+        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
       </c>
       <c r="L71" t="str">
-        <v>Amor Bonito - Kany García</v>
+        <v>Kissing The Ground - Nell Mescal</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Patchwork</v>
+        <v>Joy</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
+        <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-13</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Patchwork - Single</v>
+        <v>All In Now</v>
       </c>
       <c r="G72" t="str">
-        <v>3:07</v>
+        <v>3:41</v>
       </c>
       <c r="H72" t="str">
-        <v>Carlita</v>
+        <v>Dogstar</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/carlita/599607197</v>
+        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
+        <v>https://music.apple.com/us/album/joy/1877978262</v>
       </c>
       <c r="L72" t="str">
-        <v>Patchwork - Carlita</v>
+        <v>Joy - Dogstar</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>She's A Devil</v>
+        <v>Amor Bonito</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
+        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-13</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>She's A Devil - Single</v>
+        <v>PUERTA ABIERTA</v>
       </c>
       <c r="G73" t="str">
-        <v>3:24</v>
+        <v>2:44</v>
       </c>
       <c r="H73" t="str">
-        <v>Layton Giordani</v>
+        <v>Kany García</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
+        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
       </c>
       <c r="L73" t="str">
-        <v>She's A Devil - Layton Giordani</v>
+        <v>Amor Bonito - Kany García</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Do It All Alone</v>
+        <v>Patchwork</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
+        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-13</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Patchwork - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:52</v>
+        <v>3:07</v>
       </c>
       <c r="H74" t="str">
-        <v>Rend Collective</v>
+        <v>Carlita</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/carlita/599607197</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
+        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
       </c>
       <c r="L74" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Patchwork - Carlita</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Time</v>
+        <v>She's A Devil</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/time/1880476913</v>
+        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-13</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Time - Single</v>
+        <v>She's A Devil - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:20</v>
+        <v>3:24</v>
       </c>
       <c r="H75" t="str">
-        <v>David Leonard</v>
+        <v>Layton Giordani</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
+        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/time/1880476790</v>
+        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
       </c>
       <c r="L75" t="str">
-        <v>Time - David Leonard</v>
+        <v>She's A Devil - Layton Giordani</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Andamos Ready</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-13</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Andamos Ready - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>3:10</v>
+        <v>2:52</v>
       </c>
       <c r="H76" t="str">
-        <v>Los Tucanes de Tijuana</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
       </c>
       <c r="L76" t="str">
-        <v>Andamos Ready - Los Tucanes de Tijuana</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Van y Vienen</v>
+        <v>Time</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
+        <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-13</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Van y Vienen - Single</v>
+        <v>Time - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:46</v>
+        <v>3:20</v>
       </c>
       <c r="H77" t="str">
-        <v>El Fantasma</v>
+        <v>David Leonard</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
+        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
+        <v>https://music.apple.com/us/album/time/1880476790</v>
       </c>
       <c r="L77" t="str">
-        <v>Van y Vienen - El Fantasma</v>
+        <v>Time - David Leonard</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>No Vuelvas</v>
+        <v>Andamos Ready</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
+        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-13</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>No Vuelvas - Single</v>
+        <v>Andamos Ready - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:46</v>
+        <v>3:10</v>
       </c>
       <c r="H78" t="str">
-        <v>Majo Aguilar</v>
+        <v>Los Tucanes de Tijuana</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
+        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
+        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
       </c>
       <c r="L78" t="str">
-        <v>No Vuelvas - Majo Aguilar</v>
+        <v>Andamos Ready - Los Tucanes de Tijuana</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>RUNNIN</v>
+        <v>Van y Vienen</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/runnin/1886581872</v>
+        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-13</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>RUNNIN - Single</v>
+        <v>Van y Vienen - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:40</v>
+        <v>2:46</v>
       </c>
       <c r="H79" t="str">
-        <v>RUA YOUNG</v>
+        <v>El Fantasma</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
+        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/runnin/1886581868</v>
+        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
       </c>
       <c r="L79" t="str">
-        <v>RUNNIN - RUA YOUNG</v>
+        <v>Van y Vienen - El Fantasma</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Talk You Through It</v>
+        <v>No Vuelvas</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
+        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-13</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Talk You Through It - Single</v>
+        <v>No Vuelvas - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:33</v>
+        <v>3:46</v>
       </c>
       <c r="H80" t="str">
-        <v>Kenyon Dixon</v>
+        <v>Majo Aguilar</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
+        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
+        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
       </c>
       <c r="L80" t="str">
-        <v>Talk You Through It - Kenyon Dixon</v>
+        <v>No Vuelvas - Majo Aguilar</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Partners in Crime</v>
+        <v>RUNNIN</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
+        <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-13</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Born to Kill</v>
+        <v>RUNNIN - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:50</v>
+        <v>2:40</v>
       </c>
       <c r="H81" t="str">
-        <v>Social Distortion</v>
+        <v>RUA YOUNG</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
+        <v>https://music.apple.com/us/album/runnin/1886581868</v>
       </c>
       <c r="L81" t="str">
-        <v>Partners in Crime - Social Distortion</v>
+        <v>RUNNIN - RUA YOUNG</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Change your mind</v>
+        <v>Talk You Through It</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
+        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-13</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Change your mind - Single</v>
+        <v>Talk You Through It - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:21</v>
+        <v>3:33</v>
       </c>
       <c r="H82" t="str">
-        <v>Casper Sage</v>
+        <v>Kenyon Dixon</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
+        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
       </c>
       <c r="L82" t="str">
-        <v>Change your mind - Casper Sage</v>
+        <v>Talk You Through It - Kenyon Dixon</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Bones to Ashes, Dark to Light</v>
+        <v>Partners in Crime</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
+        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-13</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Bones to Ashes, Dark to Light - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G83" t="str">
-        <v>3:29</v>
+        <v>3:50</v>
       </c>
       <c r="H83" t="str">
-        <v>The Franklin Electric</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
+        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
       </c>
       <c r="L83" t="str">
-        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
+        <v>Partners in Crime - Social Distortion</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Venus in the Zinnia</v>
+        <v>Change your mind</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
+        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-13</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Train on the Island</v>
+        <v>Change your mind - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H84" t="str">
-        <v>Aldous Harding</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
+        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
       </c>
       <c r="L84" t="str">
-        <v>Venus in the Zinnia - Aldous Harding</v>
+        <v>Change your mind - Casper Sage</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Lover</v>
+        <v>Bones to Ashes, Dark to Light</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/lover/1878758405</v>
+        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-13</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Lover - Single</v>
+        <v>Bones to Ashes, Dark to Light - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:26</v>
+        <v>3:29</v>
       </c>
       <c r="H85" t="str">
-        <v>Juke Ross</v>
+        <v>The Franklin Electric</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
+        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/lover/1878758400</v>
+        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
       </c>
       <c r="L85" t="str">
-        <v>Lover - Juke Ross</v>
+        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>pink moon</v>
+        <v>Venus in the Zinnia</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
+        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-13</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Train on the Island</v>
       </c>
       <c r="G86" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H86" t="str">
-        <v>runo plum</v>
+        <v>Aldous Harding</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
+        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
       </c>
       <c r="L86" t="str">
-        <v>pink moon - runo plum</v>
+        <v>Venus in the Zinnia - Aldous Harding</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Summer</v>
+        <v>Lover</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/summer/1884646207</v>
+        <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-13</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Summer - Single</v>
+        <v>Lover - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H87" t="str">
-        <v>Tasha</v>
+        <v>Juke Ross</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/summer/1884645989</v>
+        <v>https://music.apple.com/us/album/lover/1878758400</v>
       </c>
       <c r="L87" t="str">
-        <v>Summer - Tasha</v>
+        <v>Lover - Juke Ross</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Lizzie mcguire</v>
+        <v>pink moon</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
+        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-13</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Tearless, thoughtless</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G88" t="str">
-        <v>4:20</v>
+        <v>3:21</v>
       </c>
       <c r="H88" t="str">
-        <v>Nara's Room</v>
+        <v>runo plum</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
+        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
       </c>
       <c r="L88" t="str">
-        <v>Lizzie mcguire - Nara's Room</v>
+        <v>pink moon - runo plum</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Fabienk</v>
+        <v>Summer</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
+        <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-13</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Vol.II</v>
+        <v>Summer - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>6:31</v>
+        <v>3:21</v>
       </c>
       <c r="H89" t="str">
-        <v>Angine de Poitrine</v>
+        <v>Tasha</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
+        <v>https://music.apple.com/us/album/summer/1884645989</v>
       </c>
       <c r="L89" t="str">
-        <v>Fabienk - Angine de Poitrine</v>
+        <v>Summer - Tasha</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>My Girl</v>
+        <v>Lizzie mcguire</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
+        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-13</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Soren - EP</v>
+        <v>Tearless, thoughtless</v>
       </c>
       <c r="G90" t="str">
-        <v>3:45</v>
+        <v>4:20</v>
       </c>
       <c r="H90" t="str">
-        <v>Orca</v>
+        <v>Nara's Room</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
+        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
       </c>
       <c r="L90" t="str">
-        <v>My Girl - Orca</v>
+        <v>Lizzie mcguire - Nara's Room</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Bone Structure</v>
+        <v>Fabienk</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
+        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-13</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Bone Structure - Single</v>
+        <v>Vol.II</v>
       </c>
       <c r="G91" t="str">
-        <v>3:01</v>
+        <v>6:31</v>
       </c>
       <c r="H91" t="str">
-        <v>Dolder</v>
+        <v>Angine de Poitrine</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
+        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
       </c>
       <c r="L91" t="str">
-        <v>Bone Structure - Dolder</v>
+        <v>Fabienk - Angine de Poitrine</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Turning Into Us</v>
+        <v>My Girl</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
+        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-13</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Turning Into Us - Single</v>
+        <v>Soren - EP</v>
       </c>
       <c r="G92" t="str">
-        <v>3:30</v>
+        <v>3:45</v>
       </c>
       <c r="H92" t="str">
-        <v>Rhys Rutherford</v>
+        <v>Orca</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
+        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
       </c>
       <c r="L92" t="str">
-        <v>Turning Into Us - Rhys Rutherford</v>
+        <v>My Girl - Orca</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Bother Me (feat. Victony)</v>
+        <v>Bone Structure</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
+        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-13</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Bother Me (feat. Victony) - Single</v>
+        <v>Bone Structure - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>3:00</v>
+        <v>3:01</v>
       </c>
       <c r="H93" t="str">
-        <v>Osé</v>
+        <v>Dolder</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
+        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
       </c>
       <c r="L93" t="str">
-        <v>Bother Me (feat. Victony) - Osé</v>
+        <v>Bone Structure - Dolder</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Fright</v>
+        <v>Turning Into Us</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/fright/1890396431</v>
+        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-13</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Fright - Single</v>
+        <v>Turning Into Us - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>2:25</v>
+        <v>3:30</v>
       </c>
       <c r="H94" t="str">
-        <v>Creepy Nuts</v>
+        <v>Rhys Rutherford</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
+        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/fright/1890396429</v>
+        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
       </c>
       <c r="L94" t="str">
-        <v>Fright - Creepy Nuts</v>
+        <v>Turning Into Us - Rhys Rutherford</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Smoking In Bed</v>
+        <v>Bother Me (feat. Victony)</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
+        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-13</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Smoking In Bed - Single</v>
+        <v>Bother Me (feat. Victony) - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:24</v>
+        <v>3:00</v>
       </c>
       <c r="H95" t="str">
-        <v>The Bends</v>
+        <v>Osé</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
+        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
+        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
       </c>
       <c r="L95" t="str">
-        <v>Smoking In Bed - The Bends</v>
+        <v>Bother Me (feat. Victony) - Osé</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>The Dissonant Void</v>
+        <v>Fright</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+        <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-13</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Fright - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>2:47</v>
+        <v>2:25</v>
       </c>
       <c r="H96" t="str">
-        <v>At The Gates</v>
+        <v>Creepy Nuts</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+        <v>https://music.apple.com/us/album/fright/1890396429</v>
       </c>
       <c r="L96" t="str">
-        <v>The Dissonant Void - At The Gates</v>
+        <v>Fright - Creepy Nuts</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Nine Days Of Rain</v>
+        <v>Smoking In Bed</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-13</v>
@@ -4061,68 +4061,144 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Smoking In Bed - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>3:51</v>
+        <v>3:24</v>
       </c>
       <c r="H97" t="str">
-        <v>Melvins</v>
+        <v>The Bends</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
       </c>
       <c r="L97" t="str">
-        <v>Nine Days Of Rain - Melvins</v>
+        <v>Smoking In Bed - The Bends</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>The Dissonant Void</v>
+      </c>
+      <c r="B98" t="str">
+        <v/>
+      </c>
+      <c r="C98" t="str">
+        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v>The Ghost of a Future Dead</v>
+      </c>
+      <c r="G98" t="str">
+        <v>2:47</v>
+      </c>
+      <c r="H98" t="str">
+        <v>At The Gates</v>
+      </c>
+      <c r="I98" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J98" t="str">
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+      </c>
+      <c r="K98" t="str">
+        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+      </c>
+      <c r="L98" t="str">
+        <v>The Dissonant Void - At The Gates</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Nine Days Of Rain</v>
+      </c>
+      <c r="B99" t="str">
+        <v/>
+      </c>
+      <c r="C99" t="str">
+        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v>Savage Imperial Death March</v>
+      </c>
+      <c r="G99" t="str">
+        <v>3:51</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Melvins</v>
+      </c>
+      <c r="I99" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J99" t="str">
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
+      </c>
+      <c r="K99" t="str">
+        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+      </c>
+      <c r="L99" t="str">
+        <v>Nine Days Of Rain - Melvins</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <v>Invocation of the Dreamer</v>
       </c>
-      <c r="B98" t="str">
-        <v/>
-      </c>
-      <c r="C98" t="str">
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
-      <c r="D98" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="E98" t="str">
-        <v/>
-      </c>
-      <c r="F98" t="str">
+      <c r="D100" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="G98" t="str">
+      <c r="G100" t="str">
         <v>4:46</v>
       </c>
-      <c r="H98" t="str">
+      <c r="H100" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="I98" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J98" t="str">
+      <c r="I100" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J100" t="str">
         <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
       </c>
-      <c r="K98" t="str">
+      <c r="K100" t="str">
         <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
       </c>
-      <c r="L98" t="str">
+      <c r="L100" t="str">
         <v>Invocation of the Dreamer - Khemmis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/runway/1891472591</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/madwoman/1873116853</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/stuck/1875303118</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/echo/1891104992</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E100" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>i just get worse</v>
+        <v>YOU COULD BE THAT BOY</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-14</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>i just get worse - Single</v>
+        <v>LUCID DREAMS - EP</v>
       </c>
       <c r="G2" t="str">
-        <v>3:25</v>
+        <v>3:14</v>
       </c>
       <c r="H2" t="str">
-        <v>Kevian Kraemer</v>
+        <v>DANNA</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/danna/1891412909</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
       </c>
       <c r="L2" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>YOU COULD BE THAT BOY - DANNA</v>
       </c>
     </row>
     <row r="3">
@@ -816,13 +816,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Sick Of Love</v>
+        <v>i just get worse</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-14</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>The Afterparty</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>3:36</v>
+        <v>3:25</v>
       </c>
       <c r="H12" t="str">
-        <v>Lykke Li</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/sick-of-love/1857952252</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L12" t="str">
-        <v>Sick Of Love - Lykke Li</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Ember</v>
+        <v>Sick Of Love</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/ember/1880484164</v>
+        <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-14</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G13" t="str">
-        <v>3:25</v>
+        <v>3:36</v>
       </c>
       <c r="H13" t="str">
-        <v>Iceage</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/ember/1880484160</v>
+        <v>https://music.apple.com/us/album/sick-of-love/1857952252</v>
       </c>
       <c r="L13" t="str">
-        <v>Ember - Iceage</v>
+        <v>Sick Of Love - Lykke Li</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Turnaround</v>
+        <v>Ember</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
+        <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-14</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Turnaround / I'm Hooked - Single</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G14" t="str">
-        <v>3:14</v>
+        <v>3:25</v>
       </c>
       <c r="H14" t="str">
-        <v>54 Ultra</v>
+        <v>Iceage</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
+        <v>https://music.apple.com/us/album/ember/1880484160</v>
       </c>
       <c r="L14" t="str">
-        <v>Turnaround - 54 Ultra</v>
+        <v>Ember - Iceage</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Turnaround</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-14</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Turnaround / I'm Hooked - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>3:05</v>
+        <v>3:14</v>
       </c>
       <c r="H15" t="str">
-        <v>Labrinth</v>
+        <v>54 Ultra</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
       </c>
       <c r="L15" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Turnaround - 54 Ultra</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Madwoman</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-14</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>3:59</v>
+        <v>3:05</v>
       </c>
       <c r="H16" t="str">
-        <v>Laufey</v>
+        <v>Labrinth</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L16" t="str">
-        <v>Madwoman - Laufey</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Come Clean (Mine)</v>
+        <v>Madwoman</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
+        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-14</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Come Clean (Mine) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G17" t="str">
-        <v>3:33</v>
+        <v>3:59</v>
       </c>
       <c r="H17" t="str">
-        <v>Hilary Duff</v>
+        <v>Laufey</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
+        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
       </c>
       <c r="L17" t="str">
-        <v>Come Clean (Mine) - Hilary Duff</v>
+        <v>Madwoman - Laufey</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>One of Them</v>
+        <v>Come Clean (Mine)</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
+        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-14</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>One of Them - Single</v>
+        <v>Come Clean (Mine) - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>3:24</v>
+        <v>3:33</v>
       </c>
       <c r="H18" t="str">
-        <v>DJ Khaled</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
+        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
       </c>
       <c r="L18" t="str">
-        <v>One of Them - DJ Khaled</v>
+        <v>Come Clean (Mine) - Hilary Duff</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>One of Them</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
+        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-14</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>One of Them - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>2:49</v>
+        <v>3:24</v>
       </c>
       <c r="H19" t="str">
-        <v>Bossman Dlow</v>
+        <v>DJ Khaled</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
+        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
       </c>
       <c r="L19" t="str">
-        <v>Chicken Talkin Bastard - Bossman Dlow</v>
+        <v>One of Them - DJ Khaled</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>stuck</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/stuck/1875303118</v>
+        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-14</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>ghosted - EP</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="G20" t="str">
-        <v>2:41</v>
+        <v>2:49</v>
       </c>
       <c r="H20" t="str">
-        <v>Saint Harison</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/stuck/1875302904</v>
+        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
       </c>
       <c r="L20" t="str">
-        <v>stuck - Saint Harison</v>
+        <v>Chicken Talkin Bastard - Bossman Dlow</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>De Lejitos</v>
+        <v>stuck</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
+        <v>https://music.apple.com/us/song/stuck/1875303118</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-14</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>De Lejitos - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G21" t="str">
-        <v>3:27</v>
+        <v>2:41</v>
       </c>
       <c r="H21" t="str">
-        <v>Jay Wheeler</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
+        <v>https://music.apple.com/us/album/stuck/1875302904</v>
       </c>
       <c r="L21" t="str">
-        <v>De Lejitos - Jay Wheeler</v>
+        <v>stuck - Saint Harison</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Echo</v>
+        <v>De Lejitos</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/echo/1891104992</v>
+        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-14</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Echo - Single</v>
+        <v>De Lejitos - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:39</v>
+        <v>3:27</v>
       </c>
       <c r="H22" t="str">
-        <v>The Chainsmokers</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/echo/1891104991</v>
+        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
       </c>
       <c r="L22" t="str">
-        <v>Echo - The Chainsmokers</v>
+        <v>De Lejitos - Jay Wheeler</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Where We Go</v>
+        <v>Echo</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
+        <v>https://music.apple.com/us/song/echo/1891104992</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-14</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Where We Go - Single</v>
+        <v>Echo - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>3:16</v>
+        <v>3:39</v>
       </c>
       <c r="H23" t="str">
-        <v>Marshmello</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
+        <v>https://music.apple.com/us/album/echo/1891104991</v>
       </c>
       <c r="L23" t="str">
-        <v>Where We Go - Marshmello</v>
+        <v>Echo - The Chainsmokers</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Te hacen falta dos</v>
+        <v>Where We Go</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
+        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-14</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Apambichao</v>
+        <v>Where We Go - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H24" t="str">
-        <v>Manuel Turizo</v>
+        <v>Marshmello</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
+        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
       </c>
       <c r="L24" t="str">
-        <v>Te hacen falta dos - Manuel Turizo</v>
+        <v>Where We Go - Marshmello</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Of All People</v>
+        <v>Te hacen falta dos</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
+        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-14</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Apambichao</v>
       </c>
       <c r="G25" t="str">
-        <v>2:34</v>
+        <v>2:41</v>
       </c>
       <c r="H25" t="str">
-        <v>Foo Fighters</v>
+        <v>Manuel Turizo</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
+        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
       </c>
       <c r="L25" t="str">
-        <v>Of All People - Foo Fighters</v>
+        <v>Te hacen falta dos - Manuel Turizo</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Waves of You</v>
+        <v>Of All People</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
+        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-14</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Waves of You - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G26" t="str">
-        <v>3:15</v>
+        <v>2:34</v>
       </c>
       <c r="H26" t="str">
-        <v>After Hours</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
+        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
       </c>
       <c r="L26" t="str">
-        <v>Waves of You - After Hours</v>
+        <v>Of All People - Foo Fighters</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>idea 1</v>
+        <v>Waves of You</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
+        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-14</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>idea 1 - Single</v>
+        <v>Waves of You - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>3:25</v>
+        <v>3:15</v>
       </c>
       <c r="H27" t="str">
-        <v>Kelela</v>
+        <v>After Hours</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
+        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
       </c>
       <c r="L27" t="str">
-        <v>idea 1 - Kelela</v>
+        <v>Waves of You - After Hours</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Attitude</v>
+        <v>idea 1</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/attitude/1840517116</v>
+        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-14</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Sweat</v>
+        <v>idea 1 - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H28" t="str">
-        <v>Melanie C</v>
+        <v>Kelela</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/attitude/1840516706</v>
+        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
       </c>
       <c r="L28" t="str">
-        <v>Attitude - Melanie C</v>
+        <v>idea 1 - Kelela</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Carrie Bradshaw</v>
+        <v>Attitude</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
+        <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-14</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Carrie Bradshaw - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G29" t="str">
-        <v>2:54</v>
+        <v>3:13</v>
       </c>
       <c r="H29" t="str">
-        <v>Kylie Cantrall</v>
+        <v>Melanie C</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
+        <v>https://music.apple.com/us/album/attitude/1840516706</v>
       </c>
       <c r="L29" t="str">
-        <v>Carrie Bradshaw - Kylie Cantrall</v>
+        <v>Attitude - Melanie C</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Work</v>
+        <v>Carrie Bradshaw</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/work/1885916583</v>
+        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-14</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Work - Single</v>
+        <v>Carrie Bradshaw - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H30" t="str">
-        <v>Pitbull</v>
+        <v>Kylie Cantrall</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/work/1885916578</v>
+        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
       </c>
       <c r="L30" t="str">
-        <v>Work - Pitbull</v>
+        <v>Carrie Bradshaw - Kylie Cantrall</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Obvious</v>
+        <v>Work</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/obvious/1891759136</v>
+        <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-14</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Obvious - Single</v>
+        <v>Work - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>3:06</v>
+        <v>2:51</v>
       </c>
       <c r="H31" t="str">
-        <v>Chris Brown</v>
+        <v>Pitbull</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/obvious/1891759134</v>
+        <v>https://music.apple.com/us/album/work/1885916578</v>
       </c>
       <c r="L31" t="str">
-        <v>Obvious - Chris Brown</v>
+        <v>Work - Pitbull</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>As Time Goes By</v>
+        <v>Obvious</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
+        <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-14</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>CINEMATIC</v>
+        <v>Obvious - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>5:06</v>
+        <v>3:06</v>
       </c>
       <c r="H32" t="str">
-        <v>Josh Groban</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
+        <v>https://music.apple.com/us/album/obvious/1891759134</v>
       </c>
       <c r="L32" t="str">
-        <v>As Time Goes By - Josh Groban</v>
+        <v>Obvious - Chris Brown</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>My Mess</v>
+        <v>As Time Goes By</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
+        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-14</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>CINEMATIC</v>
       </c>
       <c r="G33" t="str">
-        <v>3:11</v>
+        <v>5:06</v>
       </c>
       <c r="H33" t="str">
-        <v>Myles Smith</v>
+        <v>Josh Groban</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
+        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
       </c>
       <c r="L33" t="str">
-        <v>My Mess - Myles Smith</v>
+        <v>As Time Goes By - Josh Groban</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Going Shopping</v>
+        <v>My Mess</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
+        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-14</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Reality Awaits</v>
+        <v>My Mess, My Heart, My Life.</v>
       </c>
       <c r="G34" t="str">
-        <v>4:21</v>
+        <v>3:11</v>
       </c>
       <c r="H34" t="str">
-        <v>The Strokes</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
+        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
       </c>
       <c r="L34" t="str">
-        <v>Going Shopping - The Strokes</v>
+        <v>My Mess - Myles Smith</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Choka Choka</v>
+        <v>Going Shopping</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
+        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-14</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Choka Choka - Single</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G35" t="str">
-        <v>2:11</v>
+        <v>4:21</v>
       </c>
       <c r="H35" t="str">
-        <v>Anitta</v>
+        <v>The Strokes</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
+        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
       </c>
       <c r="L35" t="str">
-        <v>Choka Choka - Anitta</v>
+        <v>Going Shopping - The Strokes</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>side slider</v>
+        <v>Choka Choka</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
+        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-14</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Choka Choka - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>3:47</v>
+        <v>2:11</v>
       </c>
       <c r="H36" t="str">
-        <v>Isaia Huron</v>
+        <v>Anitta</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
+        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
       </c>
       <c r="L36" t="str">
-        <v>side slider - Isaia Huron</v>
+        <v>Choka Choka - Anitta</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Woman I Am</v>
+        <v>side slider</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
+        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-14</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>SE9</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G37" t="str">
-        <v>3:31</v>
+        <v>3:47</v>
       </c>
       <c r="H37" t="str">
-        <v>Skye Newman</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/woman-i-am/1890182220</v>
+        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
       </c>
       <c r="L37" t="str">
-        <v>Woman I Am - Skye Newman</v>
+        <v>side slider - Isaia Huron</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Bubee</v>
+        <v>Woman I Am</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/bubee/1885450942</v>
+        <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-14</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Bubee - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G38" t="str">
-        <v>3:02</v>
+        <v>3:31</v>
       </c>
       <c r="H38" t="str">
-        <v>ILLIT</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/bubee/1885450328</v>
+        <v>https://music.apple.com/us/album/woman-i-am/1890182220</v>
       </c>
       <c r="L38" t="str">
-        <v>Bubee - ILLIT</v>
+        <v>Woman I Am - Skye Newman</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Good Morning</v>
+        <v>Bubee</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
+        <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-14</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>24</v>
+        <v>Bubee - Single</v>
       </c>
       <c r="G39" t="str">
         <v>3:02</v>
       </c>
       <c r="H39" t="str">
-        <v>Alexis Ffrench</v>
+        <v>ILLIT</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
+        <v>https://music.apple.com/us/album/bubee/1885450328</v>
       </c>
       <c r="L39" t="str">
-        <v>Good Morning - Alexis Ffrench</v>
+        <v>Bubee - ILLIT</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Positano</v>
+        <v>Good Morning</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/positano/1886736661</v>
+        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-14</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>24</v>
       </c>
       <c r="G40" t="str">
-        <v>3:27</v>
+        <v>3:02</v>
       </c>
       <c r="H40" t="str">
-        <v>Stephan Moccio</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/positano/1886736650</v>
+        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
       </c>
       <c r="L40" t="str">
-        <v>Positano - Stephan Moccio</v>
+        <v>Good Morning - Alexis Ffrench</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>sophie</v>
+        <v>Positano</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/sophie/1887348036</v>
+        <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-14</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>notes from the in between - EP</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G41" t="str">
-        <v>2:36</v>
+        <v>3:27</v>
       </c>
       <c r="H41" t="str">
-        <v>kenzie</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/sophie/1887348032</v>
+        <v>https://music.apple.com/us/album/positano/1886736650</v>
       </c>
       <c r="L41" t="str">
-        <v>sophie - kenzie</v>
+        <v>Positano - Stephan Moccio</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>kiss goodbye</v>
+        <v>sophie</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
+        <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-14</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>kiss goodbye / brb - Single</v>
+        <v>notes from the in between - EP</v>
       </c>
       <c r="G42" t="str">
-        <v>2:43</v>
+        <v>2:36</v>
       </c>
       <c r="H42" t="str">
-        <v>The Two Lips</v>
+        <v>kenzie</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
+        <v>https://music.apple.com/us/album/sophie/1887348032</v>
       </c>
       <c r="L42" t="str">
-        <v>kiss goodbye - The Two Lips</v>
+        <v>sophie - kenzie</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENTRÉGAME</v>
+        <v>kiss goodbye</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
+        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-14</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>RADIO VENEZUELA</v>
+        <v>kiss goodbye / brb - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:08</v>
+        <v>2:43</v>
       </c>
       <c r="H43" t="str">
-        <v>Chino &amp; Nacho</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
+        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
       </c>
       <c r="L43" t="str">
-        <v>ENTRÉGAME - Chino &amp; Nacho</v>
+        <v>kiss goodbye - The Two Lips</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>EL SENTRITA</v>
+        <v>ENTRÉGAME</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
+        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-14</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>ETERNO</v>
+        <v>RADIO VENEZUELA</v>
       </c>
       <c r="G44" t="str">
-        <v>2:57</v>
+        <v>3:08</v>
       </c>
       <c r="H44" t="str">
-        <v>Calle 24</v>
+        <v>Chino &amp; Nacho</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
+        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
+        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
       </c>
       <c r="L44" t="str">
-        <v>EL SENTRITA - Calle 24</v>
+        <v>ENTRÉGAME - Chino &amp; Nacho</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>SOMETHING IN THE WATER</v>
+        <v>EL SENTRITA</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
+        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-14</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>DAWN PATROL</v>
+        <v>ETERNO</v>
       </c>
       <c r="G45" t="str">
-        <v>2:39</v>
+        <v>2:57</v>
       </c>
       <c r="H45" t="str">
-        <v>PARTY WAVE</v>
+        <v>Calle 24</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
+        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
+        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
       </c>
       <c r="L45" t="str">
-        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
+        <v>EL SENTRITA - Calle 24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Formation</v>
+        <v>SOMETHING IN THE WATER</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/formation/1882714068</v>
+        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-14</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Formation - Single</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G46" t="str">
-        <v>2:36</v>
+        <v>2:39</v>
       </c>
       <c r="H46" t="str">
-        <v>Adekunle Gold</v>
+        <v>PARTY WAVE</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/formation/1882714060</v>
+        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
       </c>
       <c r="L46" t="str">
-        <v>Formation - Adekunle Gold</v>
+        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Who Will You Follow</v>
+        <v>Formation</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
+        <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-14</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Sanctuary</v>
+        <v>Formation - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:55</v>
+        <v>2:36</v>
       </c>
       <c r="H47" t="str">
-        <v>Evanescence</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
+        <v>https://music.apple.com/us/album/formation/1882714060</v>
       </c>
       <c r="L47" t="str">
-        <v>Who Will You Follow - Evanescence</v>
+        <v>Formation - Adekunle Gold</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>That's When You Know</v>
+        <v>Who Will You Follow</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
+        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-14</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>That's When You Know - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G48" t="str">
-        <v>3:13</v>
+        <v>3:55</v>
       </c>
       <c r="H48" t="str">
-        <v>Kygo</v>
+        <v>Evanescence</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
+        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
       </c>
       <c r="L48" t="str">
-        <v>That's When You Know - Kygo</v>
+        <v>Who Will You Follow - Evanescence</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Drinking Game</v>
+        <v>That's When You Know</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
+        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-14</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Drinking Game - Single</v>
+        <v>That's When You Know - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:50</v>
+        <v>3:13</v>
       </c>
       <c r="H49" t="str">
-        <v>Warren Zeiders</v>
+        <v>Kygo</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
+        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
       </c>
       <c r="L49" t="str">
-        <v>Drinking Game - Warren Zeiders</v>
+        <v>That's When You Know - Kygo</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Anything But Me</v>
+        <v>Drinking Game</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
+        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-14</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>In The Feeling</v>
+        <v>Drinking Game - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>4:59</v>
+        <v>2:50</v>
       </c>
       <c r="H50" t="str">
-        <v>Owen Riegling</v>
+        <v>Warren Zeiders</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
+        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
       </c>
       <c r="L50" t="str">
-        <v>Anything But Me - Owen Riegling</v>
+        <v>Drinking Game - Warren Zeiders</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>American Dream</v>
+        <v>Anything But Me</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
+        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-14</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>American Dream - Single</v>
+        <v>In The Feeling</v>
       </c>
       <c r="G51" t="str">
-        <v>4:27</v>
+        <v>4:59</v>
       </c>
       <c r="H51" t="str">
-        <v>Alabama Shakes</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
+        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
       </c>
       <c r="L51" t="str">
-        <v>American Dream - Alabama Shakes</v>
+        <v>Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Already There</v>
+        <v>American Dream</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/already-there/1866700770</v>
+        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-14</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Victory Garden</v>
+        <v>American Dream - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:50</v>
+        <v>4:27</v>
       </c>
       <c r="H52" t="str">
-        <v>Young the Giant</v>
+        <v>Alabama Shakes</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/already-there/1866700309</v>
+        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
       </c>
       <c r="L52" t="str">
-        <v>Already There - Young the Giant</v>
+        <v>American Dream - Alabama Shakes</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ROCK BOTTOM</v>
+        <v>Already There</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
+        <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-14</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>KINDA HARD</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G53" t="str">
-        <v>2:47</v>
+        <v>3:50</v>
       </c>
       <c r="H53" t="str">
-        <v>Bilmuri</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
+        <v>https://music.apple.com/us/album/already-there/1866700309</v>
       </c>
       <c r="L53" t="str">
-        <v>ROCK BOTTOM - Bilmuri</v>
+        <v>Already There - Young the Giant</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Alone For A Year</v>
+        <v>ROCK BOTTOM</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-14</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Joy Next Door</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G54" t="str">
-        <v>3:22</v>
+        <v>2:47</v>
       </c>
       <c r="H54" t="str">
-        <v>The Maine</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
       </c>
       <c r="L54" t="str">
-        <v>Alone For A Year - The Maine</v>
+        <v>ROCK BOTTOM - Bilmuri</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Bring Home My Man</v>
+        <v>Alone For A Year</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
+        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-14</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G55" t="str">
-        <v>4:22</v>
+        <v>3:22</v>
       </c>
       <c r="H55" t="str">
-        <v>Maya Hawke</v>
+        <v>The Maine</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
+        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
       </c>
       <c r="L55" t="str">
-        <v>Bring Home My Man - Maya Hawke</v>
+        <v>Alone For A Year - The Maine</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SUPERMAN</v>
+        <v>Bring Home My Man</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/superman/1890027996</v>
+        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-14</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>SUPERMAN - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G56" t="str">
-        <v>3:24</v>
+        <v>4:22</v>
       </c>
       <c r="H56" t="str">
-        <v>South Arcade</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/superman/1890027995</v>
+        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
       </c>
       <c r="L56" t="str">
-        <v>SUPERMAN - South Arcade</v>
+        <v>Bring Home My Man - Maya Hawke</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>1989</v>
+        <v>SUPERMAN</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/1989/1887250155</v>
+        <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-14</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>1989 - Single</v>
+        <v>SUPERMAN - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:34</v>
+        <v>3:24</v>
       </c>
       <c r="H57" t="str">
-        <v>Nightly</v>
+        <v>South Arcade</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/1989/1887250154</v>
+        <v>https://music.apple.com/us/album/superman/1890027995</v>
       </c>
       <c r="L57" t="str">
-        <v>1989 - Nightly</v>
+        <v>SUPERMAN - South Arcade</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>waste your pain</v>
+        <v>1989</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
+        <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-14</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>waste your pain - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>2:23</v>
+        <v>2:34</v>
       </c>
       <c r="H58" t="str">
-        <v>Cruz Beckham</v>
+        <v>Nightly</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
+        <v>https://music.apple.com/us/album/1989/1887250154</v>
       </c>
       <c r="L58" t="str">
-        <v>waste your pain - Cruz Beckham</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Strangers</v>
+        <v>waste your pain</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/strangers/1883252372</v>
+        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-14</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>F**k, Marry, Kill</v>
+        <v>waste your pain - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:44</v>
+        <v>2:23</v>
       </c>
       <c r="H59" t="str">
-        <v>Tink</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/strangers/1883252371</v>
+        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
       </c>
       <c r="L59" t="str">
-        <v>Strangers - Tink</v>
+        <v>waste your pain - Cruz Beckham</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Right In Front Of Me</v>
+        <v>Strangers</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
+        <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-14</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Right In Front Of Me - Single</v>
+        <v>F**k, Marry, Kill</v>
       </c>
       <c r="G60" t="str">
-        <v>2:45</v>
+        <v>2:44</v>
       </c>
       <c r="H60" t="str">
-        <v>Tiny Habits</v>
+        <v>Tink</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
+        <v>https://music.apple.com/us/album/strangers/1883252371</v>
       </c>
       <c r="L60" t="str">
-        <v>Right In Front Of Me - Tiny Habits</v>
+        <v>Strangers - Tink</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SAME SH!T</v>
+        <v>Right In Front Of Me</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
+        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-14</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>SAME SH!T - Single</v>
+        <v>Right In Front Of Me - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:13</v>
+        <v>2:45</v>
       </c>
       <c r="H61" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Tiny Habits</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
+        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
       </c>
       <c r="L61" t="str">
-        <v>SAME SH!T - Isaiah Rashad</v>
+        <v>Right In Front Of Me - Tiny Habits</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Children of Light (feat. Max Cavalera)</v>
+        <v>SAME SH!T</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
+        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-14</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>The End is Not the End</v>
+        <v>SAME SH!T - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>4:12</v>
+        <v>3:13</v>
       </c>
       <c r="H62" t="str">
-        <v>Atreyu</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
+        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
       </c>
       <c r="L62" t="str">
-        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
+        <v>SAME SH!T - Isaiah Rashad</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Heal</v>
+        <v>Children of Light (feat. Max Cavalera)</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/heal/1884661632</v>
+        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-14</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Heal - Single</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G63" t="str">
-        <v>3:26</v>
+        <v>4:12</v>
       </c>
       <c r="H63" t="str">
-        <v>HAYLA</v>
+        <v>Atreyu</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/heal/1884661625</v>
+        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
       </c>
       <c r="L63" t="str">
-        <v>Heal - HAYLA</v>
+        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Free</v>
+        <v>Heal</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/free/1886600087</v>
+        <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-14</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Songs I Wrote In New York - EP</v>
+        <v>Heal - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>4:13</v>
+        <v>3:26</v>
       </c>
       <c r="H64" t="str">
-        <v>Simone Ashley</v>
+        <v>HAYLA</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
+        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/free/1886600085</v>
+        <v>https://music.apple.com/us/album/heal/1884661625</v>
       </c>
       <c r="L64" t="str">
-        <v>Free - Simone Ashley</v>
+        <v>Heal - HAYLA</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Cállate</v>
+        <v>Free</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
+        <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-14</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Songs I Wrote In New York - EP</v>
       </c>
       <c r="G65" t="str">
-        <v>1:59</v>
+        <v>4:13</v>
       </c>
       <c r="H65" t="str">
-        <v>Dua Saleh</v>
+        <v>Simone Ashley</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
+        <v>https://music.apple.com/us/album/free/1886600085</v>
       </c>
       <c r="L65" t="str">
-        <v>Cállate - Dua Saleh</v>
+        <v>Free - Simone Ashley</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Raindrops</v>
+        <v>Cállate</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
+        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-14</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Raindrops - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G66" t="str">
-        <v>3:34</v>
+        <v>1:59</v>
       </c>
       <c r="H66" t="str">
-        <v>Rick Astley</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
+        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
       </c>
       <c r="L66" t="str">
-        <v>Raindrops - Rick Astley</v>
+        <v>Cállate - Dua Saleh</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>WORK OF ART</v>
+        <v>Raindrops</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
+        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-14</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>PRODIGY</v>
+        <v>Raindrops - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H67" t="str">
-        <v>Tkandz</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
+        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
+        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
       </c>
       <c r="L67" t="str">
-        <v>WORK OF ART - Tkandz</v>
+        <v>Raindrops - Rick Astley</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Scottie Pippen</v>
+        <v>WORK OF ART</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
+        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-14</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Scottie Pippen - Single</v>
+        <v>PRODIGY</v>
       </c>
       <c r="G68" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H68" t="str">
-        <v>SUNSHINE BENZI</v>
+        <v>Tkandz</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
+        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
+        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
       </c>
       <c r="L68" t="str">
-        <v>Scottie Pippen - SUNSHINE BENZI</v>
+        <v>WORK OF ART - Tkandz</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Damn Good Actress</v>
+        <v>Scottie Pippen</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
+        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-14</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Damn Good Actress - Single</v>
+        <v>Scottie Pippen - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:49</v>
+        <v>2:34</v>
       </c>
       <c r="H69" t="str">
-        <v>Tiffany Stringer</v>
+        <v>SUNSHINE BENZI</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
+        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
+        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
       </c>
       <c r="L69" t="str">
-        <v>Damn Good Actress - Tiffany Stringer</v>
+        <v>Scottie Pippen - SUNSHINE BENZI</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ricota</v>
+        <v>Damn Good Actress</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/ricota/1889387735</v>
+        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-14</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Ricota - Single</v>
+        <v>Damn Good Actress - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:25</v>
+        <v>2:49</v>
       </c>
       <c r="H70" t="str">
-        <v>ZULAN</v>
+        <v>Tiffany Stringer</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
+        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/ricota/1889387732</v>
+        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
       </c>
       <c r="L70" t="str">
-        <v>Ricota - ZULAN</v>
+        <v>Damn Good Actress - Tiffany Stringer</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Kissing The Ground</v>
+        <v>Ricota</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
+        <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-14</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Kissing The Ground - Single</v>
+        <v>Ricota - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:50</v>
+        <v>2:25</v>
       </c>
       <c r="H71" t="str">
-        <v>Nell Mescal</v>
+        <v>ZULAN</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
+        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
+        <v>https://music.apple.com/us/album/ricota/1889387732</v>
       </c>
       <c r="L71" t="str">
-        <v>Kissing The Ground - Nell Mescal</v>
+        <v>Ricota - ZULAN</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Joy</v>
+        <v>Kissing The Ground</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/joy/1877978274</v>
+        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-14</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>All In Now</v>
+        <v>Kissing The Ground - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:41</v>
+        <v>3:50</v>
       </c>
       <c r="H72" t="str">
-        <v>Dogstar</v>
+        <v>Nell Mescal</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
+        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/joy/1877978262</v>
+        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
       </c>
       <c r="L72" t="str">
-        <v>Joy - Dogstar</v>
+        <v>Kissing The Ground - Nell Mescal</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Amor Bonito</v>
+        <v>Joy</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
+        <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-14</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>PUERTA ABIERTA</v>
+        <v>All In Now</v>
       </c>
       <c r="G73" t="str">
-        <v>2:44</v>
+        <v>3:41</v>
       </c>
       <c r="H73" t="str">
-        <v>Kany García</v>
+        <v>Dogstar</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
+        <v>https://music.apple.com/us/album/joy/1877978262</v>
       </c>
       <c r="L73" t="str">
-        <v>Amor Bonito - Kany García</v>
+        <v>Joy - Dogstar</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Patchwork</v>
+        <v>Amor Bonito</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
+        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-14</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Patchwork - Single</v>
+        <v>PUERTA ABIERTA</v>
       </c>
       <c r="G74" t="str">
-        <v>3:07</v>
+        <v>2:44</v>
       </c>
       <c r="H74" t="str">
-        <v>Carlita</v>
+        <v>Kany García</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/carlita/599607197</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
+        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
       </c>
       <c r="L74" t="str">
-        <v>Patchwork - Carlita</v>
+        <v>Amor Bonito - Kany García</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>She's A Devil</v>
+        <v>Patchwork</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
+        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-14</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>She's A Devil - Single</v>
+        <v>Patchwork - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:24</v>
+        <v>3:07</v>
       </c>
       <c r="H75" t="str">
-        <v>Layton Giordani</v>
+        <v>Carlita</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
+        <v>https://music.apple.com/us/artist/carlita/599607197</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
+        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
       </c>
       <c r="L75" t="str">
-        <v>She's A Devil - Layton Giordani</v>
+        <v>Patchwork - Carlita</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Do It All Alone</v>
+        <v>She's A Devil</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
+        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-14</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>She's A Devil - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:52</v>
+        <v>3:24</v>
       </c>
       <c r="H76" t="str">
-        <v>Rend Collective</v>
+        <v>Layton Giordani</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
+        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
       </c>
       <c r="L76" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>She's A Devil - Layton Giordani</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Time</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/time/1880476913</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-14</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Time - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:20</v>
+        <v>2:52</v>
       </c>
       <c r="H77" t="str">
-        <v>David Leonard</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/time/1880476790</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
       </c>
       <c r="L77" t="str">
-        <v>Time - David Leonard</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Andamos Ready</v>
+        <v>Time</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
+        <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-14</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Andamos Ready - Single</v>
+        <v>Time - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:10</v>
+        <v>3:20</v>
       </c>
       <c r="H78" t="str">
-        <v>Los Tucanes de Tijuana</v>
+        <v>David Leonard</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
+        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
+        <v>https://music.apple.com/us/album/time/1880476790</v>
       </c>
       <c r="L78" t="str">
-        <v>Andamos Ready - Los Tucanes de Tijuana</v>
+        <v>Time - David Leonard</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Van y Vienen</v>
+        <v>Andamos Ready</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
+        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-14</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Van y Vienen - Single</v>
+        <v>Andamos Ready - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:46</v>
+        <v>3:10</v>
       </c>
       <c r="H79" t="str">
-        <v>El Fantasma</v>
+        <v>Los Tucanes de Tijuana</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
+        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
+        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
       </c>
       <c r="L79" t="str">
-        <v>Van y Vienen - El Fantasma</v>
+        <v>Andamos Ready - Los Tucanes de Tijuana</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>No Vuelvas</v>
+        <v>Van y Vienen</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
+        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-14</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>No Vuelvas - Single</v>
+        <v>Van y Vienen - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:46</v>
+        <v>2:46</v>
       </c>
       <c r="H80" t="str">
-        <v>Majo Aguilar</v>
+        <v>El Fantasma</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
+        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
+        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
       </c>
       <c r="L80" t="str">
-        <v>No Vuelvas - Majo Aguilar</v>
+        <v>Van y Vienen - El Fantasma</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>RUNNIN</v>
+        <v>No Vuelvas</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/runnin/1886581872</v>
+        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-14</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>RUNNIN - Single</v>
+        <v>No Vuelvas - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:40</v>
+        <v>3:46</v>
       </c>
       <c r="H81" t="str">
-        <v>RUA YOUNG</v>
+        <v>Majo Aguilar</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
+        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/runnin/1886581868</v>
+        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
       </c>
       <c r="L81" t="str">
-        <v>RUNNIN - RUA YOUNG</v>
+        <v>No Vuelvas - Majo Aguilar</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Talk You Through It</v>
+        <v>RUNNIN</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
+        <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-14</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Talk You Through It - Single</v>
+        <v>RUNNIN - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:33</v>
+        <v>2:40</v>
       </c>
       <c r="H82" t="str">
-        <v>Kenyon Dixon</v>
+        <v>RUA YOUNG</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
+        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
+        <v>https://music.apple.com/us/album/runnin/1886581868</v>
       </c>
       <c r="L82" t="str">
-        <v>Talk You Through It - Kenyon Dixon</v>
+        <v>RUNNIN - RUA YOUNG</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Partners in Crime</v>
+        <v>Talk You Through It</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
+        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-14</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Born to Kill</v>
+        <v>Talk You Through It - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:50</v>
+        <v>3:33</v>
       </c>
       <c r="H83" t="str">
-        <v>Social Distortion</v>
+        <v>Kenyon Dixon</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
+        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
       </c>
       <c r="L83" t="str">
-        <v>Partners in Crime - Social Distortion</v>
+        <v>Talk You Through It - Kenyon Dixon</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Change your mind</v>
+        <v>Partners in Crime</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
+        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-14</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Change your mind - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G84" t="str">
-        <v>3:21</v>
+        <v>3:50</v>
       </c>
       <c r="H84" t="str">
-        <v>Casper Sage</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
+        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
       </c>
       <c r="L84" t="str">
-        <v>Change your mind - Casper Sage</v>
+        <v>Partners in Crime - Social Distortion</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bones to Ashes, Dark to Light</v>
+        <v>Change your mind</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
+        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-14</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Bones to Ashes, Dark to Light - Single</v>
+        <v>Change your mind - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:29</v>
+        <v>3:21</v>
       </c>
       <c r="H85" t="str">
-        <v>The Franklin Electric</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
+        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
       </c>
       <c r="L85" t="str">
-        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
+        <v>Change your mind - Casper Sage</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Venus in the Zinnia</v>
+        <v>Bones to Ashes, Dark to Light</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
+        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-14</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Train on the Island</v>
+        <v>Bones to Ashes, Dark to Light - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:17</v>
+        <v>3:29</v>
       </c>
       <c r="H86" t="str">
-        <v>Aldous Harding</v>
+        <v>The Franklin Electric</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
+        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
+        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
       </c>
       <c r="L86" t="str">
-        <v>Venus in the Zinnia - Aldous Harding</v>
+        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Lover</v>
+        <v>Venus in the Zinnia</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/lover/1878758405</v>
+        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-14</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Lover - Single</v>
+        <v>Train on the Island</v>
       </c>
       <c r="G87" t="str">
-        <v>3:26</v>
+        <v>3:17</v>
       </c>
       <c r="H87" t="str">
-        <v>Juke Ross</v>
+        <v>Aldous Harding</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
+        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/lover/1878758400</v>
+        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
       </c>
       <c r="L87" t="str">
-        <v>Lover - Juke Ross</v>
+        <v>Venus in the Zinnia - Aldous Harding</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>pink moon</v>
+        <v>Lover</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
+        <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-14</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Lover - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H88" t="str">
-        <v>runo plum</v>
+        <v>Juke Ross</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
+        <v>https://music.apple.com/us/album/lover/1878758400</v>
       </c>
       <c r="L88" t="str">
-        <v>pink moon - runo plum</v>
+        <v>Lover - Juke Ross</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Summer</v>
+        <v>pink moon</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/summer/1884646207</v>
+        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-14</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Summer - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G89" t="str">
         <v>3:21</v>
       </c>
       <c r="H89" t="str">
-        <v>Tasha</v>
+        <v>runo plum</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/summer/1884645989</v>
+        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
       </c>
       <c r="L89" t="str">
-        <v>Summer - Tasha</v>
+        <v>pink moon - runo plum</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Lizzie mcguire</v>
+        <v>Summer</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
+        <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-14</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Tearless, thoughtless</v>
+        <v>Summer - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>4:20</v>
+        <v>3:21</v>
       </c>
       <c r="H90" t="str">
-        <v>Nara's Room</v>
+        <v>Tasha</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
+        <v>https://music.apple.com/us/album/summer/1884645989</v>
       </c>
       <c r="L90" t="str">
-        <v>Lizzie mcguire - Nara's Room</v>
+        <v>Summer - Tasha</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Fabienk</v>
+        <v>Lizzie mcguire</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
+        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-14</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Vol.II</v>
+        <v>Tearless, thoughtless</v>
       </c>
       <c r="G91" t="str">
-        <v>6:31</v>
+        <v>4:20</v>
       </c>
       <c r="H91" t="str">
-        <v>Angine de Poitrine</v>
+        <v>Nara's Room</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
+        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
+        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
       </c>
       <c r="L91" t="str">
-        <v>Fabienk - Angine de Poitrine</v>
+        <v>Lizzie mcguire - Nara's Room</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>My Girl</v>
+        <v>Fabienk</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
+        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-14</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Soren - EP</v>
+        <v>Vol.II</v>
       </c>
       <c r="G92" t="str">
-        <v>3:45</v>
+        <v>6:31</v>
       </c>
       <c r="H92" t="str">
-        <v>Orca</v>
+        <v>Angine de Poitrine</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
+        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
       </c>
       <c r="L92" t="str">
-        <v>My Girl - Orca</v>
+        <v>Fabienk - Angine de Poitrine</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Bone Structure</v>
+        <v>My Girl</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
+        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-14</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Bone Structure - Single</v>
+        <v>Soren - EP</v>
       </c>
       <c r="G93" t="str">
-        <v>3:01</v>
+        <v>3:45</v>
       </c>
       <c r="H93" t="str">
-        <v>Dolder</v>
+        <v>Orca</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
+        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
       </c>
       <c r="L93" t="str">
-        <v>Bone Structure - Dolder</v>
+        <v>My Girl - Orca</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Turning Into Us</v>
+        <v>Bone Structure</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
+        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-14</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Turning Into Us - Single</v>
+        <v>Bone Structure - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H94" t="str">
-        <v>Rhys Rutherford</v>
+        <v>Dolder</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
+        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
       </c>
       <c r="L94" t="str">
-        <v>Turning Into Us - Rhys Rutherford</v>
+        <v>Bone Structure - Dolder</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Bother Me (feat. Victony)</v>
+        <v>Turning Into Us</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
+        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-14</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Bother Me (feat. Victony) - Single</v>
+        <v>Turning Into Us - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:00</v>
+        <v>3:30</v>
       </c>
       <c r="H95" t="str">
-        <v>Osé</v>
+        <v>Rhys Rutherford</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
+        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
+        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
       </c>
       <c r="L95" t="str">
-        <v>Bother Me (feat. Victony) - Osé</v>
+        <v>Turning Into Us - Rhys Rutherford</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Fright</v>
+        <v>Bother Me (feat. Victony)</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/fright/1890396431</v>
+        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-14</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Fright - Single</v>
+        <v>Bother Me (feat. Victony) - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>2:25</v>
+        <v>3:00</v>
       </c>
       <c r="H96" t="str">
-        <v>Creepy Nuts</v>
+        <v>Osé</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
+        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/fright/1890396429</v>
+        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
       </c>
       <c r="L96" t="str">
-        <v>Fright - Creepy Nuts</v>
+        <v>Bother Me (feat. Victony) - Osé</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Smoking In Bed</v>
+        <v>Fright</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
+        <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-14</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Smoking In Bed - Single</v>
+        <v>Fright - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>3:24</v>
+        <v>2:25</v>
       </c>
       <c r="H97" t="str">
-        <v>The Bends</v>
+        <v>Creepy Nuts</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
+        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
+        <v>https://music.apple.com/us/album/fright/1890396429</v>
       </c>
       <c r="L97" t="str">
-        <v>Smoking In Bed - The Bends</v>
+        <v>Fright - Creepy Nuts</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>The Dissonant Void</v>
+        <v>Smoking In Bed</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-14</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Smoking In Bed - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>2:47</v>
+        <v>3:24</v>
       </c>
       <c r="H98" t="str">
-        <v>At The Gates</v>
+        <v>The Bends</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
       </c>
       <c r="L98" t="str">
-        <v>The Dissonant Void - At The Gates</v>
+        <v>Smoking In Bed - The Bends</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Nine Days Of Rain</v>
+        <v>The Dissonant Void</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-14</v>
@@ -4137,68 +4137,106 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G99" t="str">
-        <v>3:51</v>
+        <v>2:47</v>
       </c>
       <c r="H99" t="str">
-        <v>Melvins</v>
+        <v>At The Gates</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
       </c>
       <c r="L99" t="str">
-        <v>Nine Days Of Rain - Melvins</v>
+        <v>The Dissonant Void - At The Gates</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Nine Days Of Rain</v>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
+        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v>Savage Imperial Death March</v>
+      </c>
+      <c r="G100" t="str">
+        <v>3:51</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Melvins</v>
+      </c>
+      <c r="I100" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J100" t="str">
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
+      </c>
+      <c r="K100" t="str">
+        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Nine Days Of Rain - Melvins</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>Invocation of the Dreamer</v>
       </c>
-      <c r="B100" t="str">
-        <v/>
-      </c>
-      <c r="C100" t="str">
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
-      <c r="D100" t="str">
-        <v>2026-04-14</v>
-      </c>
-      <c r="E100" t="str">
-        <v/>
-      </c>
-      <c r="F100" t="str">
+      <c r="D101" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="G100" t="str">
+      <c r="G101" t="str">
         <v>4:46</v>
       </c>
-      <c r="H100" t="str">
+      <c r="H101" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="I100" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J100" t="str">
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
         <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
       </c>
-      <c r="K100" t="str">
+      <c r="K101" t="str">
         <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
       </c>
-      <c r="L100" t="str">
+      <c r="L101" t="str">
         <v>Invocation of the Dreamer - Khemmis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
   </ignoredErrors>
 </worksheet>
 </file>